--- a/data/transactions/أذونات الإضافة لشهر 5.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 5.xlsx
@@ -5,39 +5,30 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252F3D61-5D21-43A2-95D9-14CE517EA24F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D150F8-59D7-4B1C-B701-8FD963B52A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="15600" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$370</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$194</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="386">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -510,9 +501,6 @@
     <t>كوع SST (1/2)بوصه</t>
   </si>
   <si>
-    <t>االرضوان</t>
-  </si>
-  <si>
     <t>10401016</t>
   </si>
   <si>
@@ -594,9 +582,6 @@
     <t>كيس ترمله بنز 6 مم</t>
   </si>
   <si>
-    <t xml:space="preserve">االعصريه </t>
-  </si>
-  <si>
     <t>لفه كابل 4 ×6</t>
   </si>
   <si>
@@ -876,9 +861,6 @@
     <t>لوح SST 1.5 مط 1×2</t>
   </si>
   <si>
-    <t>لوح SST 1.5 لميع 430 1×250</t>
-  </si>
-  <si>
     <t xml:space="preserve">لوح SST 2 مم مصنفر 125 ×250 </t>
   </si>
   <si>
@@ -891,9 +873,6 @@
     <t>هيتر قلايه زيت 9ك</t>
   </si>
   <si>
-    <t>جالون دوكو ازرق كاسي</t>
-  </si>
-  <si>
     <t>شريط صنفره خشن 120</t>
   </si>
   <si>
@@ -973,13 +952,247 @@
   </si>
   <si>
     <t>مسدس دوكو عدل كبير</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مروحه 25 وات </t>
+  </si>
+  <si>
+    <t>4/5/2026</t>
+  </si>
+  <si>
+    <t>27/4/2026</t>
+  </si>
+  <si>
+    <t>نيو المصريه</t>
+  </si>
+  <si>
+    <t>5/5/2026</t>
+  </si>
+  <si>
+    <t>عجله كاوتش 6 بوصه بفرامل</t>
+  </si>
+  <si>
+    <t>عجله كاوتش 6 بوصه بدون فرامل</t>
+  </si>
+  <si>
+    <t>لفه كابل نت 6 مم السويدي</t>
+  </si>
+  <si>
+    <t>لمبه قلاوظ 15 وات</t>
+  </si>
+  <si>
+    <t>لمبه ميتا لايت 400 وات</t>
+  </si>
+  <si>
+    <t>ميكروستش بسلكه</t>
+  </si>
+  <si>
+    <t>لوح خشب مطبخ</t>
+  </si>
+  <si>
+    <t>كالون درج مكتب مربع 2 سكه</t>
+  </si>
+  <si>
+    <t>كباس 1 ح R404</t>
+  </si>
+  <si>
+    <t>مكثف 1 حصان</t>
+  </si>
+  <si>
+    <t>كرتونه غراء ابيض</t>
+  </si>
+  <si>
+    <t>كيس قطن طبي</t>
+  </si>
+  <si>
+    <t>كباس 3/4 حصان R404</t>
+  </si>
+  <si>
+    <t>بلف شحن نحاس طويل</t>
+  </si>
+  <si>
+    <t>سخان باب سيلكتور 5.5 متر</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هيتر درين 2 متر </t>
+  </si>
+  <si>
+    <t>لفه موسير نحاس 1/4</t>
+  </si>
+  <si>
+    <t>لفه مةاسير نحاس 5/16</t>
+  </si>
+  <si>
+    <t>كويل مروحه</t>
+  </si>
+  <si>
+    <t>لفه كابلري 0.55</t>
+  </si>
+  <si>
+    <t>مكثف 1/2 حصان</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مكثف 3/4 حثان </t>
+  </si>
+  <si>
+    <t>14/5/2026</t>
+  </si>
+  <si>
+    <t>كباس 1/2 حصان R404</t>
+  </si>
+  <si>
+    <t>كباس 3/4 حصان R134</t>
+  </si>
+  <si>
+    <t>11301014</t>
+  </si>
+  <si>
+    <t>لوح 1.5 مم SST لميع مغلف 1.25 ×3 م</t>
+  </si>
+  <si>
+    <t>11301033</t>
+  </si>
+  <si>
+    <t>10202014</t>
+  </si>
+  <si>
+    <t>10701007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">جالون دوكو ازرق كابس </t>
+  </si>
+  <si>
+    <t>10701005</t>
+  </si>
+  <si>
+    <t>12101008</t>
+  </si>
+  <si>
+    <t>11105099</t>
+  </si>
+  <si>
+    <t>10701069</t>
+  </si>
+  <si>
+    <t>10701009</t>
+  </si>
+  <si>
+    <t>10701024</t>
+  </si>
+  <si>
+    <t>12101012</t>
+  </si>
+  <si>
+    <t>10107012</t>
+  </si>
+  <si>
+    <t>10107013</t>
+  </si>
+  <si>
+    <t>10409014</t>
+  </si>
+  <si>
+    <t>10409015</t>
+  </si>
+  <si>
+    <t>11105160</t>
+  </si>
+  <si>
+    <t>10209061</t>
+  </si>
+  <si>
+    <t>10209006</t>
+  </si>
+  <si>
+    <t>10701044</t>
+  </si>
+  <si>
+    <t>11105117</t>
+  </si>
+  <si>
+    <t>10202057</t>
+  </si>
+  <si>
+    <t>11302019</t>
+  </si>
+  <si>
+    <t>11302010</t>
+  </si>
+  <si>
+    <t>10702002</t>
+  </si>
+  <si>
+    <t>10601037</t>
+  </si>
+  <si>
+    <t>10601038</t>
+  </si>
+  <si>
+    <t>10207029</t>
+  </si>
+  <si>
+    <t>10205033</t>
+  </si>
+  <si>
+    <t>10205042</t>
+  </si>
+  <si>
+    <t>10106034</t>
+  </si>
+  <si>
+    <t>10102002</t>
+  </si>
+  <si>
+    <t>10104006</t>
+  </si>
+  <si>
+    <t>10701011</t>
+  </si>
+  <si>
+    <t>10701031</t>
+  </si>
+  <si>
+    <t>10202048</t>
+  </si>
+  <si>
+    <t>10202056</t>
+  </si>
+  <si>
+    <t>10106001</t>
+  </si>
+  <si>
+    <t>10106035</t>
+  </si>
+  <si>
+    <t>10102006</t>
+  </si>
+  <si>
+    <t>10102008</t>
+  </si>
+  <si>
+    <t>19-4-2027</t>
+  </si>
+  <si>
+    <t>19-4-2028</t>
+  </si>
+  <si>
+    <t>19-4-2029</t>
+  </si>
+  <si>
+    <t>19-4-2030</t>
+  </si>
+  <si>
+    <t>19-4-2031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">العصريه </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1068,8 +1281,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1085,6 +1310,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1196,7 +1427,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1241,7 +1472,7 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1251,7 +1482,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1261,43 +1492,56 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1580,19 +1824,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M368"/>
+  <dimension ref="A1:M195"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" customWidth="1"/>
     <col min="9" max="10" width="18.7109375" customWidth="1"/>
-    <col min="11" max="11" width="23.140625" customWidth="1"/>
+    <col min="11" max="11" width="30.42578125" customWidth="1"/>
     <col min="12" max="12" width="14.85546875" customWidth="1"/>
     <col min="13" max="13" width="15.140625" customWidth="1"/>
   </cols>
@@ -1609,7 +1853,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1626,7 +1870,7 @@
     </row>
     <row r="4" spans="1:13" s="23" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3310,186 +3554,206 @@
       </c>
     </row>
     <row r="49" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1">
+      <c r="A49" s="25">
         <v>45</v>
       </c>
-      <c r="B49" s="12" t="s">
+      <c r="B49" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="25" t="s">
+      <c r="D49" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="36">
         <v>8.5370000000000008</v>
       </c>
-      <c r="F49" s="28">
+      <c r="F49" s="39">
         <v>149122.79999999999</v>
       </c>
-      <c r="G49" s="25">
+      <c r="G49" s="36">
         <v>1451290</v>
       </c>
-      <c r="H49" s="25">
+      <c r="H49" s="28">
         <v>59830</v>
       </c>
-      <c r="I49" s="9" t="s">
+      <c r="I49" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J49" s="8"/>
-      <c r="K49" s="4" t="s">
+      <c r="J49" s="29"/>
+      <c r="K49" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L49" s="4">
+      <c r="L49" s="27">
         <v>6323</v>
       </c>
-      <c r="M49" s="9">
+      <c r="M49" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1">
+      <c r="A50" s="25">
         <v>46</v>
       </c>
-      <c r="B50" s="12" t="s">
+      <c r="B50" s="26" t="s">
         <v>110</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="26"/>
-      <c r="E50" s="26"/>
-      <c r="F50" s="29"/>
-      <c r="G50" s="26"/>
-      <c r="H50" s="26"/>
-      <c r="I50" s="9" t="s">
+      <c r="D50" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" s="37"/>
+      <c r="F50" s="40"/>
+      <c r="G50" s="37"/>
+      <c r="H50" s="28">
+        <v>59830</v>
+      </c>
+      <c r="I50" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J50" s="8"/>
-      <c r="K50" s="4" t="s">
+      <c r="J50" s="29"/>
+      <c r="K50" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L50" s="4">
+      <c r="L50" s="27">
         <v>6323</v>
       </c>
-      <c r="M50" s="9">
+      <c r="M50" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1">
+      <c r="A51" s="25">
         <v>47</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="26"/>
-      <c r="E51" s="26"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="26"/>
-      <c r="I51" s="9" t="s">
+      <c r="D51" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E51" s="37"/>
+      <c r="F51" s="40"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="28">
+        <v>59830</v>
+      </c>
+      <c r="I51" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J51" s="8"/>
-      <c r="K51" s="4" t="s">
+      <c r="J51" s="29"/>
+      <c r="K51" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L51" s="4">
+      <c r="L51" s="27">
         <v>6323</v>
       </c>
-      <c r="M51" s="9">
+      <c r="M51" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="1">
+      <c r="A52" s="25">
         <v>48</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="27" t="s">
         <v>106</v>
       </c>
-      <c r="D52" s="26"/>
-      <c r="E52" s="26"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="26"/>
-      <c r="H52" s="26"/>
-      <c r="I52" s="9" t="s">
+      <c r="D52" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E52" s="37"/>
+      <c r="F52" s="40"/>
+      <c r="G52" s="37"/>
+      <c r="H52" s="28">
+        <v>59830</v>
+      </c>
+      <c r="I52" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J52" s="8"/>
-      <c r="K52" s="4" t="s">
+      <c r="J52" s="29"/>
+      <c r="K52" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L52" s="4">
+      <c r="L52" s="27">
         <v>6323</v>
       </c>
-      <c r="M52" s="9">
+      <c r="M52" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="1">
+      <c r="A53" s="25">
         <v>49</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="26"/>
-      <c r="H53" s="26"/>
-      <c r="I53" s="9" t="s">
+      <c r="D53" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E53" s="37"/>
+      <c r="F53" s="40"/>
+      <c r="G53" s="37"/>
+      <c r="H53" s="28">
+        <v>59830</v>
+      </c>
+      <c r="I53" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J53" s="8"/>
-      <c r="K53" s="4" t="s">
+      <c r="J53" s="29"/>
+      <c r="K53" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L53" s="4">
+      <c r="L53" s="27">
         <v>6323</v>
       </c>
-      <c r="M53" s="9">
+      <c r="M53" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="1">
+      <c r="A54" s="25">
         <v>50</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="9" t="s">
+      <c r="D54" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E54" s="38"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="28">
+        <v>59830</v>
+      </c>
+      <c r="I54" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J54" s="8"/>
-      <c r="K54" s="4" t="s">
+      <c r="J54" s="29"/>
+      <c r="K54" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L54" s="4">
+      <c r="L54" s="27">
         <v>6323</v>
       </c>
-      <c r="M54" s="9">
+      <c r="M54" s="30">
         <v>46117</v>
       </c>
     </row>
@@ -3611,146 +3875,146 @@
       </c>
     </row>
     <row r="58" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="1">
+      <c r="A58" s="25">
         <v>54</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D58" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E58" s="4">
+      <c r="D58" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E58" s="27">
         <v>70</v>
       </c>
-      <c r="F58" s="28">
+      <c r="F58" s="39">
         <v>157894.73000000001</v>
       </c>
-      <c r="G58" s="25">
+      <c r="G58" s="36">
         <v>913894.73</v>
       </c>
-      <c r="H58" s="4">
+      <c r="H58" s="27">
         <v>59837</v>
       </c>
-      <c r="I58" s="9" t="s">
+      <c r="I58" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J58" s="8"/>
-      <c r="K58" s="4" t="s">
+      <c r="J58" s="29"/>
+      <c r="K58" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L58" s="4">
+      <c r="L58" s="27">
         <v>6325</v>
       </c>
-      <c r="M58" s="9">
+      <c r="M58" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="1">
+      <c r="A59" s="25">
         <v>55</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="27" t="s">
         <v>108</v>
       </c>
-      <c r="D59" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E59" s="4">
+      <c r="D59" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E59" s="27">
         <v>95</v>
       </c>
-      <c r="F59" s="29"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="4">
+      <c r="F59" s="40"/>
+      <c r="G59" s="37"/>
+      <c r="H59" s="27">
         <v>59837</v>
       </c>
-      <c r="I59" s="9" t="s">
+      <c r="I59" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J59" s="8"/>
-      <c r="K59" s="4" t="s">
+      <c r="J59" s="29"/>
+      <c r="K59" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L59" s="4">
+      <c r="L59" s="27">
         <v>6325</v>
       </c>
-      <c r="M59" s="9">
+      <c r="M59" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="1">
+      <c r="A60" s="25">
         <v>56</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="27" t="s">
         <v>124</v>
       </c>
-      <c r="D60" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" s="4">
+      <c r="D60" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="27">
         <v>88</v>
       </c>
-      <c r="F60" s="29"/>
-      <c r="G60" s="26"/>
-      <c r="H60" s="4">
+      <c r="F60" s="40"/>
+      <c r="G60" s="37"/>
+      <c r="H60" s="27">
         <v>59837</v>
       </c>
-      <c r="I60" s="9" t="s">
+      <c r="I60" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J60" s="8"/>
-      <c r="K60" s="4" t="s">
+      <c r="J60" s="29"/>
+      <c r="K60" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L60" s="4">
+      <c r="L60" s="27">
         <v>6325</v>
       </c>
-      <c r="M60" s="9">
+      <c r="M60" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="1">
+      <c r="A61" s="25">
         <v>57</v>
       </c>
-      <c r="B61" s="12" t="s">
+      <c r="B61" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D61" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="4">
+      <c r="D61" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="27">
         <v>80</v>
       </c>
-      <c r="F61" s="30"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="4">
+      <c r="F61" s="41"/>
+      <c r="G61" s="38"/>
+      <c r="H61" s="27">
         <v>59837</v>
       </c>
-      <c r="I61" s="9" t="s">
+      <c r="I61" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="J61" s="8"/>
-      <c r="K61" s="4" t="s">
+      <c r="J61" s="29"/>
+      <c r="K61" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="L61" s="4">
+      <c r="L61" s="27">
         <v>6325</v>
       </c>
-      <c r="M61" s="9">
+      <c r="M61" s="30">
         <v>46117</v>
       </c>
     </row>
@@ -4188,7 +4452,7 @@
         <v>70</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>153</v>
@@ -4213,7 +4477,7 @@
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L73" s="4">
         <v>6328</v>
@@ -4227,7 +4491,7 @@
         <v>71</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>154</v>
@@ -4252,7 +4516,7 @@
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L74" s="4">
         <v>6328</v>
@@ -4266,7 +4530,7 @@
         <v>72</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>155</v>
@@ -4291,7 +4555,7 @@
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L75" s="4">
         <v>6328</v>
@@ -4305,7 +4569,7 @@
         <v>73</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>156</v>
@@ -4330,7 +4594,7 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="4" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="L76" s="4">
         <v>6328</v>
@@ -4344,13 +4608,13 @@
         <v>74</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C77" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>163</v>
       </c>
       <c r="E77" s="4">
         <v>45.5</v>
@@ -4369,7 +4633,7 @@
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L77" s="4">
         <v>6329</v>
@@ -4383,10 +4647,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>16</v>
@@ -4408,7 +4672,7 @@
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L78" s="4">
         <v>6330</v>
@@ -4422,10 +4686,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>16</v>
@@ -4443,11 +4707,11 @@
         <v>6525</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L79" s="4">
         <v>6331</v>
@@ -4461,10 +4725,10 @@
         <v>77</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>16</v>
@@ -4482,11 +4746,11 @@
         <v>6525</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L80" s="4">
         <v>6331</v>
@@ -4500,10 +4764,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>16</v>
@@ -4521,11 +4785,11 @@
         <v>6526</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L81" s="4">
         <v>6332</v>
@@ -4539,10 +4803,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>16</v>
@@ -4560,11 +4824,11 @@
         <v>6526</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L82" s="4">
         <v>6332</v>
@@ -4578,10 +4842,10 @@
         <v>80</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>16</v>
@@ -4599,11 +4863,11 @@
         <v>6526</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="L83" s="4">
         <v>6332</v>
@@ -4617,10 +4881,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C84" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>16</v>
@@ -4638,11 +4902,11 @@
         <v>929</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L84" s="4">
         <v>6333</v>
@@ -4656,10 +4920,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>16</v>
@@ -4677,11 +4941,11 @@
         <v>929</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L85" s="4">
         <v>6333</v>
@@ -4695,10 +4959,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>16</v>
@@ -4716,11 +4980,11 @@
         <v>929</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L86" s="4">
         <v>6333</v>
@@ -4734,10 +4998,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>16</v>
@@ -4755,11 +5019,11 @@
         <v>929</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L87" s="4">
         <v>6333</v>
@@ -4794,11 +5058,11 @@
         <v>929</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L88" s="4">
         <v>6333</v>
@@ -4812,10 +5076,10 @@
         <v>86</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>16</v>
@@ -4833,11 +5097,11 @@
         <v>929</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L89" s="4">
         <v>6333</v>
@@ -4872,11 +5136,11 @@
         <v>929</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L90" s="4">
         <v>6333</v>
@@ -4890,10 +5154,10 @@
         <v>88</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>16</v>
@@ -4911,11 +5175,11 @@
         <v>929</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L91" s="4">
         <v>6333</v>
@@ -4929,10 +5193,10 @@
         <v>89</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>16</v>
@@ -4950,11 +5214,11 @@
         <v>929</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L92" s="4">
         <v>6333</v>
@@ -4968,10 +5232,10 @@
         <v>90</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>16</v>
@@ -4989,11 +5253,11 @@
         <v>929</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L93" s="4">
         <v>6333</v>
@@ -5007,10 +5271,10 @@
         <v>91</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>16</v>
@@ -5028,11 +5292,11 @@
         <v>929</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L94" s="4">
         <v>6333</v>
@@ -5046,10 +5310,10 @@
         <v>92</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>16</v>
@@ -5067,11 +5331,11 @@
         <v>929</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L95" s="4">
         <v>6333</v>
@@ -5085,10 +5349,10 @@
         <v>93</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>16</v>
@@ -5106,11 +5370,11 @@
         <v>929</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L96" s="4">
         <v>6333</v>
@@ -5124,10 +5388,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>16</v>
@@ -5145,11 +5409,11 @@
         <v>929</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L97" s="4">
         <v>6333</v>
@@ -5163,10 +5427,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>16</v>
@@ -5184,11 +5448,11 @@
         <v>928</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L98" s="4">
         <v>6335</v>
@@ -5202,10 +5466,10 @@
         <v>96</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>16</v>
@@ -5223,11 +5487,11 @@
         <v>928</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L99" s="4">
         <v>6335</v>
@@ -5241,10 +5505,10 @@
         <v>97</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D100" s="4" t="s">
         <v>137</v>
@@ -5262,11 +5526,11 @@
         <v>928</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L100" s="4">
         <v>6335</v>
@@ -5280,10 +5544,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>16</v>
@@ -5301,11 +5565,11 @@
         <v>928</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L101" s="4">
         <v>6335</v>
@@ -5319,10 +5583,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>16</v>
@@ -5340,11 +5604,11 @@
         <v>928</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L102" s="4">
         <v>6335</v>
@@ -5358,10 +5622,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>16</v>
@@ -5379,11 +5643,11 @@
         <v>928</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L103" s="4">
         <v>6335</v>
@@ -5397,10 +5661,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C104" s="15" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>16</v>
@@ -5418,11 +5682,11 @@
         <v>928</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L104" s="4">
         <v>6335</v>
@@ -5436,10 +5700,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D105" s="4" t="s">
         <v>137</v>
@@ -5457,11 +5721,11 @@
         <v>928</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J105" s="8"/>
       <c r="K105" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L105" s="4">
         <v>6335</v>
@@ -5475,10 +5739,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>16</v>
@@ -5496,11 +5760,11 @@
         <v>928</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J106" s="8"/>
       <c r="K106" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L106" s="4">
         <v>6335</v>
@@ -5514,10 +5778,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>16</v>
@@ -5535,11 +5799,11 @@
         <v>928</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L107" s="4">
         <v>6335</v>
@@ -5553,10 +5817,10 @@
         <v>105</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D108" s="4" t="s">
         <v>137</v>
@@ -5574,11 +5838,11 @@
         <v>928</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="4" t="s">
-        <v>185</v>
+        <v>385</v>
       </c>
       <c r="L108" s="4">
         <v>6335</v>
@@ -5592,10 +5856,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D109" s="4" t="s">
         <v>137</v>
@@ -5613,11 +5877,11 @@
         <v>81</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L109" s="4">
         <v>6336</v>
@@ -5631,10 +5895,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>16</v>
@@ -5652,11 +5916,11 @@
         <v>81</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J110" s="8"/>
       <c r="K110" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L110" s="4">
         <v>6336</v>
@@ -5670,10 +5934,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>16</v>
@@ -5691,11 +5955,11 @@
         <v>81</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J111" s="8"/>
       <c r="K111" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L111" s="4">
         <v>6336</v>
@@ -5709,10 +5973,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>16</v>
@@ -5730,11 +5994,11 @@
         <v>81</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L112" s="4">
         <v>6336</v>
@@ -5748,10 +6012,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>16</v>
@@ -5769,11 +6033,11 @@
         <v>81</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J113" s="8"/>
       <c r="K113" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L113" s="4">
         <v>6336</v>
@@ -5787,10 +6051,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>16</v>
@@ -5808,11 +6072,11 @@
         <v>81</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J114" s="8"/>
       <c r="K114" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L114" s="4">
         <v>6336</v>
@@ -5826,10 +6090,10 @@
         <v>113</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D115" s="17" t="s">
         <v>16</v>
@@ -5847,11 +6111,11 @@
         <v>1755</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J115" s="19"/>
       <c r="K115" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L115" s="17">
         <v>6337</v>
@@ -5865,10 +6129,10 @@
         <v>114</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D116" s="17" t="s">
         <v>16</v>
@@ -5886,11 +6150,11 @@
         <v>1755</v>
       </c>
       <c r="I116" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J116" s="19"/>
       <c r="K116" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L116" s="17">
         <v>6337</v>
@@ -5904,10 +6168,10 @@
         <v>115</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D117" s="17" t="s">
         <v>16</v>
@@ -5925,11 +6189,11 @@
         <v>1755</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J117" s="19"/>
       <c r="K117" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L117" s="17">
         <v>6337</v>
@@ -5943,10 +6207,10 @@
         <v>116</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D118" s="17" t="s">
         <v>16</v>
@@ -5964,11 +6228,11 @@
         <v>1755</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J118" s="19"/>
       <c r="K118" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L118" s="17">
         <v>6337</v>
@@ -5982,10 +6246,10 @@
         <v>117</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>16</v>
@@ -6003,11 +6267,11 @@
         <v>85</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J119" s="8"/>
       <c r="K119" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L119" s="4">
         <v>6339</v>
@@ -6021,10 +6285,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>16</v>
@@ -6042,11 +6306,11 @@
         <v>85</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J120" s="8"/>
       <c r="K120" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L120" s="4">
         <v>6339</v>
@@ -6060,10 +6324,10 @@
         <v>119</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>16</v>
@@ -6081,11 +6345,11 @@
         <v>85</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J121" s="8"/>
       <c r="K121" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L121" s="4">
         <v>6339</v>
@@ -6099,10 +6363,10 @@
         <v>120</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>16</v>
@@ -6120,11 +6384,11 @@
         <v>85</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J122" s="8"/>
       <c r="K122" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L122" s="4">
         <v>6339</v>
@@ -6138,10 +6402,10 @@
         <v>121</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>16</v>
@@ -6159,11 +6423,11 @@
         <v>85</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J123" s="8"/>
       <c r="K123" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L123" s="4">
         <v>6339</v>
@@ -6177,10 +6441,10 @@
         <v>122</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>16</v>
@@ -6198,11 +6462,11 @@
         <v>85</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J124" s="8"/>
       <c r="K124" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L124" s="4">
         <v>6339</v>
@@ -6216,10 +6480,10 @@
         <v>123</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>16</v>
@@ -6237,11 +6501,11 @@
         <v>86</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J125" s="8"/>
       <c r="K125" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L125" s="4">
         <v>6340</v>
@@ -6255,10 +6519,10 @@
         <v>124</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>16</v>
@@ -6276,11 +6540,11 @@
         <v>86</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J126" s="8"/>
       <c r="K126" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L126" s="4">
         <v>6340</v>
@@ -6294,10 +6558,10 @@
         <v>125</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>16</v>
@@ -6315,11 +6579,11 @@
         <v>86</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J127" s="8"/>
       <c r="K127" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L127" s="4">
         <v>6340</v>
@@ -6333,10 +6597,10 @@
         <v>126</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>16</v>
@@ -6354,11 +6618,11 @@
         <v>86</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="J128" s="8"/>
       <c r="K128" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L128" s="4">
         <v>6340</v>
@@ -6372,10 +6636,10 @@
         <v>127</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>16</v>
@@ -6393,11 +6657,11 @@
         <v>722</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J129" s="8"/>
       <c r="K129" s="4" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L129" s="4">
         <v>6341</v>
@@ -6411,10 +6675,10 @@
         <v>128</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>16</v>
@@ -6432,17 +6696,17 @@
         <v>89</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L130" s="4">
         <v>6342</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6450,10 +6714,10 @@
         <v>129</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>16</v>
@@ -6471,17 +6735,17 @@
         <v>89</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L131" s="4">
         <v>6342</v>
       </c>
       <c r="M131" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6489,10 +6753,10 @@
         <v>130</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>16</v>
@@ -6510,17 +6774,17 @@
         <v>89</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J132" s="8"/>
       <c r="K132" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L132" s="4">
         <v>6342</v>
       </c>
       <c r="M132" s="9" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6528,10 +6792,10 @@
         <v>131</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D133" s="16" t="s">
         <v>16</v>
@@ -6549,11 +6813,11 @@
         <v>19241</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="J133" s="8"/>
       <c r="K133" s="4" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L133" s="4">
         <v>6343</v>
@@ -6563,168 +6827,212 @@
       </c>
     </row>
     <row r="134" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="1">
+      <c r="A134" s="25">
         <v>132</v>
       </c>
-      <c r="B134" s="12" t="s">
+      <c r="B134" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="C134" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D134" s="25" t="s">
+      <c r="C134" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="D134" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E134" s="25">
+      <c r="E134" s="36">
         <v>109.649</v>
       </c>
-      <c r="F134" s="25">
+      <c r="F134" s="36">
         <v>109.649</v>
       </c>
-      <c r="G134" s="25">
+      <c r="G134" s="36">
         <v>230372.8</v>
       </c>
-      <c r="H134" s="25">
+      <c r="H134" s="28">
         <v>59846</v>
       </c>
-      <c r="I134" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="J134" s="8"/>
+      <c r="I134" s="35" t="s">
+        <v>168</v>
+      </c>
+      <c r="J134" s="29"/>
       <c r="K134" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="L134" s="4">
+      <c r="L134" s="27">
         <v>6338</v>
       </c>
-      <c r="M134" s="9">
+      <c r="M134" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="1">
+      <c r="A135" s="25">
         <v>133</v>
       </c>
-      <c r="B135" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="C135" s="4" t="s">
+      <c r="B135" s="26" t="s">
+        <v>279</v>
+      </c>
+      <c r="C135" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="D135" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E135" s="37"/>
+      <c r="F135" s="37"/>
+      <c r="G135" s="37"/>
+      <c r="H135" s="28">
+        <v>59846</v>
+      </c>
+      <c r="I135" s="35" t="s">
+        <v>380</v>
+      </c>
+      <c r="J135" s="29"/>
+      <c r="K135" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L135" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M135" s="30">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="25">
+        <v>134</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C136" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D136" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E136" s="37"/>
+      <c r="F136" s="37"/>
+      <c r="G136" s="37"/>
+      <c r="H136" s="28">
+        <v>59846</v>
+      </c>
+      <c r="I136" s="35" t="s">
+        <v>381</v>
+      </c>
+      <c r="J136" s="29"/>
+      <c r="K136" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L136" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M136" s="30">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="25">
+        <v>135</v>
+      </c>
+      <c r="B137" s="32" t="s">
+        <v>338</v>
+      </c>
+      <c r="C137" s="33" t="s">
+        <v>339</v>
+      </c>
+      <c r="D137" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E137" s="38"/>
+      <c r="F137" s="38"/>
+      <c r="G137" s="38"/>
+      <c r="H137" s="28">
+        <v>59846</v>
+      </c>
+      <c r="I137" s="35" t="s">
+        <v>382</v>
+      </c>
+      <c r="J137" s="29"/>
+      <c r="K137" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L137" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M137" s="30">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="25">
+        <v>136</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="C138" s="27" t="s">
+        <v>277</v>
+      </c>
+      <c r="D138" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E138" s="36">
+        <v>2.101</v>
+      </c>
+      <c r="F138" s="36">
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G138" s="36">
+        <v>283368.40000000002</v>
+      </c>
+      <c r="H138" s="28">
+        <v>59846</v>
+      </c>
+      <c r="I138" s="35" t="s">
+        <v>383</v>
+      </c>
+      <c r="J138" s="29"/>
+      <c r="K138" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L138" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M138" s="30">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="25">
+        <v>137</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="C139" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="D135" s="26"/>
-      <c r="E135" s="26"/>
-      <c r="F135" s="26"/>
-      <c r="G135" s="26"/>
-      <c r="H135" s="26"/>
-      <c r="I135" s="32"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="35"/>
-      <c r="L135" s="4">
+      <c r="D139" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="E139" s="38"/>
+      <c r="F139" s="38"/>
+      <c r="G139" s="38"/>
+      <c r="H139" s="28">
+        <v>59846</v>
+      </c>
+      <c r="I139" s="35" t="s">
+        <v>384</v>
+      </c>
+      <c r="J139" s="29"/>
+      <c r="K139" s="34" t="s">
+        <v>119</v>
+      </c>
+      <c r="L139" s="27">
         <v>6338</v>
       </c>
-      <c r="M135" s="9">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="1">
-        <v>134</v>
-      </c>
-      <c r="B136" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="C136" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D136" s="26"/>
-      <c r="E136" s="26"/>
-      <c r="F136" s="26"/>
-      <c r="G136" s="26"/>
-      <c r="H136" s="26"/>
-      <c r="I136" s="32"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="35"/>
-      <c r="L136" s="4">
-        <v>6338</v>
-      </c>
-      <c r="M136" s="9">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="137" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="1">
-        <v>135</v>
-      </c>
-      <c r="B137" s="6"/>
-      <c r="C137" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D137" s="26"/>
-      <c r="E137" s="27"/>
-      <c r="F137" s="27"/>
-      <c r="G137" s="27"/>
-      <c r="H137" s="26"/>
-      <c r="I137" s="32"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="35"/>
-      <c r="L137" s="4">
-        <v>6338</v>
-      </c>
-      <c r="M137" s="9">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="1">
-        <v>136</v>
-      </c>
-      <c r="B138" s="6"/>
-      <c r="C138" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="D138" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="E138" s="25">
-        <v>2.101</v>
-      </c>
-      <c r="F138" s="25">
-        <v>157.89400000000001</v>
-      </c>
-      <c r="G138" s="25">
-        <v>283368.40000000002</v>
-      </c>
-      <c r="H138" s="26"/>
-      <c r="I138" s="32"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="35"/>
-      <c r="L138" s="4">
-        <v>6338</v>
-      </c>
-      <c r="M138" s="9">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="1">
-        <v>137</v>
-      </c>
-      <c r="B139" s="6"/>
-      <c r="C139" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="D139" s="27"/>
-      <c r="E139" s="27"/>
-      <c r="F139" s="27"/>
-      <c r="G139" s="27"/>
-      <c r="H139" s="27"/>
-      <c r="I139" s="33"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="36"/>
-      <c r="L139" s="4">
-        <v>6338</v>
-      </c>
-      <c r="M139" s="9">
+      <c r="M139" s="30">
         <v>46117</v>
       </c>
     </row>
@@ -6732,9 +7040,11 @@
       <c r="A140" s="1">
         <v>138</v>
       </c>
-      <c r="B140" s="24"/>
+      <c r="B140" s="11" t="s">
+        <v>341</v>
+      </c>
       <c r="C140" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>16</v>
@@ -6756,22 +7066,24 @@
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L140" s="4">
         <v>6344</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>139</v>
       </c>
-      <c r="B141" s="6"/>
-      <c r="C141" s="4" t="s">
-        <v>284</v>
+      <c r="B141" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="C141" s="14" t="s">
+        <v>343</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>16</v>
@@ -6793,22 +7105,24 @@
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L141" s="4">
         <v>6345</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>140</v>
       </c>
-      <c r="B142" s="6"/>
+      <c r="B142" s="12" t="s">
+        <v>146</v>
+      </c>
       <c r="C142" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>16</v>
@@ -6830,22 +7144,24 @@
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L142" s="4">
         <v>6345</v>
       </c>
       <c r="M142" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>141</v>
       </c>
-      <c r="B143" s="6"/>
+      <c r="B143" s="12" t="s">
+        <v>344</v>
+      </c>
       <c r="C143" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>16</v>
@@ -6867,22 +7183,24 @@
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L143" s="4">
         <v>6345</v>
       </c>
       <c r="M143" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>142</v>
       </c>
-      <c r="B144" s="6"/>
+      <c r="B144" s="12" t="s">
+        <v>345</v>
+      </c>
       <c r="C144" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>16</v>
@@ -6904,22 +7222,24 @@
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L144" s="4">
         <v>6345</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>143</v>
       </c>
-      <c r="B145" s="6"/>
+      <c r="B145" s="12" t="s">
+        <v>346</v>
+      </c>
       <c r="C145" s="4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>16</v>
@@ -6941,13 +7261,13 @@
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L145" s="4">
         <v>6345</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6956,7 +7276,7 @@
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>16</v>
@@ -6978,22 +7298,24 @@
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L146" s="4">
         <v>6345</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>145</v>
       </c>
-      <c r="B147" s="6"/>
+      <c r="B147" s="12" t="s">
+        <v>347</v>
+      </c>
       <c r="C147" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>16</v>
@@ -7015,22 +7337,24 @@
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L147" s="4">
         <v>6345</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>146</v>
       </c>
-      <c r="B148" s="6"/>
+      <c r="B148" s="12" t="s">
+        <v>348</v>
+      </c>
       <c r="C148" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>16</v>
@@ -7052,22 +7376,24 @@
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L148" s="4">
         <v>6345</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>147</v>
       </c>
-      <c r="B149" s="6"/>
+      <c r="B149" s="12" t="s">
+        <v>349</v>
+      </c>
       <c r="C149" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>16</v>
@@ -7089,22 +7415,24 @@
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L149" s="4">
         <v>6345</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>148</v>
       </c>
-      <c r="B150" s="6"/>
+      <c r="B150" s="12" t="s">
+        <v>350</v>
+      </c>
       <c r="C150" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>16</v>
@@ -7126,22 +7454,24 @@
       </c>
       <c r="J150" s="8"/>
       <c r="K150" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L150" s="4">
         <v>6345</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>149</v>
       </c>
-      <c r="B151" s="6"/>
+      <c r="B151" s="11" t="s">
+        <v>351</v>
+      </c>
       <c r="C151" s="4" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>16</v>
@@ -7163,22 +7493,24 @@
       </c>
       <c r="J151" s="8"/>
       <c r="K151" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L151" s="4">
         <v>6347</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>150</v>
       </c>
-      <c r="B152" s="6"/>
+      <c r="B152" s="11" t="s">
+        <v>352</v>
+      </c>
       <c r="C152" s="4" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>16</v>
@@ -7200,22 +7532,24 @@
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L152" s="4">
         <v>6347</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>151</v>
       </c>
-      <c r="B153" s="6"/>
+      <c r="B153" s="12" t="s">
+        <v>353</v>
+      </c>
       <c r="C153" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>16</v>
@@ -7237,22 +7571,24 @@
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L153" s="4">
         <v>6347</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>152</v>
       </c>
-      <c r="B154" s="6"/>
+      <c r="B154" s="12" t="s">
+        <v>354</v>
+      </c>
       <c r="C154" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>16</v>
@@ -7274,22 +7610,24 @@
       </c>
       <c r="J154" s="8"/>
       <c r="K154" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L154" s="4">
         <v>6347</v>
       </c>
       <c r="M154" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>153</v>
       </c>
-      <c r="B155" s="6"/>
+      <c r="B155" s="12" t="s">
+        <v>355</v>
+      </c>
       <c r="C155" s="4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>16</v>
@@ -7311,22 +7649,24 @@
       </c>
       <c r="J155" s="8"/>
       <c r="K155" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L155" s="4">
         <v>6347</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>154</v>
       </c>
-      <c r="B156" s="6"/>
+      <c r="B156" s="11" t="s">
+        <v>356</v>
+      </c>
       <c r="C156" s="4" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>16</v>
@@ -7344,11 +7684,11 @@
         <v>93</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J156" s="8"/>
       <c r="K156" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L156" s="4">
         <v>6348</v>
@@ -7361,9 +7701,11 @@
       <c r="A157" s="1">
         <v>155</v>
       </c>
-      <c r="B157" s="6"/>
+      <c r="B157" s="11" t="s">
+        <v>357</v>
+      </c>
       <c r="C157" s="4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>16</v>
@@ -7381,11 +7723,11 @@
         <v>93</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L157" s="4">
         <v>6348</v>
@@ -7398,9 +7740,11 @@
       <c r="A158" s="1">
         <v>156</v>
       </c>
-      <c r="B158" s="6"/>
+      <c r="B158" s="12" t="s">
+        <v>358</v>
+      </c>
       <c r="C158" s="4" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>16</v>
@@ -7418,11 +7762,11 @@
         <v>93</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L158" s="4">
         <v>6348</v>
@@ -7435,9 +7779,11 @@
       <c r="A159" s="1">
         <v>157</v>
       </c>
-      <c r="B159" s="6"/>
+      <c r="B159" s="12" t="s">
+        <v>359</v>
+      </c>
       <c r="C159" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>16</v>
@@ -7455,11 +7801,11 @@
         <v>93</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L159" s="4">
         <v>6348</v>
@@ -7472,9 +7818,11 @@
       <c r="A160" s="1">
         <v>158</v>
       </c>
-      <c r="B160" s="6"/>
+      <c r="B160" s="11" t="s">
+        <v>360</v>
+      </c>
       <c r="C160" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>16</v>
@@ -7492,11 +7840,11 @@
         <v>93</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="4" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="L160" s="4">
         <v>6348</v>
@@ -7509,9 +7857,11 @@
       <c r="A161" s="1">
         <v>159</v>
       </c>
-      <c r="B161" s="6"/>
+      <c r="B161" s="12" t="s">
+        <v>361</v>
+      </c>
       <c r="C161" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>16</v>
@@ -7529,7 +7879,7 @@
         <v>713</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="4" t="s">
@@ -7546,9 +7896,11 @@
       <c r="A162" s="1">
         <v>160</v>
       </c>
-      <c r="B162" s="6"/>
+      <c r="B162" s="12" t="s">
+        <v>362</v>
+      </c>
       <c r="C162" s="4" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>16</v>
@@ -7566,7 +7918,7 @@
         <v>713</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="4" t="s">
@@ -7583,9 +7935,11 @@
       <c r="A163" s="1">
         <v>161</v>
       </c>
-      <c r="B163" s="6"/>
+      <c r="B163" s="12" t="s">
+        <v>363</v>
+      </c>
       <c r="C163" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>16</v>
@@ -7603,11 +7957,11 @@
         <v>6350</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="4" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="L163" s="4">
         <v>6350</v>
@@ -7620,2333 +7974,1223 @@
       <c r="A164" s="1">
         <v>162</v>
       </c>
-      <c r="B164" s="6"/>
-      <c r="C164" s="4"/>
-      <c r="D164" s="4"/>
-      <c r="E164" s="4"/>
-      <c r="F164" s="4"/>
-      <c r="G164" s="4"/>
-      <c r="H164" s="4"/>
-      <c r="I164" s="9"/>
+      <c r="B164" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C164" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D164" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E164" s="4">
+        <v>1</v>
+      </c>
+      <c r="F164" s="4">
+        <v>480</v>
+      </c>
+      <c r="G164" s="4">
+        <v>480</v>
+      </c>
+      <c r="H164" s="4">
+        <v>26</v>
+      </c>
+      <c r="I164" s="9" t="s">
+        <v>304</v>
+      </c>
       <c r="J164" s="8"/>
-      <c r="K164" s="4"/>
-      <c r="L164" s="4"/>
-      <c r="M164" s="9"/>
+      <c r="K164" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L164" s="4">
+        <v>6351</v>
+      </c>
+      <c r="M164" s="9" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="165" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>163</v>
       </c>
-      <c r="B165" s="6"/>
-      <c r="C165" s="4"/>
-      <c r="D165" s="4"/>
-      <c r="E165" s="4"/>
-      <c r="F165" s="4"/>
-      <c r="G165" s="4"/>
-      <c r="H165" s="4"/>
-      <c r="I165" s="9"/>
+      <c r="B165" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="D165" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E165" s="4">
+        <v>10</v>
+      </c>
+      <c r="F165" s="4">
+        <v>275</v>
+      </c>
+      <c r="G165" s="4">
+        <v>27500</v>
+      </c>
+      <c r="H165" s="4">
+        <v>141</v>
+      </c>
+      <c r="I165" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="J165" s="8"/>
-      <c r="K165" s="4"/>
-      <c r="L165" s="4"/>
-      <c r="M165" s="9"/>
+      <c r="K165" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L165" s="4">
+        <v>6358</v>
+      </c>
+      <c r="M165" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="166" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>164</v>
       </c>
-      <c r="B166" s="6"/>
-      <c r="C166" s="4"/>
-      <c r="D166" s="4"/>
-      <c r="E166" s="4"/>
-      <c r="F166" s="4"/>
-      <c r="G166" s="4"/>
-      <c r="H166" s="4"/>
-      <c r="I166" s="9"/>
+      <c r="B166" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C166" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D166" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E166" s="4">
+        <v>10</v>
+      </c>
+      <c r="F166" s="4">
+        <v>1025</v>
+      </c>
+      <c r="G166" s="4">
+        <v>10250</v>
+      </c>
+      <c r="H166" s="4">
+        <v>1528</v>
+      </c>
+      <c r="I166" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="J166" s="8"/>
-      <c r="K166" s="4"/>
-      <c r="L166" s="4"/>
-      <c r="M166" s="9"/>
+      <c r="K166" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L166" s="4">
+        <v>6359</v>
+      </c>
+      <c r="M166" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="167" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>165</v>
       </c>
-      <c r="B167" s="6"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
-      <c r="F167" s="4"/>
-      <c r="G167" s="4"/>
-      <c r="H167" s="4"/>
-      <c r="I167" s="9"/>
+      <c r="B167" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="C167" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="D167" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E167" s="4">
+        <v>10</v>
+      </c>
+      <c r="F167" s="4">
+        <v>900</v>
+      </c>
+      <c r="G167" s="4">
+        <v>9000</v>
+      </c>
+      <c r="H167" s="4">
+        <v>1528</v>
+      </c>
+      <c r="I167" s="9" t="s">
+        <v>310</v>
+      </c>
       <c r="J167" s="8"/>
-      <c r="K167" s="4"/>
-      <c r="L167" s="4"/>
-      <c r="M167" s="9"/>
+      <c r="K167" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L167" s="4">
+        <v>6359</v>
+      </c>
+      <c r="M167" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="168" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>166</v>
       </c>
-      <c r="B168" s="6"/>
-      <c r="C168" s="4"/>
-      <c r="D168" s="4"/>
-      <c r="E168" s="4"/>
-      <c r="F168" s="4"/>
-      <c r="G168" s="4"/>
-      <c r="H168" s="4"/>
-      <c r="I168" s="9"/>
+      <c r="B168" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="C168" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D168" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E168" s="4">
+        <v>1</v>
+      </c>
+      <c r="F168" s="4">
+        <v>11000</v>
+      </c>
+      <c r="G168" s="4">
+        <v>11000</v>
+      </c>
+      <c r="H168" s="4">
+        <v>142</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J168" s="8"/>
-      <c r="K168" s="4"/>
-      <c r="L168" s="4"/>
-      <c r="M168" s="9"/>
+      <c r="K168" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L168" s="4">
+        <v>6360</v>
+      </c>
+      <c r="M168" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="169" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>167</v>
       </c>
-      <c r="B169" s="6"/>
-      <c r="C169" s="4"/>
-      <c r="D169" s="4"/>
-      <c r="E169" s="4"/>
-      <c r="F169" s="4"/>
-      <c r="G169" s="4"/>
-      <c r="H169" s="4"/>
-      <c r="I169" s="9"/>
+      <c r="B169" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="C169" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="D169" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E169" s="4">
+        <v>50</v>
+      </c>
+      <c r="F169" s="4">
+        <v>15</v>
+      </c>
+      <c r="G169" s="4">
+        <v>750</v>
+      </c>
+      <c r="H169" s="4">
+        <v>142</v>
+      </c>
+      <c r="I169" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J169" s="8"/>
-      <c r="K169" s="4"/>
-      <c r="L169" s="4"/>
-      <c r="M169" s="9"/>
+      <c r="K169" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L169" s="4">
+        <v>6360</v>
+      </c>
+      <c r="M169" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="170" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>168</v>
       </c>
-      <c r="B170" s="6"/>
-      <c r="C170" s="4"/>
-      <c r="D170" s="4"/>
-      <c r="E170" s="4"/>
-      <c r="F170" s="4"/>
-      <c r="G170" s="4"/>
-      <c r="H170" s="4"/>
-      <c r="I170" s="9"/>
+      <c r="B170" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="C170" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="D170" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E170" s="4">
+        <v>1</v>
+      </c>
+      <c r="F170" s="4">
+        <v>450</v>
+      </c>
+      <c r="G170" s="4">
+        <v>450</v>
+      </c>
+      <c r="H170" s="4">
+        <v>143</v>
+      </c>
+      <c r="I170" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J170" s="8"/>
-      <c r="K170" s="4"/>
-      <c r="L170" s="4"/>
-      <c r="M170" s="9"/>
+      <c r="K170" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="L170" s="4">
+        <v>6361</v>
+      </c>
+      <c r="M170" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="171" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="1"/>
-      <c r="B171" s="6"/>
-      <c r="C171" s="4"/>
-      <c r="D171" s="4"/>
-      <c r="E171" s="4"/>
-      <c r="F171" s="4"/>
-      <c r="G171" s="4"/>
-      <c r="H171" s="4"/>
-      <c r="I171" s="9"/>
+      <c r="A171" s="1">
+        <v>169</v>
+      </c>
+      <c r="B171" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C171" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="D171" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E171" s="4">
+        <v>15</v>
+      </c>
+      <c r="F171" s="4">
+        <v>351</v>
+      </c>
+      <c r="G171" s="4">
+        <v>5265</v>
+      </c>
+      <c r="H171" s="4">
+        <v>94</v>
+      </c>
+      <c r="I171" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J171" s="8"/>
-      <c r="K171" s="4"/>
-      <c r="L171" s="4"/>
-      <c r="M171" s="9"/>
+      <c r="K171" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L171" s="4">
+        <v>6362</v>
+      </c>
+      <c r="M171" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="172" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="1"/>
-      <c r="B172" s="6"/>
-      <c r="C172" s="4"/>
-      <c r="D172" s="4"/>
-      <c r="E172" s="4"/>
-      <c r="F172" s="4"/>
-      <c r="G172" s="4"/>
-      <c r="H172" s="4"/>
-      <c r="I172" s="9"/>
+      <c r="A172" s="1">
+        <v>170</v>
+      </c>
+      <c r="B172" s="12"/>
+      <c r="C172" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="D172" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E172" s="4">
+        <v>1</v>
+      </c>
+      <c r="F172" s="4">
+        <v>702</v>
+      </c>
+      <c r="G172" s="4">
+        <v>702</v>
+      </c>
+      <c r="H172" s="4">
+        <v>94</v>
+      </c>
+      <c r="I172" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J172" s="8"/>
-      <c r="K172" s="4"/>
-      <c r="L172" s="4"/>
-      <c r="M172" s="9"/>
+      <c r="K172" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L172" s="4">
+        <v>6362</v>
+      </c>
+      <c r="M172" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="173" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="1"/>
-      <c r="B173" s="6"/>
-      <c r="C173" s="4"/>
-      <c r="D173" s="4"/>
-      <c r="E173" s="4"/>
-      <c r="F173" s="4"/>
-      <c r="G173" s="4"/>
-      <c r="H173" s="4"/>
-      <c r="I173" s="9"/>
+      <c r="A173" s="1">
+        <v>171</v>
+      </c>
+      <c r="B173" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C173" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D173" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E173" s="4">
+        <v>24</v>
+      </c>
+      <c r="F173" s="4">
+        <v>117</v>
+      </c>
+      <c r="G173" s="4">
+        <v>2808</v>
+      </c>
+      <c r="H173" s="4">
+        <v>94</v>
+      </c>
+      <c r="I173" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J173" s="8"/>
-      <c r="K173" s="4"/>
-      <c r="L173" s="4"/>
-      <c r="M173" s="9"/>
+      <c r="K173" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L173" s="4">
+        <v>6362</v>
+      </c>
+      <c r="M173" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="174" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="1"/>
-      <c r="B174" s="6"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="4"/>
-      <c r="G174" s="4"/>
-      <c r="H174" s="4"/>
-      <c r="I174" s="9"/>
+      <c r="A174" s="1">
+        <v>172</v>
+      </c>
+      <c r="B174" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="C174" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D174" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E174" s="4">
+        <v>3</v>
+      </c>
+      <c r="F174" s="4">
+        <v>25740</v>
+      </c>
+      <c r="G174" s="4">
+        <v>17220</v>
+      </c>
+      <c r="H174" s="4">
+        <v>94</v>
+      </c>
+      <c r="I174" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J174" s="8"/>
-      <c r="K174" s="4"/>
-      <c r="L174" s="4"/>
-      <c r="M174" s="9"/>
+      <c r="K174" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L174" s="4">
+        <v>6362</v>
+      </c>
+      <c r="M174" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="175" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="1"/>
-      <c r="B175" s="6"/>
-      <c r="C175" s="4"/>
-      <c r="D175" s="4"/>
-      <c r="E175" s="4"/>
-      <c r="F175" s="4"/>
-      <c r="G175" s="4"/>
-      <c r="H175" s="4"/>
-      <c r="I175" s="9"/>
+      <c r="A175" s="1">
+        <v>173</v>
+      </c>
+      <c r="B175" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="D175" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E175" s="4">
+        <v>3</v>
+      </c>
+      <c r="F175" s="4">
+        <v>2457</v>
+      </c>
+      <c r="G175" s="4">
+        <v>7371</v>
+      </c>
+      <c r="H175" s="4">
+        <v>94</v>
+      </c>
+      <c r="I175" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J175" s="8"/>
-      <c r="K175" s="4"/>
-      <c r="L175" s="4"/>
-      <c r="M175" s="9"/>
+      <c r="K175" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="L175" s="4">
+        <v>6362</v>
+      </c>
+      <c r="M175" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="176" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="1"/>
-      <c r="B176" s="6"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="4"/>
-      <c r="F176" s="4"/>
-      <c r="G176" s="4"/>
-      <c r="H176" s="4"/>
-      <c r="I176" s="9"/>
+      <c r="A176" s="1">
+        <v>174</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E176" s="4">
+        <v>2</v>
+      </c>
+      <c r="F176" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G176" s="4">
+        <v>2000</v>
+      </c>
+      <c r="H176" s="4">
+        <v>14057</v>
+      </c>
+      <c r="I176" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J176" s="8"/>
-      <c r="K176" s="4"/>
-      <c r="L176" s="4"/>
-      <c r="M176" s="9"/>
+      <c r="K176" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L176" s="4">
+        <v>6363</v>
+      </c>
+      <c r="M176" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="177" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="1"/>
-      <c r="B177" s="6"/>
-      <c r="C177" s="4"/>
-      <c r="D177" s="4"/>
-      <c r="E177" s="4"/>
-      <c r="F177" s="4"/>
-      <c r="G177" s="4"/>
-      <c r="H177" s="4"/>
-      <c r="I177" s="9"/>
+      <c r="A177" s="1">
+        <v>175</v>
+      </c>
+      <c r="B177" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="C177" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D177" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E177" s="4">
+        <v>5</v>
+      </c>
+      <c r="F177" s="4">
+        <v>550</v>
+      </c>
+      <c r="G177" s="4">
+        <v>2750</v>
+      </c>
+      <c r="H177" s="4">
+        <v>14057</v>
+      </c>
+      <c r="I177" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J177" s="8"/>
-      <c r="K177" s="4"/>
-      <c r="L177" s="4"/>
-      <c r="M177" s="9"/>
+      <c r="K177" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L177" s="4">
+        <v>6363</v>
+      </c>
+      <c r="M177" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="178" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="1"/>
-      <c r="B178" s="6"/>
-      <c r="C178" s="4"/>
-      <c r="D178" s="4"/>
-      <c r="E178" s="4"/>
-      <c r="F178" s="4"/>
-      <c r="G178" s="4"/>
-      <c r="H178" s="4"/>
-      <c r="I178" s="9"/>
+      <c r="A178" s="1">
+        <v>176</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="C178" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="D178" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E178" s="4">
+        <v>50</v>
+      </c>
+      <c r="F178" s="4">
+        <v>20</v>
+      </c>
+      <c r="G178" s="4">
+        <v>1000</v>
+      </c>
+      <c r="H178" s="4">
+        <v>14057</v>
+      </c>
+      <c r="I178" s="9" t="s">
+        <v>298</v>
+      </c>
       <c r="J178" s="8"/>
-      <c r="K178" s="4"/>
-      <c r="L178" s="4"/>
-      <c r="M178" s="9"/>
+      <c r="K178" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="L178" s="4">
+        <v>6363</v>
+      </c>
+      <c r="M178" s="9" t="s">
+        <v>312</v>
+      </c>
     </row>
     <row r="179" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="1"/>
-      <c r="B179" s="6"/>
-      <c r="C179" s="4"/>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="4"/>
-      <c r="G179" s="4"/>
-      <c r="H179" s="4"/>
-      <c r="I179" s="9"/>
+      <c r="A179" s="1">
+        <v>177</v>
+      </c>
+      <c r="B179" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C179" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="D179" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E179" s="4">
+        <v>4</v>
+      </c>
+      <c r="F179" s="4">
+        <v>7649</v>
+      </c>
+      <c r="G179" s="4">
+        <v>30597</v>
+      </c>
+      <c r="H179" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I179" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J179" s="8"/>
-      <c r="K179" s="4"/>
-      <c r="L179" s="4"/>
-      <c r="M179" s="9"/>
+      <c r="K179" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L179" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M179" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="180" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="1"/>
-      <c r="B180" s="6"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-      <c r="E180" s="4"/>
-      <c r="F180" s="4"/>
-      <c r="G180" s="4"/>
-      <c r="H180" s="4"/>
-      <c r="I180" s="9"/>
+      <c r="A180" s="1">
+        <v>178</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E180" s="4">
+        <v>70</v>
+      </c>
+      <c r="F180" s="4">
+        <v>32</v>
+      </c>
+      <c r="G180" s="4">
+        <v>2240</v>
+      </c>
+      <c r="H180" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I180" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J180" s="8"/>
-      <c r="K180" s="4"/>
-      <c r="L180" s="4"/>
-      <c r="M180" s="9"/>
+      <c r="K180" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L180" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M180" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="181" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="1"/>
-      <c r="B181" s="6"/>
-      <c r="C181" s="4"/>
-      <c r="D181" s="4"/>
-      <c r="E181" s="4"/>
-      <c r="F181" s="4"/>
-      <c r="G181" s="4"/>
-      <c r="H181" s="4"/>
-      <c r="I181" s="9"/>
+      <c r="A181" s="1">
+        <v>179</v>
+      </c>
+      <c r="B181" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="C181" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="D181" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E181" s="4">
+        <v>10</v>
+      </c>
+      <c r="F181" s="4">
+        <v>313</v>
+      </c>
+      <c r="G181" s="4">
+        <v>3135</v>
+      </c>
+      <c r="H181" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I181" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J181" s="8"/>
-      <c r="K181" s="4"/>
-      <c r="L181" s="4"/>
-      <c r="M181" s="9"/>
+      <c r="K181" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L181" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M181" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="182" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="1"/>
-      <c r="B182" s="6"/>
-      <c r="C182" s="4"/>
-      <c r="D182" s="4"/>
-      <c r="E182" s="4"/>
-      <c r="F182" s="4"/>
-      <c r="G182" s="4"/>
-      <c r="H182" s="4"/>
-      <c r="I182" s="9"/>
+      <c r="A182" s="1">
+        <v>180</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="C182" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E182" s="4">
+        <v>10</v>
+      </c>
+      <c r="F182" s="4">
+        <v>313</v>
+      </c>
+      <c r="G182" s="4">
+        <v>3135</v>
+      </c>
+      <c r="H182" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I182" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J182" s="8"/>
-      <c r="K182" s="4"/>
-      <c r="L182" s="4"/>
-      <c r="M182" s="9"/>
+      <c r="K182" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L182" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M182" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="183" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="1"/>
-      <c r="B183" s="6"/>
-      <c r="C183" s="4"/>
-      <c r="D183" s="4"/>
-      <c r="E183" s="4"/>
-      <c r="F183" s="4"/>
-      <c r="G183" s="4"/>
-      <c r="H183" s="4"/>
-      <c r="I183" s="9"/>
+      <c r="A183" s="1">
+        <v>181</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C183" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183" s="4">
+        <v>15</v>
+      </c>
+      <c r="F183" s="4">
+        <v>1661</v>
+      </c>
+      <c r="G183" s="4">
+        <v>249222</v>
+      </c>
+      <c r="H183" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I183" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J183" s="8"/>
-      <c r="K183" s="4"/>
-      <c r="L183" s="4"/>
-      <c r="M183" s="9"/>
+      <c r="K183" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L183" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M183" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="184" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="1"/>
-      <c r="B184" s="6"/>
-      <c r="C184" s="4"/>
-      <c r="D184" s="4"/>
-      <c r="E184" s="4"/>
-      <c r="F184" s="4"/>
-      <c r="G184" s="4"/>
-      <c r="H184" s="4"/>
-      <c r="I184" s="9"/>
+      <c r="A184" s="1">
+        <v>182</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C184" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E184" s="4">
+        <v>13</v>
+      </c>
+      <c r="F184" s="4">
+        <v>2225</v>
+      </c>
+      <c r="G184" s="4">
+        <v>28936</v>
+      </c>
+      <c r="H184" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I184" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J184" s="8"/>
-      <c r="K184" s="4"/>
-      <c r="L184" s="4"/>
-      <c r="M184" s="9"/>
+      <c r="K184" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L184" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M184" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="1"/>
-      <c r="B185" s="6"/>
-      <c r="C185" s="4"/>
-      <c r="D185" s="4"/>
-      <c r="E185" s="4"/>
-      <c r="F185" s="4"/>
-      <c r="G185" s="4"/>
-      <c r="H185" s="4"/>
-      <c r="I185" s="9"/>
+      <c r="A185" s="1">
+        <v>183</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E185" s="4">
+        <v>18</v>
+      </c>
+      <c r="F185" s="4">
+        <v>5580</v>
+      </c>
+      <c r="G185" s="4">
+        <v>80045</v>
+      </c>
+      <c r="H185" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I185" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J185" s="8"/>
-      <c r="K185" s="4"/>
-      <c r="L185" s="4"/>
-      <c r="M185" s="9"/>
+      <c r="K185" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L185" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M185" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="1"/>
-      <c r="B186" s="6"/>
-      <c r="C186" s="4"/>
-      <c r="D186" s="4"/>
-      <c r="E186" s="4"/>
-      <c r="F186" s="4"/>
-      <c r="G186" s="4"/>
-      <c r="H186" s="4"/>
-      <c r="I186" s="9"/>
+      <c r="A186" s="1">
+        <v>184</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C186" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186" s="4">
+        <v>21</v>
+      </c>
+      <c r="F186" s="4">
+        <v>288</v>
+      </c>
+      <c r="G186" s="4">
+        <v>6056</v>
+      </c>
+      <c r="H186" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I186" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J186" s="8"/>
-      <c r="K186" s="4"/>
-      <c r="L186" s="4"/>
-      <c r="M186" s="9"/>
+      <c r="K186" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L186" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M186" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="1"/>
-      <c r="B187" s="6"/>
-      <c r="C187" s="4"/>
-      <c r="D187" s="4"/>
-      <c r="E187" s="4"/>
-      <c r="F187" s="4"/>
-      <c r="G187" s="4"/>
-      <c r="H187" s="4"/>
-      <c r="I187" s="9"/>
+      <c r="A187" s="1">
+        <v>185</v>
+      </c>
+      <c r="B187" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="C187" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E187" s="4">
+        <v>1</v>
+      </c>
+      <c r="F187" s="4">
+        <v>1943</v>
+      </c>
+      <c r="G187" s="4">
+        <v>1943</v>
+      </c>
+      <c r="H187" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I187" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J187" s="8"/>
-      <c r="K187" s="4"/>
-      <c r="L187" s="4"/>
-      <c r="M187" s="9"/>
+      <c r="K187" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L187" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M187" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="1"/>
-      <c r="B188" s="6"/>
-      <c r="C188" s="4"/>
-      <c r="D188" s="4"/>
-      <c r="E188" s="4"/>
-      <c r="F188" s="4"/>
-      <c r="G188" s="4"/>
-      <c r="H188" s="4"/>
-      <c r="I188" s="9"/>
+      <c r="A188" s="1">
+        <v>186</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C188" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E188" s="4">
+        <v>18</v>
+      </c>
+      <c r="F188" s="4">
+        <v>1611</v>
+      </c>
+      <c r="G188" s="4">
+        <v>29005</v>
+      </c>
+      <c r="H188" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I188" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J188" s="8"/>
-      <c r="K188" s="4"/>
-      <c r="L188" s="4"/>
-      <c r="M188" s="9"/>
+      <c r="K188" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L188" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M188" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="1"/>
-      <c r="B189" s="6"/>
-      <c r="C189" s="4"/>
-      <c r="D189" s="4"/>
-      <c r="E189" s="4"/>
-      <c r="F189" s="4"/>
-      <c r="G189" s="4"/>
-      <c r="H189" s="4"/>
-      <c r="I189" s="9"/>
+      <c r="A189" s="1">
+        <v>187</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C189" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E189" s="4">
+        <v>6</v>
+      </c>
+      <c r="F189" s="4">
+        <v>2100</v>
+      </c>
+      <c r="G189" s="4">
+        <v>12602</v>
+      </c>
+      <c r="H189" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I189" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J189" s="8"/>
-      <c r="K189" s="4"/>
-      <c r="L189" s="4"/>
-      <c r="M189" s="9"/>
+      <c r="K189" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L189" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M189" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="1"/>
-      <c r="B190" s="6"/>
-      <c r="C190" s="4"/>
-      <c r="D190" s="4"/>
-      <c r="E190" s="4"/>
-      <c r="F190" s="4"/>
-      <c r="G190" s="4"/>
-      <c r="H190" s="4"/>
-      <c r="I190" s="9"/>
+      <c r="A190" s="1">
+        <v>188</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C190" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E190" s="4">
+        <v>24</v>
+      </c>
+      <c r="F190" s="4">
+        <v>601</v>
+      </c>
+      <c r="G190" s="4">
+        <v>14446</v>
+      </c>
+      <c r="H190" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I190" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J190" s="8"/>
-      <c r="K190" s="4"/>
-      <c r="L190" s="4"/>
-      <c r="M190" s="9"/>
+      <c r="K190" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L190" s="4">
+        <v>6364</v>
+      </c>
+      <c r="M190" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="1"/>
-      <c r="B191" s="6"/>
-      <c r="C191" s="4"/>
-      <c r="D191" s="4"/>
-      <c r="E191" s="4"/>
-      <c r="F191" s="4"/>
-      <c r="G191" s="4"/>
-      <c r="H191" s="4"/>
-      <c r="I191" s="9"/>
+      <c r="A191" s="1">
+        <v>189</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C191" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D191" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E191" s="4">
+        <v>16</v>
+      </c>
+      <c r="F191" s="4">
+        <v>6395</v>
+      </c>
+      <c r="G191" s="4">
+        <v>102326</v>
+      </c>
+      <c r="H191" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I191" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J191" s="8"/>
-      <c r="K191" s="4"/>
-      <c r="L191" s="4"/>
-      <c r="M191" s="9"/>
+      <c r="K191" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L191" s="4">
+        <v>6365</v>
+      </c>
+      <c r="M191" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="1"/>
-      <c r="B192" s="6"/>
-      <c r="C192" s="4"/>
-      <c r="D192" s="4"/>
-      <c r="E192" s="4"/>
-      <c r="F192" s="4"/>
-      <c r="G192" s="4"/>
-      <c r="H192" s="4"/>
-      <c r="I192" s="9"/>
+      <c r="A192" s="1">
+        <v>190</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="C192" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="D192" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E192" s="4">
+        <v>2</v>
+      </c>
+      <c r="F192" s="4">
+        <v>6395</v>
+      </c>
+      <c r="G192" s="4">
+        <v>12790</v>
+      </c>
+      <c r="H192" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I192" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J192" s="8"/>
-      <c r="K192" s="4"/>
-      <c r="L192" s="4"/>
-      <c r="M192" s="9"/>
+      <c r="K192" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L192" s="4">
+        <v>6365</v>
+      </c>
+      <c r="M192" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="1"/>
-      <c r="B193" s="6"/>
-      <c r="C193" s="4"/>
-      <c r="D193" s="4"/>
-      <c r="E193" s="4"/>
-      <c r="F193" s="4"/>
-      <c r="G193" s="4"/>
-      <c r="H193" s="4"/>
-      <c r="I193" s="9"/>
+      <c r="A193" s="1">
+        <v>191</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="D193" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E193" s="4">
+        <v>2</v>
+      </c>
+      <c r="F193" s="4">
+        <v>8030</v>
+      </c>
+      <c r="G193" s="4">
+        <v>16060</v>
+      </c>
+      <c r="H193" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I193" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J193" s="8"/>
-      <c r="K193" s="4"/>
-      <c r="L193" s="4"/>
-      <c r="M193" s="9"/>
+      <c r="K193" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L193" s="4">
+        <v>6365</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="194" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="1"/>
-      <c r="B194" s="6"/>
-      <c r="C194" s="4"/>
-      <c r="D194" s="4"/>
-      <c r="E194" s="4"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="4"/>
-      <c r="H194" s="4"/>
-      <c r="I194" s="9"/>
+      <c r="A194" s="1">
+        <v>192</v>
+      </c>
+      <c r="B194" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C194" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D194" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E194" s="4">
+        <v>21</v>
+      </c>
+      <c r="F194" s="4">
+        <v>2445</v>
+      </c>
+      <c r="G194" s="4">
+        <v>51351</v>
+      </c>
+      <c r="H194" s="4">
+        <v>2464</v>
+      </c>
+      <c r="I194" s="9" t="s">
+        <v>335</v>
+      </c>
       <c r="J194" s="8"/>
-      <c r="K194" s="4"/>
-      <c r="L194" s="4"/>
-      <c r="M194" s="9"/>
-    </row>
-    <row r="195" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="1"/>
-      <c r="B195" s="6"/>
-      <c r="C195" s="4"/>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="4"/>
-      <c r="G195" s="4"/>
-      <c r="H195" s="4"/>
-      <c r="I195" s="9"/>
-      <c r="J195" s="8"/>
-      <c r="K195" s="4"/>
-      <c r="L195" s="4"/>
-      <c r="M195" s="9"/>
-    </row>
-    <row r="196" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="1"/>
-      <c r="B196" s="6"/>
-      <c r="C196" s="4"/>
-      <c r="D196" s="4"/>
-      <c r="E196" s="4"/>
-      <c r="F196" s="4"/>
-      <c r="G196" s="4"/>
-      <c r="H196" s="4"/>
-      <c r="I196" s="9"/>
-      <c r="J196" s="8"/>
-      <c r="K196" s="4"/>
-      <c r="L196" s="4"/>
-      <c r="M196" s="9"/>
-    </row>
-    <row r="197" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="1"/>
-      <c r="B197" s="6"/>
-      <c r="C197" s="4"/>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="4"/>
-      <c r="G197" s="4"/>
-      <c r="H197" s="4"/>
-      <c r="I197" s="9"/>
-      <c r="J197" s="8"/>
-      <c r="K197" s="4"/>
-      <c r="L197" s="4"/>
-      <c r="M197" s="9"/>
-    </row>
-    <row r="198" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="1"/>
-      <c r="B198" s="6"/>
-      <c r="C198" s="4"/>
-      <c r="D198" s="4"/>
-      <c r="E198" s="4"/>
-      <c r="F198" s="4"/>
-      <c r="G198" s="4"/>
-      <c r="H198" s="4"/>
-      <c r="I198" s="9"/>
-      <c r="J198" s="8"/>
-      <c r="K198" s="4"/>
-      <c r="L198" s="4"/>
-      <c r="M198" s="9"/>
-    </row>
-    <row r="199" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="1"/>
-      <c r="B199" s="6"/>
-      <c r="C199" s="4"/>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="4"/>
-      <c r="G199" s="4"/>
-      <c r="H199" s="4"/>
-      <c r="I199" s="9"/>
-      <c r="J199" s="8"/>
-      <c r="K199" s="4"/>
-      <c r="L199" s="4"/>
-      <c r="M199" s="9"/>
-    </row>
-    <row r="200" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="1"/>
-      <c r="B200" s="6"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="4"/>
-      <c r="G200" s="4"/>
-      <c r="H200" s="4"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="8"/>
-      <c r="K200" s="4"/>
-      <c r="L200" s="4"/>
-      <c r="M200" s="9"/>
-    </row>
-    <row r="201" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="1"/>
-      <c r="B201" s="6"/>
-      <c r="C201" s="4"/>
-      <c r="D201" s="4"/>
-      <c r="E201" s="4"/>
-      <c r="F201" s="4"/>
-      <c r="G201" s="4"/>
-      <c r="H201" s="4"/>
-      <c r="I201" s="9"/>
-      <c r="J201" s="8"/>
-      <c r="K201" s="4"/>
-      <c r="L201" s="4"/>
-      <c r="M201" s="9"/>
-    </row>
-    <row r="202" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="1"/>
-      <c r="B202" s="6"/>
-      <c r="C202" s="4"/>
-      <c r="D202" s="4"/>
-      <c r="E202" s="4"/>
-      <c r="F202" s="4"/>
-      <c r="G202" s="4"/>
-      <c r="H202" s="4"/>
-      <c r="I202" s="9"/>
-      <c r="J202" s="8"/>
-      <c r="K202" s="4"/>
-      <c r="L202" s="4"/>
-      <c r="M202" s="9"/>
-    </row>
-    <row r="203" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="1"/>
-      <c r="B203" s="6"/>
-      <c r="C203" s="4"/>
-      <c r="D203" s="4"/>
-      <c r="E203" s="4"/>
-      <c r="F203" s="4"/>
-      <c r="G203" s="4"/>
-      <c r="H203" s="4"/>
-      <c r="I203" s="9"/>
-      <c r="J203" s="8"/>
-      <c r="K203" s="4"/>
-      <c r="L203" s="4"/>
-      <c r="M203" s="9"/>
-    </row>
-    <row r="204" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="1"/>
-      <c r="B204" s="6"/>
-      <c r="C204" s="4"/>
-      <c r="D204" s="4"/>
-      <c r="E204" s="4"/>
-      <c r="F204" s="4"/>
-      <c r="G204" s="4"/>
-      <c r="H204" s="4"/>
-      <c r="I204" s="9"/>
-      <c r="J204" s="8"/>
-      <c r="K204" s="4"/>
-      <c r="L204" s="4"/>
-      <c r="M204" s="9"/>
-    </row>
-    <row r="205" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="1"/>
-      <c r="B205" s="6"/>
-      <c r="C205" s="4"/>
-      <c r="D205" s="4"/>
-      <c r="E205" s="4"/>
-      <c r="F205" s="4"/>
-      <c r="G205" s="4"/>
-      <c r="H205" s="4"/>
-      <c r="I205" s="9"/>
-      <c r="J205" s="8"/>
-      <c r="K205" s="4"/>
-      <c r="L205" s="4"/>
-      <c r="M205" s="9"/>
-    </row>
-    <row r="206" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="1"/>
-      <c r="B206" s="6"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="4"/>
-      <c r="E206" s="4"/>
-      <c r="F206" s="4"/>
-      <c r="G206" s="4"/>
-      <c r="H206" s="4"/>
-      <c r="I206" s="9"/>
-      <c r="J206" s="8"/>
-      <c r="K206" s="4"/>
-      <c r="L206" s="4"/>
-      <c r="M206" s="9"/>
-    </row>
-    <row r="207" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A207" s="1"/>
-      <c r="B207" s="6"/>
-      <c r="C207" s="4"/>
-      <c r="D207" s="4"/>
-      <c r="E207" s="4"/>
-      <c r="F207" s="4"/>
-      <c r="G207" s="4"/>
-      <c r="H207" s="4"/>
-      <c r="I207" s="9"/>
-      <c r="J207" s="8"/>
-      <c r="K207" s="4"/>
-      <c r="L207" s="4"/>
-      <c r="M207" s="9"/>
-    </row>
-    <row r="208" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A208" s="1"/>
-      <c r="B208" s="6"/>
-      <c r="C208" s="4"/>
-      <c r="D208" s="4"/>
-      <c r="E208" s="4"/>
-      <c r="F208" s="4"/>
-      <c r="G208" s="4"/>
-      <c r="H208" s="4"/>
-      <c r="I208" s="9"/>
-      <c r="J208" s="8"/>
-      <c r="K208" s="4"/>
-      <c r="L208" s="4"/>
-      <c r="M208" s="9"/>
-    </row>
-    <row r="209" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A209" s="1"/>
-      <c r="B209" s="6"/>
-      <c r="C209" s="4"/>
-      <c r="D209" s="4"/>
-      <c r="E209" s="4"/>
-      <c r="F209" s="4"/>
-      <c r="G209" s="4"/>
-      <c r="H209" s="4"/>
-      <c r="I209" s="9"/>
-      <c r="J209" s="8"/>
-      <c r="K209" s="4"/>
-      <c r="L209" s="4"/>
-      <c r="M209" s="9"/>
-    </row>
-    <row r="210" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A210" s="1"/>
-      <c r="B210" s="6"/>
-      <c r="C210" s="4"/>
-      <c r="D210" s="4"/>
-      <c r="E210" s="4"/>
-      <c r="F210" s="4"/>
-      <c r="G210" s="4"/>
-      <c r="H210" s="4"/>
-      <c r="I210" s="9"/>
-      <c r="J210" s="8"/>
-      <c r="K210" s="4"/>
-      <c r="L210" s="4"/>
-      <c r="M210" s="9"/>
-    </row>
-    <row r="211" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A211" s="1"/>
-      <c r="B211" s="6"/>
-      <c r="C211" s="4"/>
-      <c r="D211" s="4"/>
-      <c r="E211" s="4"/>
-      <c r="F211" s="4"/>
-      <c r="G211" s="4"/>
-      <c r="H211" s="4"/>
-      <c r="I211" s="9"/>
-      <c r="J211" s="8"/>
-      <c r="K211" s="4"/>
-      <c r="L211" s="4"/>
-      <c r="M211" s="9"/>
-    </row>
-    <row r="212" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A212" s="1"/>
-      <c r="B212" s="6"/>
-      <c r="C212" s="4"/>
-      <c r="D212" s="4"/>
-      <c r="E212" s="4"/>
-      <c r="F212" s="4"/>
-      <c r="G212" s="4"/>
-      <c r="H212" s="4"/>
-      <c r="I212" s="9"/>
-      <c r="J212" s="8"/>
-      <c r="K212" s="4"/>
-      <c r="L212" s="4"/>
-      <c r="M212" s="9"/>
-    </row>
-    <row r="213" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="1"/>
-      <c r="B213" s="6"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="4"/>
-      <c r="G213" s="4"/>
-      <c r="H213" s="4"/>
-      <c r="I213" s="9"/>
-      <c r="J213" s="8"/>
-      <c r="K213" s="4"/>
-      <c r="L213" s="4"/>
-      <c r="M213" s="9"/>
-    </row>
-    <row r="214" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="1"/>
-      <c r="B214" s="6"/>
-      <c r="C214" s="4"/>
-      <c r="D214" s="4"/>
-      <c r="E214" s="4"/>
-      <c r="F214" s="4"/>
-      <c r="G214" s="4"/>
-      <c r="H214" s="4"/>
-      <c r="I214" s="9"/>
-      <c r="J214" s="8"/>
-      <c r="K214" s="4"/>
-      <c r="L214" s="4"/>
-      <c r="M214" s="9"/>
-    </row>
-    <row r="215" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="1"/>
-      <c r="B215" s="6"/>
-      <c r="C215" s="4"/>
-      <c r="D215" s="4"/>
-      <c r="E215" s="4"/>
-      <c r="F215" s="4"/>
-      <c r="G215" s="4"/>
-      <c r="H215" s="4"/>
-      <c r="I215" s="9"/>
-      <c r="J215" s="8"/>
-      <c r="K215" s="4"/>
-      <c r="L215" s="4"/>
-      <c r="M215" s="9"/>
-    </row>
-    <row r="216" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A216" s="1"/>
-      <c r="B216" s="6"/>
-      <c r="C216" s="4"/>
-      <c r="D216" s="4"/>
-      <c r="E216" s="4"/>
-      <c r="F216" s="4"/>
-      <c r="G216" s="4"/>
-      <c r="H216" s="4"/>
-      <c r="I216" s="9"/>
-      <c r="J216" s="8"/>
-      <c r="K216" s="4"/>
-      <c r="L216" s="4"/>
-      <c r="M216" s="9"/>
-    </row>
-    <row r="217" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A217" s="1"/>
-      <c r="B217" s="6"/>
-      <c r="C217" s="4"/>
-      <c r="D217" s="4"/>
-      <c r="E217" s="4"/>
-      <c r="F217" s="4"/>
-      <c r="G217" s="4"/>
-      <c r="H217" s="4"/>
-      <c r="I217" s="9"/>
-      <c r="J217" s="8"/>
-      <c r="K217" s="4"/>
-      <c r="L217" s="4"/>
-      <c r="M217" s="9"/>
-    </row>
-    <row r="218" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A218" s="1"/>
-      <c r="B218" s="6"/>
-      <c r="C218" s="4"/>
-      <c r="D218" s="4"/>
-      <c r="E218" s="4"/>
-      <c r="F218" s="4"/>
-      <c r="G218" s="4"/>
-      <c r="H218" s="4"/>
-      <c r="I218" s="9"/>
-      <c r="J218" s="8"/>
-      <c r="K218" s="4"/>
-      <c r="L218" s="4"/>
-      <c r="M218" s="9"/>
-    </row>
-    <row r="219" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A219" s="1"/>
-      <c r="B219" s="6"/>
-      <c r="C219" s="4"/>
-      <c r="D219" s="4"/>
-      <c r="E219" s="4"/>
-      <c r="F219" s="4"/>
-      <c r="G219" s="4"/>
-      <c r="H219" s="4"/>
-      <c r="I219" s="9"/>
-      <c r="J219" s="8"/>
-      <c r="K219" s="4"/>
-      <c r="L219" s="4"/>
-      <c r="M219" s="9"/>
-    </row>
-    <row r="220" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A220" s="1"/>
-      <c r="B220" s="6"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="4"/>
-      <c r="E220" s="4"/>
-      <c r="F220" s="4"/>
-      <c r="G220" s="4"/>
-      <c r="H220" s="4"/>
-      <c r="I220" s="9"/>
-      <c r="J220" s="8"/>
-      <c r="K220" s="4"/>
-      <c r="L220" s="4"/>
-      <c r="M220" s="9"/>
-    </row>
-    <row r="221" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A221" s="1"/>
-      <c r="B221" s="6"/>
-      <c r="C221" s="4"/>
-      <c r="D221" s="4"/>
-      <c r="E221" s="4"/>
-      <c r="F221" s="4"/>
-      <c r="G221" s="4"/>
-      <c r="H221" s="4"/>
-      <c r="I221" s="9"/>
-      <c r="J221" s="8"/>
-      <c r="K221" s="4"/>
-      <c r="L221" s="4"/>
-      <c r="M221" s="9"/>
-    </row>
-    <row r="222" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A222" s="1"/>
-      <c r="B222" s="6"/>
-      <c r="C222" s="4"/>
-      <c r="D222" s="4"/>
-      <c r="E222" s="4"/>
-      <c r="F222" s="4"/>
-      <c r="G222" s="4"/>
-      <c r="H222" s="4"/>
-      <c r="I222" s="9"/>
-      <c r="J222" s="8"/>
-      <c r="K222" s="4"/>
-      <c r="L222" s="4"/>
-      <c r="M222" s="9"/>
-    </row>
-    <row r="223" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A223" s="1"/>
-      <c r="B223" s="6"/>
-      <c r="C223" s="4"/>
-      <c r="D223" s="4"/>
-      <c r="E223" s="4"/>
-      <c r="F223" s="4"/>
-      <c r="G223" s="4"/>
-      <c r="H223" s="4"/>
-      <c r="I223" s="9"/>
-      <c r="J223" s="8"/>
-      <c r="K223" s="4"/>
-      <c r="L223" s="4"/>
-      <c r="M223" s="9"/>
-    </row>
-    <row r="224" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A224" s="1"/>
-      <c r="B224" s="6"/>
-      <c r="C224" s="4"/>
-      <c r="D224" s="4"/>
-      <c r="E224" s="4"/>
-      <c r="F224" s="4"/>
-      <c r="G224" s="4"/>
-      <c r="H224" s="4"/>
-      <c r="I224" s="9"/>
-      <c r="J224" s="8"/>
-      <c r="K224" s="4"/>
-      <c r="L224" s="4"/>
-      <c r="M224" s="9"/>
-    </row>
-    <row r="225" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="1"/>
-      <c r="B225" s="6"/>
-      <c r="C225" s="4"/>
-      <c r="D225" s="4"/>
-      <c r="E225" s="4"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="4"/>
-      <c r="H225" s="4"/>
-      <c r="I225" s="9"/>
-      <c r="J225" s="8"/>
-      <c r="K225" s="4"/>
-      <c r="L225" s="4"/>
-      <c r="M225" s="9"/>
-    </row>
-    <row r="226" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A226" s="1"/>
-      <c r="B226" s="6"/>
-      <c r="C226" s="4"/>
-      <c r="D226" s="4"/>
-      <c r="E226" s="4"/>
-      <c r="F226" s="4"/>
-      <c r="G226" s="4"/>
-      <c r="H226" s="4"/>
-      <c r="I226" s="9"/>
-      <c r="J226" s="8"/>
-      <c r="K226" s="4"/>
-      <c r="L226" s="4"/>
-      <c r="M226" s="9"/>
-    </row>
-    <row r="227" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A227" s="1"/>
-      <c r="B227" s="6"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="4"/>
-      <c r="G227" s="4"/>
-      <c r="H227" s="4"/>
-      <c r="I227" s="9"/>
-      <c r="J227" s="8"/>
-      <c r="K227" s="4"/>
-      <c r="L227" s="4"/>
-      <c r="M227" s="9"/>
-    </row>
-    <row r="228" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A228" s="1"/>
-      <c r="B228" s="6"/>
-      <c r="C228" s="4"/>
-      <c r="D228" s="4"/>
-      <c r="E228" s="4"/>
-      <c r="F228" s="4"/>
-      <c r="G228" s="4"/>
-      <c r="H228" s="4"/>
-      <c r="I228" s="9"/>
-      <c r="J228" s="8"/>
-      <c r="K228" s="4"/>
-      <c r="L228" s="4"/>
-      <c r="M228" s="9"/>
-    </row>
-    <row r="229" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A229" s="1"/>
-      <c r="B229" s="6"/>
-      <c r="C229" s="4"/>
-      <c r="D229" s="4"/>
-      <c r="E229" s="4"/>
-      <c r="F229" s="4"/>
-      <c r="G229" s="4"/>
-      <c r="H229" s="4"/>
-      <c r="I229" s="9"/>
-      <c r="J229" s="8"/>
-      <c r="K229" s="4"/>
-      <c r="L229" s="4"/>
-      <c r="M229" s="9"/>
-    </row>
-    <row r="230" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A230" s="1"/>
-      <c r="B230" s="6"/>
-      <c r="C230" s="4"/>
-      <c r="D230" s="4"/>
-      <c r="E230" s="4"/>
-      <c r="F230" s="4"/>
-      <c r="G230" s="4"/>
-      <c r="H230" s="4"/>
-      <c r="I230" s="9"/>
-      <c r="J230" s="8"/>
-      <c r="K230" s="4"/>
-      <c r="L230" s="4"/>
-      <c r="M230" s="9"/>
-    </row>
-    <row r="231" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A231" s="1"/>
-      <c r="B231" s="6"/>
-      <c r="C231" s="4"/>
-      <c r="D231" s="4"/>
-      <c r="E231" s="4"/>
-      <c r="F231" s="4"/>
-      <c r="G231" s="4"/>
-      <c r="H231" s="4"/>
-      <c r="I231" s="9"/>
-      <c r="J231" s="8"/>
-      <c r="K231" s="4"/>
-      <c r="L231" s="4"/>
-      <c r="M231" s="9"/>
-    </row>
-    <row r="232" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A232" s="1"/>
-      <c r="B232" s="6"/>
-      <c r="C232" s="4"/>
-      <c r="D232" s="4"/>
-      <c r="E232" s="4"/>
-      <c r="F232" s="4"/>
-      <c r="G232" s="4"/>
-      <c r="H232" s="4"/>
-      <c r="I232" s="9"/>
-      <c r="J232" s="8"/>
-      <c r="K232" s="4"/>
-      <c r="L232" s="4"/>
-      <c r="M232" s="9"/>
-    </row>
-    <row r="233" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A233" s="1"/>
-      <c r="B233" s="6"/>
-      <c r="C233" s="4"/>
-      <c r="D233" s="4"/>
-      <c r="E233" s="4"/>
-      <c r="F233" s="4"/>
-      <c r="G233" s="4"/>
-      <c r="H233" s="4"/>
-      <c r="I233" s="9"/>
-      <c r="J233" s="8"/>
-      <c r="K233" s="4"/>
-      <c r="L233" s="4"/>
-      <c r="M233" s="9"/>
-    </row>
-    <row r="234" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A234" s="1"/>
-      <c r="B234" s="6"/>
-      <c r="C234" s="4"/>
-      <c r="D234" s="4"/>
-      <c r="E234" s="4"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="4"/>
-      <c r="H234" s="4"/>
-      <c r="I234" s="9"/>
-      <c r="J234" s="8"/>
-      <c r="K234" s="4"/>
-      <c r="L234" s="4"/>
-      <c r="M234" s="9"/>
-    </row>
-    <row r="235" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A235" s="1"/>
-      <c r="B235" s="6"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="4"/>
-      <c r="G235" s="4"/>
-      <c r="H235" s="4"/>
-      <c r="I235" s="9"/>
-      <c r="J235" s="8"/>
-      <c r="K235" s="4"/>
-      <c r="L235" s="4"/>
-      <c r="M235" s="9"/>
-    </row>
-    <row r="236" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A236" s="1"/>
-      <c r="B236" s="6"/>
-      <c r="C236" s="4"/>
-      <c r="D236" s="4"/>
-      <c r="E236" s="4"/>
-      <c r="F236" s="4"/>
-      <c r="G236" s="4"/>
-      <c r="H236" s="4"/>
-      <c r="I236" s="9"/>
-      <c r="J236" s="8"/>
-      <c r="K236" s="4"/>
-      <c r="L236" s="4"/>
-      <c r="M236" s="9"/>
-    </row>
-    <row r="237" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A237" s="1"/>
-      <c r="B237" s="6"/>
-      <c r="C237" s="4"/>
-      <c r="D237" s="4"/>
-      <c r="E237" s="4"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="4"/>
-      <c r="H237" s="4"/>
-      <c r="I237" s="9"/>
-      <c r="J237" s="8"/>
-      <c r="K237" s="4"/>
-      <c r="L237" s="4"/>
-      <c r="M237" s="9"/>
-    </row>
-    <row r="238" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A238" s="1"/>
-      <c r="B238" s="6"/>
-      <c r="C238" s="4"/>
-      <c r="D238" s="4"/>
-      <c r="E238" s="4"/>
-      <c r="F238" s="4"/>
-      <c r="G238" s="4"/>
-      <c r="H238" s="4"/>
-      <c r="I238" s="9"/>
-      <c r="J238" s="8"/>
-      <c r="K238" s="4"/>
-      <c r="L238" s="4"/>
-      <c r="M238" s="9"/>
-    </row>
-    <row r="239" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A239" s="1"/>
-      <c r="B239" s="6"/>
-      <c r="C239" s="4"/>
-      <c r="D239" s="4"/>
-      <c r="E239" s="4"/>
-      <c r="F239" s="4"/>
-      <c r="G239" s="4"/>
-      <c r="H239" s="4"/>
-      <c r="I239" s="9"/>
-      <c r="J239" s="8"/>
-      <c r="K239" s="4"/>
-      <c r="L239" s="4"/>
-      <c r="M239" s="9"/>
-    </row>
-    <row r="240" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A240" s="1"/>
-      <c r="B240" s="6"/>
-      <c r="C240" s="4"/>
-      <c r="D240" s="4"/>
-      <c r="E240" s="4"/>
-      <c r="F240" s="4"/>
-      <c r="G240" s="4"/>
-      <c r="H240" s="4"/>
-      <c r="I240" s="9"/>
-      <c r="J240" s="8"/>
-      <c r="K240" s="4"/>
-      <c r="L240" s="4"/>
-      <c r="M240" s="9"/>
-    </row>
-    <row r="241" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A241" s="1"/>
-      <c r="B241" s="6"/>
-      <c r="C241" s="4"/>
-      <c r="D241" s="4"/>
-      <c r="E241" s="4"/>
-      <c r="F241" s="4"/>
-      <c r="G241" s="4"/>
-      <c r="H241" s="4"/>
-      <c r="I241" s="9"/>
-      <c r="J241" s="8"/>
-      <c r="K241" s="4"/>
-      <c r="L241" s="4"/>
-      <c r="M241" s="9"/>
-    </row>
-    <row r="242" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A242" s="1"/>
-      <c r="B242" s="6"/>
-      <c r="C242" s="4"/>
-      <c r="D242" s="4"/>
-      <c r="E242" s="4"/>
-      <c r="F242" s="4"/>
-      <c r="G242" s="4"/>
-      <c r="H242" s="4"/>
-      <c r="I242" s="9"/>
-      <c r="J242" s="8"/>
-      <c r="K242" s="4"/>
-      <c r="L242" s="4"/>
-      <c r="M242" s="9"/>
-    </row>
-    <row r="243" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A243" s="1"/>
-      <c r="B243" s="6"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-      <c r="E243" s="4"/>
-      <c r="F243" s="4"/>
-      <c r="G243" s="4"/>
-      <c r="H243" s="4"/>
-      <c r="I243" s="9"/>
-      <c r="J243" s="8"/>
-      <c r="K243" s="4"/>
-      <c r="L243" s="4"/>
-      <c r="M243" s="9"/>
-    </row>
-    <row r="244" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A244" s="1"/>
-      <c r="B244" s="6"/>
-      <c r="C244" s="4"/>
-      <c r="D244" s="4"/>
-      <c r="E244" s="4"/>
-      <c r="F244" s="4"/>
-      <c r="G244" s="4"/>
-      <c r="H244" s="4"/>
-      <c r="I244" s="9"/>
-      <c r="J244" s="8"/>
-      <c r="K244" s="4"/>
-      <c r="L244" s="4"/>
-      <c r="M244" s="9"/>
-    </row>
-    <row r="245" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A245" s="1"/>
-      <c r="B245" s="6"/>
-      <c r="C245" s="4"/>
-      <c r="D245" s="4"/>
-      <c r="E245" s="4"/>
-      <c r="F245" s="4"/>
-      <c r="G245" s="4"/>
-      <c r="H245" s="4"/>
-      <c r="I245" s="9"/>
-      <c r="J245" s="8"/>
-      <c r="K245" s="4"/>
-      <c r="L245" s="4"/>
-      <c r="M245" s="9"/>
-    </row>
-    <row r="246" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A246" s="1"/>
-      <c r="B246" s="6"/>
-      <c r="C246" s="4"/>
-      <c r="D246" s="4"/>
-      <c r="E246" s="4"/>
-      <c r="F246" s="4"/>
-      <c r="G246" s="4"/>
-      <c r="H246" s="4"/>
-      <c r="I246" s="9"/>
-      <c r="J246" s="8"/>
-      <c r="K246" s="4"/>
-      <c r="L246" s="4"/>
-      <c r="M246" s="9"/>
-    </row>
-    <row r="247" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A247" s="1"/>
-      <c r="B247" s="6"/>
-      <c r="C247" s="4"/>
-      <c r="D247" s="4"/>
-      <c r="E247" s="4"/>
-      <c r="F247" s="4"/>
-      <c r="G247" s="4"/>
-      <c r="H247" s="4"/>
-      <c r="I247" s="9"/>
-      <c r="J247" s="8"/>
-      <c r="K247" s="4"/>
-      <c r="L247" s="4"/>
-      <c r="M247" s="9"/>
-    </row>
-    <row r="248" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A248" s="1"/>
-      <c r="B248" s="6"/>
-      <c r="C248" s="4"/>
-      <c r="D248" s="4"/>
-      <c r="E248" s="4"/>
-      <c r="F248" s="4"/>
-      <c r="G248" s="4"/>
-      <c r="H248" s="4"/>
-      <c r="I248" s="9"/>
-      <c r="J248" s="8"/>
-      <c r="K248" s="4"/>
-      <c r="L248" s="4"/>
-      <c r="M248" s="9"/>
-    </row>
-    <row r="249" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="1"/>
-      <c r="B249" s="6"/>
-      <c r="C249" s="4"/>
-      <c r="D249" s="4"/>
-      <c r="E249" s="4"/>
-      <c r="F249" s="4"/>
-      <c r="G249" s="4"/>
-      <c r="H249" s="4"/>
-      <c r="I249" s="9"/>
-      <c r="J249" s="8"/>
-      <c r="K249" s="4"/>
-      <c r="L249" s="4"/>
-      <c r="M249" s="9"/>
-    </row>
-    <row r="250" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A250" s="1"/>
-      <c r="B250" s="6"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="4"/>
-      <c r="G250" s="4"/>
-      <c r="H250" s="4"/>
-      <c r="I250" s="9"/>
-      <c r="J250" s="8"/>
-      <c r="K250" s="4"/>
-      <c r="L250" s="4"/>
-      <c r="M250" s="9"/>
-    </row>
-    <row r="251" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A251" s="1"/>
-      <c r="B251" s="6"/>
-      <c r="C251" s="4"/>
-      <c r="D251" s="4"/>
-      <c r="E251" s="4"/>
-      <c r="F251" s="4"/>
-      <c r="G251" s="4"/>
-      <c r="H251" s="4"/>
-      <c r="I251" s="9"/>
-      <c r="J251" s="8"/>
-      <c r="K251" s="4"/>
-      <c r="L251" s="4"/>
-      <c r="M251" s="9"/>
-    </row>
-    <row r="252" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A252" s="1">
-        <v>169</v>
-      </c>
-      <c r="B252" s="6"/>
-      <c r="C252" s="4"/>
-      <c r="D252" s="4"/>
-      <c r="E252" s="4"/>
-      <c r="F252" s="4"/>
-      <c r="G252" s="4"/>
-      <c r="H252" s="4"/>
-      <c r="I252" s="9"/>
-      <c r="J252" s="8"/>
-      <c r="K252" s="4"/>
-      <c r="L252" s="4"/>
-      <c r="M252" s="9"/>
-    </row>
-    <row r="253" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A253" s="1">
-        <v>170</v>
-      </c>
-      <c r="B253" s="6"/>
-      <c r="C253" s="4"/>
-      <c r="D253" s="4"/>
-      <c r="E253" s="4"/>
-      <c r="F253" s="4"/>
-      <c r="G253" s="4"/>
-      <c r="H253" s="4"/>
-      <c r="I253" s="9"/>
-      <c r="J253" s="8"/>
-      <c r="K253" s="4"/>
-      <c r="L253" s="4"/>
-      <c r="M253" s="9"/>
-    </row>
-    <row r="254" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A254" s="1">
-        <v>171</v>
-      </c>
-      <c r="B254" s="6"/>
-      <c r="C254" s="4"/>
-      <c r="D254" s="4"/>
-      <c r="E254" s="4"/>
-      <c r="F254" s="4"/>
-      <c r="G254" s="4"/>
-      <c r="H254" s="4"/>
-      <c r="I254" s="9"/>
-      <c r="J254" s="8"/>
-      <c r="K254" s="4"/>
-      <c r="L254" s="4"/>
-      <c r="M254" s="9"/>
-    </row>
-    <row r="255" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A255" s="1">
-        <v>172</v>
-      </c>
-      <c r="B255" s="6"/>
-      <c r="C255" s="4"/>
-      <c r="D255" s="4"/>
-      <c r="E255" s="4"/>
-      <c r="F255" s="4"/>
-      <c r="G255" s="4"/>
-      <c r="H255" s="4"/>
-      <c r="I255" s="9"/>
-      <c r="J255" s="8"/>
-      <c r="K255" s="4"/>
-      <c r="L255" s="4"/>
-      <c r="M255" s="9"/>
-    </row>
-    <row r="256" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="1">
-        <v>173</v>
-      </c>
-      <c r="B256" s="6"/>
-      <c r="C256" s="4"/>
-      <c r="D256" s="4"/>
-      <c r="E256" s="4"/>
-      <c r="F256" s="4"/>
-      <c r="G256" s="4"/>
-      <c r="H256" s="4"/>
-      <c r="I256" s="9"/>
-      <c r="J256" s="8"/>
-      <c r="K256" s="4"/>
-      <c r="L256" s="4"/>
-      <c r="M256" s="9"/>
-    </row>
-    <row r="257" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A257" s="1">
-        <v>174</v>
-      </c>
-      <c r="B257" s="6"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="4"/>
-      <c r="G257" s="4"/>
-      <c r="H257" s="4"/>
-      <c r="I257" s="9"/>
-      <c r="J257" s="8"/>
-      <c r="K257" s="4"/>
-      <c r="L257" s="4"/>
-      <c r="M257" s="9"/>
-    </row>
-    <row r="258" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="1">
-        <v>175</v>
-      </c>
-      <c r="B258" s="6"/>
-      <c r="C258" s="4"/>
-      <c r="D258" s="4"/>
-      <c r="E258" s="4"/>
-      <c r="F258" s="4"/>
-      <c r="G258" s="4"/>
-      <c r="H258" s="4"/>
-      <c r="I258" s="9"/>
-      <c r="J258" s="8"/>
-      <c r="K258" s="4"/>
-      <c r="L258" s="4"/>
-      <c r="M258" s="9"/>
-    </row>
-    <row r="259" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="1">
-        <v>176</v>
-      </c>
-      <c r="B259" s="6"/>
-      <c r="C259" s="4"/>
-      <c r="D259" s="4"/>
-      <c r="E259" s="4"/>
-      <c r="F259" s="4"/>
-      <c r="G259" s="4"/>
-      <c r="H259" s="4"/>
-      <c r="I259" s="9"/>
-      <c r="J259" s="8"/>
-      <c r="K259" s="4"/>
-      <c r="L259" s="4"/>
-      <c r="M259" s="9"/>
-    </row>
-    <row r="260" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A260" s="1">
-        <v>177</v>
-      </c>
-      <c r="B260" s="6"/>
-      <c r="C260" s="4"/>
-      <c r="D260" s="4"/>
-      <c r="E260" s="4"/>
-      <c r="F260" s="4"/>
-      <c r="G260" s="4"/>
-      <c r="H260" s="4"/>
-      <c r="I260" s="9"/>
-      <c r="J260" s="8"/>
-      <c r="K260" s="4"/>
-      <c r="L260" s="4"/>
-      <c r="M260" s="9"/>
-    </row>
-    <row r="261" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A261" s="1">
-        <v>178</v>
-      </c>
-      <c r="B261" s="6"/>
-      <c r="C261" s="4"/>
-      <c r="D261" s="4"/>
-      <c r="E261" s="4"/>
-      <c r="F261" s="4"/>
-      <c r="G261" s="4"/>
-      <c r="H261" s="4"/>
-      <c r="I261" s="9"/>
-      <c r="J261" s="8"/>
-      <c r="K261" s="4"/>
-      <c r="L261" s="4"/>
-      <c r="M261" s="9"/>
-    </row>
-    <row r="262" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A262" s="1">
-        <v>179</v>
-      </c>
-      <c r="B262" s="6"/>
-      <c r="C262" s="4"/>
-      <c r="D262" s="4"/>
-      <c r="E262" s="4"/>
-      <c r="F262" s="4"/>
-      <c r="G262" s="4"/>
-      <c r="H262" s="4"/>
-      <c r="I262" s="9"/>
-      <c r="J262" s="8"/>
-      <c r="K262" s="4"/>
-      <c r="L262" s="4"/>
-      <c r="M262" s="9"/>
-    </row>
-    <row r="263" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A263" s="1">
-        <v>180</v>
-      </c>
-      <c r="B263" s="6"/>
-      <c r="C263" s="4"/>
-      <c r="D263" s="4"/>
-      <c r="E263" s="4"/>
-      <c r="F263" s="4"/>
-      <c r="G263" s="4"/>
-      <c r="H263" s="4"/>
-      <c r="I263" s="9"/>
-      <c r="J263" s="8"/>
-      <c r="K263" s="4"/>
-      <c r="L263" s="4"/>
-      <c r="M263" s="9"/>
-    </row>
-    <row r="264" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A264" s="1">
-        <v>181</v>
-      </c>
-      <c r="B264" s="6"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="4"/>
-      <c r="G264" s="4"/>
-      <c r="H264" s="4"/>
-      <c r="I264" s="9"/>
-      <c r="J264" s="8"/>
-      <c r="K264" s="4"/>
-      <c r="L264" s="4"/>
-      <c r="M264" s="9"/>
-    </row>
-    <row r="265" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A265" s="1">
-        <v>182</v>
-      </c>
-      <c r="B265" s="6"/>
-      <c r="C265" s="4"/>
-      <c r="D265" s="4"/>
-      <c r="E265" s="4"/>
-      <c r="F265" s="4"/>
-      <c r="G265" s="4"/>
-      <c r="H265" s="4"/>
-      <c r="I265" s="9"/>
-      <c r="J265" s="8"/>
-      <c r="K265" s="4"/>
-      <c r="L265" s="4"/>
-      <c r="M265" s="9"/>
-    </row>
-    <row r="266" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A266" s="1">
-        <v>183</v>
-      </c>
-      <c r="B266" s="6"/>
-      <c r="C266" s="4"/>
-      <c r="D266" s="4"/>
-      <c r="E266" s="4"/>
-      <c r="F266" s="4"/>
-      <c r="G266" s="4"/>
-      <c r="H266" s="4"/>
-      <c r="I266" s="9"/>
-      <c r="J266" s="8"/>
-      <c r="K266" s="4"/>
-      <c r="L266" s="4"/>
-      <c r="M266" s="9"/>
-    </row>
-    <row r="267" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A267" s="1">
-        <v>184</v>
-      </c>
-      <c r="B267" s="6"/>
-      <c r="C267" s="4"/>
-      <c r="D267" s="4"/>
-      <c r="E267" s="4"/>
-      <c r="F267" s="4"/>
-      <c r="G267" s="4"/>
-      <c r="H267" s="4"/>
-      <c r="I267" s="9"/>
-      <c r="J267" s="8"/>
-      <c r="K267" s="4"/>
-      <c r="L267" s="4"/>
-      <c r="M267" s="9"/>
-    </row>
-    <row r="268" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A268" s="1">
-        <v>185</v>
-      </c>
-      <c r="B268" s="6"/>
-      <c r="C268" s="4"/>
-      <c r="D268" s="4"/>
-      <c r="E268" s="4"/>
-      <c r="F268" s="4"/>
-      <c r="G268" s="4"/>
-      <c r="H268" s="4"/>
-      <c r="I268" s="9"/>
-      <c r="J268" s="8"/>
-      <c r="K268" s="4"/>
-      <c r="L268" s="4"/>
-      <c r="M268" s="9"/>
-    </row>
-    <row r="269" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A269" s="1">
-        <v>186</v>
-      </c>
-      <c r="B269" s="6"/>
-      <c r="C269" s="4"/>
-      <c r="D269" s="4"/>
-      <c r="E269" s="4"/>
-      <c r="F269" s="4"/>
-      <c r="G269" s="4"/>
-      <c r="H269" s="4"/>
-      <c r="I269" s="9"/>
-      <c r="J269" s="8"/>
-      <c r="K269" s="4"/>
-      <c r="L269" s="4"/>
-      <c r="M269" s="9"/>
-    </row>
-    <row r="270" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A270" s="1">
-        <v>187</v>
-      </c>
-      <c r="B270" s="6"/>
-      <c r="C270" s="4"/>
-      <c r="D270" s="4"/>
-      <c r="E270" s="4"/>
-      <c r="F270" s="4"/>
-      <c r="G270" s="4"/>
-      <c r="H270" s="4"/>
-      <c r="I270" s="9"/>
-      <c r="J270" s="8"/>
-      <c r="K270" s="4"/>
-      <c r="L270" s="4"/>
-      <c r="M270" s="9"/>
-    </row>
-    <row r="271" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A271" s="1">
-        <v>188</v>
-      </c>
-      <c r="B271" s="6"/>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-      <c r="E271" s="4"/>
-      <c r="F271" s="4"/>
-      <c r="G271" s="4"/>
-      <c r="H271" s="4"/>
-      <c r="I271" s="9"/>
-      <c r="J271" s="8"/>
-      <c r="K271" s="4"/>
-      <c r="L271" s="4"/>
-      <c r="M271" s="9"/>
-    </row>
-    <row r="272" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A272" s="1">
-        <v>189</v>
-      </c>
-      <c r="B272" s="6"/>
-      <c r="C272" s="4"/>
-      <c r="D272" s="4"/>
-      <c r="E272" s="4"/>
-      <c r="F272" s="4"/>
-      <c r="G272" s="4"/>
-      <c r="H272" s="4"/>
-      <c r="I272" s="9"/>
-      <c r="J272" s="8"/>
-      <c r="K272" s="4"/>
-      <c r="L272" s="4"/>
-      <c r="M272" s="9"/>
-    </row>
-    <row r="273" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A273" s="1">
-        <v>190</v>
-      </c>
-      <c r="B273" s="6"/>
-      <c r="C273" s="4"/>
-      <c r="D273" s="4"/>
-      <c r="E273" s="4"/>
-      <c r="F273" s="4"/>
-      <c r="G273" s="4"/>
-      <c r="H273" s="4"/>
-      <c r="I273" s="9"/>
-      <c r="J273" s="8"/>
-      <c r="K273" s="4"/>
-      <c r="L273" s="4"/>
-      <c r="M273" s="9"/>
-    </row>
-    <row r="274" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A274" s="1">
-        <v>191</v>
-      </c>
-      <c r="B274" s="6"/>
-      <c r="C274" s="4"/>
-      <c r="D274" s="4"/>
-      <c r="E274" s="4"/>
-      <c r="F274" s="4"/>
-      <c r="G274" s="4"/>
-      <c r="H274" s="4"/>
-      <c r="I274" s="9"/>
-      <c r="J274" s="8"/>
-      <c r="K274" s="4"/>
-      <c r="L274" s="4"/>
-      <c r="M274" s="9"/>
-    </row>
-    <row r="275" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A275" s="1">
-        <v>192</v>
-      </c>
-      <c r="B275" s="6"/>
-      <c r="C275" s="4"/>
-      <c r="D275" s="4"/>
-      <c r="E275" s="4"/>
-      <c r="F275" s="4"/>
-      <c r="G275" s="4"/>
-      <c r="H275" s="4"/>
-      <c r="I275" s="9"/>
-      <c r="J275" s="8"/>
-      <c r="K275" s="4"/>
-      <c r="L275" s="4"/>
-      <c r="M275" s="9"/>
-    </row>
-    <row r="276" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A276" s="1">
-        <v>193</v>
-      </c>
-      <c r="B276" s="6"/>
-      <c r="C276" s="4"/>
-      <c r="D276" s="4"/>
-      <c r="E276" s="4"/>
-      <c r="F276" s="4"/>
-      <c r="G276" s="4"/>
-      <c r="H276" s="4"/>
-      <c r="I276" s="9"/>
-      <c r="J276" s="8"/>
-      <c r="K276" s="4"/>
-      <c r="L276" s="4"/>
-      <c r="M276" s="9"/>
-    </row>
-    <row r="277" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A277" s="1">
-        <v>194</v>
-      </c>
-      <c r="B277" s="6"/>
-      <c r="C277" s="4"/>
-      <c r="D277" s="4"/>
-      <c r="E277" s="4"/>
-      <c r="F277" s="4"/>
-      <c r="G277" s="4"/>
-      <c r="H277" s="4"/>
-      <c r="I277" s="9"/>
-      <c r="J277" s="8"/>
-      <c r="K277" s="4"/>
-      <c r="L277" s="4"/>
-      <c r="M277" s="9"/>
-    </row>
-    <row r="278" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A278" s="1">
-        <v>195</v>
-      </c>
-      <c r="B278" s="6"/>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-      <c r="E278" s="4"/>
-      <c r="F278" s="4"/>
-      <c r="G278" s="4"/>
-      <c r="H278" s="4"/>
-      <c r="I278" s="9"/>
-      <c r="J278" s="8"/>
-      <c r="K278" s="4"/>
-      <c r="L278" s="4"/>
-      <c r="M278" s="9"/>
-    </row>
-    <row r="279" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A279" s="1">
-        <v>196</v>
-      </c>
-      <c r="B279" s="6"/>
-      <c r="C279" s="4"/>
-      <c r="D279" s="4"/>
-      <c r="E279" s="4"/>
-      <c r="F279" s="4"/>
-      <c r="G279" s="4"/>
-      <c r="H279" s="4"/>
-      <c r="I279" s="9"/>
-      <c r="J279" s="8"/>
-      <c r="K279" s="4"/>
-      <c r="L279" s="4"/>
-      <c r="M279" s="9"/>
-    </row>
-    <row r="280" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A280" s="1">
-        <v>197</v>
-      </c>
-      <c r="B280" s="6"/>
-      <c r="C280" s="4"/>
-      <c r="D280" s="4"/>
-      <c r="E280" s="4"/>
-      <c r="F280" s="4"/>
-      <c r="G280" s="4"/>
-      <c r="H280" s="4"/>
-      <c r="I280" s="9"/>
-      <c r="J280" s="8"/>
-      <c r="K280" s="4"/>
-      <c r="L280" s="4"/>
-      <c r="M280" s="9"/>
-    </row>
-    <row r="281" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A281" s="1">
-        <v>198</v>
-      </c>
-      <c r="B281" s="6"/>
-      <c r="C281" s="4"/>
-      <c r="D281" s="4"/>
-      <c r="E281" s="4"/>
-      <c r="F281" s="4"/>
-      <c r="G281" s="4"/>
-      <c r="H281" s="4"/>
-      <c r="I281" s="9"/>
-      <c r="J281" s="8"/>
-      <c r="K281" s="4"/>
-      <c r="L281" s="4"/>
-      <c r="M281" s="9"/>
-    </row>
-    <row r="282" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A282" s="1">
-        <v>199</v>
-      </c>
-      <c r="B282" s="6"/>
-      <c r="C282" s="4"/>
-      <c r="D282" s="4"/>
-      <c r="E282" s="4"/>
-      <c r="F282" s="4"/>
-      <c r="G282" s="4"/>
-      <c r="H282" s="4"/>
-      <c r="I282" s="9"/>
-      <c r="J282" s="8"/>
-      <c r="K282" s="4"/>
-      <c r="L282" s="4"/>
-      <c r="M282" s="9"/>
-    </row>
-    <row r="283" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A283" s="1">
-        <v>200</v>
-      </c>
-      <c r="B283" s="6"/>
-      <c r="C283" s="4"/>
-      <c r="D283" s="4"/>
-      <c r="E283" s="4"/>
-      <c r="F283" s="4"/>
-      <c r="G283" s="4"/>
-      <c r="H283" s="4"/>
-      <c r="I283" s="9"/>
-      <c r="J283" s="8"/>
-      <c r="K283" s="4"/>
-      <c r="L283" s="4"/>
-      <c r="M283" s="9"/>
-    </row>
-    <row r="284" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A284" s="1">
-        <v>201</v>
-      </c>
-      <c r="B284" s="6"/>
-      <c r="C284" s="4"/>
-      <c r="D284" s="4"/>
-      <c r="E284" s="4"/>
-      <c r="F284" s="4"/>
-      <c r="G284" s="4"/>
-      <c r="H284" s="4"/>
-      <c r="I284" s="9"/>
-      <c r="J284" s="8"/>
-      <c r="K284" s="4"/>
-      <c r="L284" s="4"/>
-      <c r="M284" s="9"/>
-    </row>
-    <row r="285" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A285" s="1">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="286" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A286" s="1">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="287" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A287" s="1">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="288" spans="1:13" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A288" s="1">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="289" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A289" s="1">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="290" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A290" s="1">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="291" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A291" s="1">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="292" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A292" s="1">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="293" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A293" s="1">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="294" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A294" s="1">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="295" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A295" s="1">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="296" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A296" s="1">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="297" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A297" s="1">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="298" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A298" s="1">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="299" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A299" s="1">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="300" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A300" s="1">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="301" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A301" s="1">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="302" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="1">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="303" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A303" s="1">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="304" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A304" s="1">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="305" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A305" s="1">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="306" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A306" s="1">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="307" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A307" s="1">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="308" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A308" s="1">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="309" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A309" s="1">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="310" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A310" s="1">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="311" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A311" s="1">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="312" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A312" s="1">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="313" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A313" s="1">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="314" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A314" s="1">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="315" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A315" s="1">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="316" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A316" s="1">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="317" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A317" s="1">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="318" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A318" s="1">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="319" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A319" s="1">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="320" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A320" s="1">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="321" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A321" s="1">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="322" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A322" s="1">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="323" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A323" s="1">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="324" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A324" s="1">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="325" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A325" s="1">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="326" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A326" s="1">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="327" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A327" s="1">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="328" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A328" s="1">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="329" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A329" s="1">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="330" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A330" s="1">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="331" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A331" s="1">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="332" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A332" s="1">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="333" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A333" s="1">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="334" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A334" s="1">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="335" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A335" s="1">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="336" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A336" s="1">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="337" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A337" s="1">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="338" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A338" s="1">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="339" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A339" s="1">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="340" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A340" s="1">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="341" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A341" s="1">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="342" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A342" s="1">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="343" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A343" s="1">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="344" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A344" s="1">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="345" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A345" s="1">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="346" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A346" s="1">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="347" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A347" s="1">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="348" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A348" s="1">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="349" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A349" s="1">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="350" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A350" s="1">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="351" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A351" s="1">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="352" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A352" s="1">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="353" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A353" s="1">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="354" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A354" s="1">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="355" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A355" s="1">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="356" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="1">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="357" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="1">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="358" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A358" s="1">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="359" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="1">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="360" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="1">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="361" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="1">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="362" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A362" s="1">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="363" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A363" s="1">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="364" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A364" s="1">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="365" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A365" s="1">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="366" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A366" s="1">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="367" spans="1:1" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A367" s="1">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="368" spans="1:1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+      <c r="K194" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L194" s="4">
+        <v>6365</v>
+      </c>
+      <c r="M194" s="9" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="195" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="I134:I139"/>
-    <mergeCell ref="K134:K139"/>
+  <mergeCells count="11">
+    <mergeCell ref="E138:E139"/>
+    <mergeCell ref="E134:E137"/>
+    <mergeCell ref="F49:F54"/>
+    <mergeCell ref="F58:F61"/>
+    <mergeCell ref="G58:G61"/>
+    <mergeCell ref="E49:E54"/>
+    <mergeCell ref="G49:G54"/>
     <mergeCell ref="F134:F137"/>
     <mergeCell ref="G134:G137"/>
     <mergeCell ref="G138:G139"/>
     <mergeCell ref="F138:F139"/>
-    <mergeCell ref="H134:H139"/>
-    <mergeCell ref="D134:D137"/>
-    <mergeCell ref="D138:D139"/>
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="H49:H54"/>
-    <mergeCell ref="F49:F54"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="D49:D54"/>
-    <mergeCell ref="E49:E54"/>
-    <mergeCell ref="G49:G54"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/data/transactions/أذونات الإضافة لشهر 5.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5D150F8-59D7-4B1C-B701-8FD963B52A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D310A3-C7CA-4D40-86A7-F9BBF452085B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -387,9 +387,6 @@
     <t>26-4-2026</t>
   </si>
   <si>
-    <t>المصريه  لتشكيل المعادن</t>
-  </si>
-  <si>
     <t>العصريه</t>
   </si>
   <si>
@@ -1186,6 +1183,9 @@
   </si>
   <si>
     <t xml:space="preserve">العصريه </t>
+  </si>
+  <si>
+    <t>المصريه لتشكيل المعادن</t>
   </si>
 </sst>
 </file>
@@ -1289,9 +1289,10 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1511,14 +1512,8 @@
     <xf numFmtId="14" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1529,10 +1524,16 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1853,7 +1854,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1870,7 +1871,7 @@
     </row>
     <row r="4" spans="1:13" s="23" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3573,7 +3574,7 @@
         <v>149122.79999999999</v>
       </c>
       <c r="G49" s="36">
-        <v>1451290</v>
+        <v>1273061</v>
       </c>
       <c r="H49" s="28">
         <v>59830</v>
@@ -3583,7 +3584,7 @@
       </c>
       <c r="J49" s="29"/>
       <c r="K49" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L49" s="27">
         <v>6323</v>
@@ -3605,9 +3606,9 @@
       <c r="D50" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E50" s="37"/>
+      <c r="E50" s="38"/>
       <c r="F50" s="40"/>
-      <c r="G50" s="37"/>
+      <c r="G50" s="38"/>
       <c r="H50" s="28">
         <v>59830</v>
       </c>
@@ -3616,7 +3617,7 @@
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L50" s="27">
         <v>6323</v>
@@ -3638,9 +3639,9 @@
       <c r="D51" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E51" s="37"/>
+      <c r="E51" s="38"/>
       <c r="F51" s="40"/>
-      <c r="G51" s="37"/>
+      <c r="G51" s="38"/>
       <c r="H51" s="28">
         <v>59830</v>
       </c>
@@ -3649,7 +3650,7 @@
       </c>
       <c r="J51" s="29"/>
       <c r="K51" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L51" s="27">
         <v>6323</v>
@@ -3671,9 +3672,9 @@
       <c r="D52" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="37"/>
+      <c r="E52" s="38"/>
       <c r="F52" s="40"/>
-      <c r="G52" s="37"/>
+      <c r="G52" s="38"/>
       <c r="H52" s="28">
         <v>59830</v>
       </c>
@@ -3682,7 +3683,7 @@
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L52" s="27">
         <v>6323</v>
@@ -3704,9 +3705,9 @@
       <c r="D53" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E53" s="37"/>
+      <c r="E53" s="38"/>
       <c r="F53" s="40"/>
-      <c r="G53" s="37"/>
+      <c r="G53" s="38"/>
       <c r="H53" s="28">
         <v>59830</v>
       </c>
@@ -3715,7 +3716,7 @@
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L53" s="27">
         <v>6323</v>
@@ -3737,9 +3738,9 @@
       <c r="D54" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E54" s="38"/>
+      <c r="E54" s="37"/>
       <c r="F54" s="41"/>
-      <c r="G54" s="38"/>
+      <c r="G54" s="37"/>
       <c r="H54" s="28">
         <v>59830</v>
       </c>
@@ -3748,7 +3749,7 @@
       </c>
       <c r="J54" s="29"/>
       <c r="K54" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L54" s="27">
         <v>6323</v>
@@ -3762,7 +3763,7 @@
         <v>51</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>115</v>
@@ -3787,7 +3788,7 @@
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L55" s="4">
         <v>6324</v>
@@ -3801,7 +3802,7 @@
         <v>52</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>116</v>
@@ -3826,7 +3827,7 @@
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L56" s="4">
         <v>6324</v>
@@ -3840,7 +3841,7 @@
         <v>53</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>117</v>
@@ -3865,7 +3866,7 @@
       </c>
       <c r="J57" s="8"/>
       <c r="K57" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L57" s="4">
         <v>6324</v>
@@ -3904,7 +3905,7 @@
       </c>
       <c r="J58" s="29"/>
       <c r="K58" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L58" s="27">
         <v>6325</v>
@@ -3930,7 +3931,7 @@
         <v>95</v>
       </c>
       <c r="F59" s="40"/>
-      <c r="G59" s="37"/>
+      <c r="G59" s="38"/>
       <c r="H59" s="27">
         <v>59837</v>
       </c>
@@ -3939,7 +3940,7 @@
       </c>
       <c r="J59" s="29"/>
       <c r="K59" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L59" s="27">
         <v>6325</v>
@@ -3953,10 +3954,10 @@
         <v>56</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D60" s="27" t="s">
         <v>16</v>
@@ -3965,7 +3966,7 @@
         <v>88</v>
       </c>
       <c r="F60" s="40"/>
-      <c r="G60" s="37"/>
+      <c r="G60" s="38"/>
       <c r="H60" s="27">
         <v>59837</v>
       </c>
@@ -3974,7 +3975,7 @@
       </c>
       <c r="J60" s="29"/>
       <c r="K60" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L60" s="27">
         <v>6325</v>
@@ -3988,10 +3989,10 @@
         <v>57</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D61" s="27" t="s">
         <v>16</v>
@@ -4000,7 +4001,7 @@
         <v>80</v>
       </c>
       <c r="F61" s="41"/>
-      <c r="G61" s="38"/>
+      <c r="G61" s="37"/>
       <c r="H61" s="27">
         <v>59837</v>
       </c>
@@ -4009,7 +4010,7 @@
       </c>
       <c r="J61" s="29"/>
       <c r="K61" s="27" t="s">
-        <v>119</v>
+        <v>385</v>
       </c>
       <c r="L61" s="27">
         <v>6325</v>
@@ -4023,10 +4024,10 @@
         <v>58</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>16</v>
@@ -4048,7 +4049,7 @@
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L62" s="4">
         <v>6326</v>
@@ -4062,10 +4063,10 @@
         <v>59</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>16</v>
@@ -4087,7 +4088,7 @@
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L63" s="4">
         <v>6326</v>
@@ -4101,10 +4102,10 @@
         <v>60</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>16</v>
@@ -4126,7 +4127,7 @@
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L64" s="4">
         <v>6327</v>
@@ -4140,10 +4141,10 @@
         <v>61</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>16</v>
@@ -4165,7 +4166,7 @@
       </c>
       <c r="J65" s="8"/>
       <c r="K65" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L65" s="4">
         <v>6327</v>
@@ -4179,13 +4180,13 @@
         <v>62</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C66" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="E66" s="4">
         <v>50</v>
@@ -4204,7 +4205,7 @@
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L66" s="4">
         <v>6327</v>
@@ -4218,10 +4219,10 @@
         <v>63</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>16</v>
@@ -4243,7 +4244,7 @@
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L67" s="4">
         <v>6327</v>
@@ -4257,10 +4258,10 @@
         <v>64</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>16</v>
@@ -4282,7 +4283,7 @@
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L68" s="4">
         <v>6327</v>
@@ -4296,10 +4297,10 @@
         <v>65</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>16</v>
@@ -4321,7 +4322,7 @@
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L69" s="4">
         <v>6327</v>
@@ -4335,10 +4336,10 @@
         <v>66</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D70" s="4" t="s">
         <v>16</v>
@@ -4360,7 +4361,7 @@
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L70" s="4">
         <v>6327</v>
@@ -4374,10 +4375,10 @@
         <v>67</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>16</v>
@@ -4399,7 +4400,7 @@
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L71" s="4">
         <v>6327</v>
@@ -4413,10 +4414,10 @@
         <v>69</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>16</v>
@@ -4438,7 +4439,7 @@
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L72" s="4">
         <v>6327</v>
@@ -4452,10 +4453,10 @@
         <v>70</v>
       </c>
       <c r="B73" s="12" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>16</v>
@@ -4477,7 +4478,7 @@
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L73" s="4">
         <v>6328</v>
@@ -4491,10 +4492,10 @@
         <v>71</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D74" s="4" t="s">
         <v>16</v>
@@ -4516,7 +4517,7 @@
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L74" s="4">
         <v>6328</v>
@@ -4530,10 +4531,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="12" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D75" s="4" t="s">
         <v>16</v>
@@ -4555,7 +4556,7 @@
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L75" s="4">
         <v>6328</v>
@@ -4569,10 +4570,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="12" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>16</v>
@@ -4594,7 +4595,7 @@
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L76" s="4">
         <v>6328</v>
@@ -4608,13 +4609,13 @@
         <v>74</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>161</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>162</v>
       </c>
       <c r="E77" s="4">
         <v>45.5</v>
@@ -4633,7 +4634,7 @@
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L77" s="4">
         <v>6329</v>
@@ -4647,10 +4648,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>16</v>
@@ -4672,7 +4673,7 @@
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L78" s="4">
         <v>6330</v>
@@ -4686,10 +4687,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>16</v>
@@ -4707,11 +4708,11 @@
         <v>6525</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L79" s="4">
         <v>6331</v>
@@ -4725,10 +4726,10 @@
         <v>77</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>16</v>
@@ -4746,11 +4747,11 @@
         <v>6525</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L80" s="4">
         <v>6331</v>
@@ -4764,10 +4765,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>16</v>
@@ -4785,11 +4786,11 @@
         <v>6526</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L81" s="4">
         <v>6332</v>
@@ -4803,10 +4804,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>16</v>
@@ -4824,11 +4825,11 @@
         <v>6526</v>
       </c>
       <c r="I82" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L82" s="4">
         <v>6332</v>
@@ -4842,10 +4843,10 @@
         <v>80</v>
       </c>
       <c r="B83" s="12" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>16</v>
@@ -4863,11 +4864,11 @@
         <v>6526</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L83" s="4">
         <v>6332</v>
@@ -4881,10 +4882,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C84" s="15" t="s">
         <v>203</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>204</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>16</v>
@@ -4902,11 +4903,11 @@
         <v>929</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L84" s="4">
         <v>6333</v>
@@ -4920,10 +4921,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>16</v>
@@ -4941,11 +4942,11 @@
         <v>929</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L85" s="4">
         <v>6333</v>
@@ -4959,10 +4960,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>16</v>
@@ -4980,11 +4981,11 @@
         <v>929</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L86" s="4">
         <v>6333</v>
@@ -4998,10 +4999,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>16</v>
@@ -5019,11 +5020,11 @@
         <v>929</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L87" s="4">
         <v>6333</v>
@@ -5037,7 +5038,7 @@
         <v>85</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C88" s="4" t="s">
         <v>115</v>
@@ -5058,11 +5059,11 @@
         <v>929</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L88" s="4">
         <v>6333</v>
@@ -5076,10 +5077,10 @@
         <v>86</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>16</v>
@@ -5097,11 +5098,11 @@
         <v>929</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L89" s="4">
         <v>6333</v>
@@ -5115,7 +5116,7 @@
         <v>87</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C90" s="4" t="s">
         <v>116</v>
@@ -5136,11 +5137,11 @@
         <v>929</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L90" s="4">
         <v>6333</v>
@@ -5154,10 +5155,10 @@
         <v>88</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D91" s="4" t="s">
         <v>16</v>
@@ -5175,11 +5176,11 @@
         <v>929</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L91" s="4">
         <v>6333</v>
@@ -5193,10 +5194,10 @@
         <v>89</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>16</v>
@@ -5214,11 +5215,11 @@
         <v>929</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L92" s="4">
         <v>6333</v>
@@ -5232,10 +5233,10 @@
         <v>90</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D93" s="4" t="s">
         <v>16</v>
@@ -5253,11 +5254,11 @@
         <v>929</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L93" s="4">
         <v>6333</v>
@@ -5271,10 +5272,10 @@
         <v>91</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>16</v>
@@ -5292,11 +5293,11 @@
         <v>929</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L94" s="4">
         <v>6333</v>
@@ -5310,10 +5311,10 @@
         <v>92</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>16</v>
@@ -5331,11 +5332,11 @@
         <v>929</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L95" s="4">
         <v>6333</v>
@@ -5349,10 +5350,10 @@
         <v>93</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>16</v>
@@ -5370,11 +5371,11 @@
         <v>929</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L96" s="4">
         <v>6333</v>
@@ -5388,10 +5389,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>16</v>
@@ -5409,11 +5410,11 @@
         <v>929</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L97" s="4">
         <v>6333</v>
@@ -5427,10 +5428,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D98" s="4" t="s">
         <v>16</v>
@@ -5448,11 +5449,11 @@
         <v>928</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L98" s="4">
         <v>6335</v>
@@ -5466,10 +5467,10 @@
         <v>96</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D99" s="4" t="s">
         <v>16</v>
@@ -5487,11 +5488,11 @@
         <v>928</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L99" s="4">
         <v>6335</v>
@@ -5505,13 +5506,13 @@
         <v>97</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E100" s="4">
         <v>6</v>
@@ -5526,11 +5527,11 @@
         <v>928</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L100" s="4">
         <v>6335</v>
@@ -5544,10 +5545,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>16</v>
@@ -5565,11 +5566,11 @@
         <v>928</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L101" s="4">
         <v>6335</v>
@@ -5583,10 +5584,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>16</v>
@@ -5604,11 +5605,11 @@
         <v>928</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L102" s="4">
         <v>6335</v>
@@ -5622,10 +5623,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D103" s="4" t="s">
         <v>16</v>
@@ -5643,11 +5644,11 @@
         <v>928</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L103" s="4">
         <v>6335</v>
@@ -5661,10 +5662,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="C104" s="15" t="s">
         <v>203</v>
-      </c>
-      <c r="C104" s="15" t="s">
-        <v>204</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>16</v>
@@ -5682,11 +5683,11 @@
         <v>928</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L104" s="4">
         <v>6335</v>
@@ -5700,13 +5701,13 @@
         <v>102</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E105" s="4">
         <v>50</v>
@@ -5721,11 +5722,11 @@
         <v>928</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J105" s="8"/>
       <c r="K105" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L105" s="4">
         <v>6335</v>
@@ -5739,10 +5740,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D106" s="4" t="s">
         <v>16</v>
@@ -5760,11 +5761,11 @@
         <v>928</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J106" s="8"/>
       <c r="K106" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L106" s="4">
         <v>6335</v>
@@ -5778,10 +5779,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D107" s="4" t="s">
         <v>16</v>
@@ -5799,11 +5800,11 @@
         <v>928</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L107" s="4">
         <v>6335</v>
@@ -5817,13 +5818,13 @@
         <v>105</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E108" s="4">
         <v>50</v>
@@ -5838,11 +5839,11 @@
         <v>928</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="L108" s="4">
         <v>6335</v>
@@ -5856,13 +5857,13 @@
         <v>106</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E109" s="4">
         <v>50</v>
@@ -5877,11 +5878,11 @@
         <v>81</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L109" s="4">
         <v>6336</v>
@@ -5895,10 +5896,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D110" s="4" t="s">
         <v>16</v>
@@ -5916,11 +5917,11 @@
         <v>81</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J110" s="8"/>
       <c r="K110" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L110" s="4">
         <v>6336</v>
@@ -5934,10 +5935,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D111" s="4" t="s">
         <v>16</v>
@@ -5955,11 +5956,11 @@
         <v>81</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J111" s="8"/>
       <c r="K111" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L111" s="4">
         <v>6336</v>
@@ -5973,10 +5974,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="12" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D112" s="4" t="s">
         <v>16</v>
@@ -5994,11 +5995,11 @@
         <v>81</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L112" s="4">
         <v>6336</v>
@@ -6012,10 +6013,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D113" s="4" t="s">
         <v>16</v>
@@ -6033,11 +6034,11 @@
         <v>81</v>
       </c>
       <c r="I113" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J113" s="8"/>
       <c r="K113" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L113" s="4">
         <v>6336</v>
@@ -6051,10 +6052,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D114" s="4" t="s">
         <v>16</v>
@@ -6072,11 +6073,11 @@
         <v>81</v>
       </c>
       <c r="I114" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J114" s="8"/>
       <c r="K114" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L114" s="4">
         <v>6336</v>
@@ -6090,10 +6091,10 @@
         <v>113</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C115" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D115" s="17" t="s">
         <v>16</v>
@@ -6111,11 +6112,11 @@
         <v>1755</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J115" s="19"/>
       <c r="K115" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L115" s="17">
         <v>6337</v>
@@ -6129,10 +6130,10 @@
         <v>114</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C116" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D116" s="17" t="s">
         <v>16</v>
@@ -6150,11 +6151,11 @@
         <v>1755</v>
       </c>
       <c r="I116" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J116" s="19"/>
       <c r="K116" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L116" s="17">
         <v>6337</v>
@@ -6168,10 +6169,10 @@
         <v>115</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C117" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D117" s="17" t="s">
         <v>16</v>
@@ -6189,11 +6190,11 @@
         <v>1755</v>
       </c>
       <c r="I117" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J117" s="19"/>
       <c r="K117" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L117" s="17">
         <v>6337</v>
@@ -6207,10 +6208,10 @@
         <v>116</v>
       </c>
       <c r="B118" s="12" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C118" s="17" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D118" s="17" t="s">
         <v>16</v>
@@ -6228,11 +6229,11 @@
         <v>1755</v>
       </c>
       <c r="I118" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J118" s="19"/>
       <c r="K118" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L118" s="17">
         <v>6337</v>
@@ -6246,10 +6247,10 @@
         <v>117</v>
       </c>
       <c r="B119" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>16</v>
@@ -6267,11 +6268,11 @@
         <v>85</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J119" s="8"/>
       <c r="K119" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L119" s="4">
         <v>6339</v>
@@ -6285,10 +6286,10 @@
         <v>118</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>16</v>
@@ -6306,11 +6307,11 @@
         <v>85</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J120" s="8"/>
       <c r="K120" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L120" s="4">
         <v>6339</v>
@@ -6324,10 +6325,10 @@
         <v>119</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>16</v>
@@ -6345,11 +6346,11 @@
         <v>85</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J121" s="8"/>
       <c r="K121" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L121" s="4">
         <v>6339</v>
@@ -6363,10 +6364,10 @@
         <v>120</v>
       </c>
       <c r="B122" s="12" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D122" s="4" t="s">
         <v>16</v>
@@ -6384,11 +6385,11 @@
         <v>85</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J122" s="8"/>
       <c r="K122" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L122" s="4">
         <v>6339</v>
@@ -6402,10 +6403,10 @@
         <v>121</v>
       </c>
       <c r="B123" s="13" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>16</v>
@@ -6423,11 +6424,11 @@
         <v>85</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J123" s="8"/>
       <c r="K123" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L123" s="4">
         <v>6339</v>
@@ -6441,10 +6442,10 @@
         <v>122</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>16</v>
@@ -6462,11 +6463,11 @@
         <v>85</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J124" s="8"/>
       <c r="K124" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L124" s="4">
         <v>6339</v>
@@ -6480,10 +6481,10 @@
         <v>123</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>16</v>
@@ -6501,11 +6502,11 @@
         <v>86</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J125" s="8"/>
       <c r="K125" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L125" s="4">
         <v>6340</v>
@@ -6519,10 +6520,10 @@
         <v>124</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>16</v>
@@ -6540,11 +6541,11 @@
         <v>86</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J126" s="8"/>
       <c r="K126" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L126" s="4">
         <v>6340</v>
@@ -6558,10 +6559,10 @@
         <v>125</v>
       </c>
       <c r="B127" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D127" s="4" t="s">
         <v>16</v>
@@ -6579,11 +6580,11 @@
         <v>86</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J127" s="8"/>
       <c r="K127" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L127" s="4">
         <v>6340</v>
@@ -6597,10 +6598,10 @@
         <v>126</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>16</v>
@@ -6618,11 +6619,11 @@
         <v>86</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J128" s="8"/>
       <c r="K128" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L128" s="4">
         <v>6340</v>
@@ -6636,10 +6637,10 @@
         <v>127</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>16</v>
@@ -6657,11 +6658,11 @@
         <v>722</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J129" s="8"/>
       <c r="K129" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L129" s="4">
         <v>6341</v>
@@ -6675,10 +6676,10 @@
         <v>128</v>
       </c>
       <c r="B130" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>16</v>
@@ -6696,17 +6697,17 @@
         <v>89</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L130" s="4">
         <v>6342</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6714,10 +6715,10 @@
         <v>129</v>
       </c>
       <c r="B131" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D131" s="4" t="s">
         <v>16</v>
@@ -6735,17 +6736,17 @@
         <v>89</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L131" s="4">
         <v>6342</v>
       </c>
       <c r="M131" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6753,10 +6754,10 @@
         <v>130</v>
       </c>
       <c r="B132" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>16</v>
@@ -6774,17 +6775,17 @@
         <v>89</v>
       </c>
       <c r="I132" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J132" s="8"/>
       <c r="K132" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L132" s="4">
         <v>6342</v>
       </c>
       <c r="M132" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6792,10 +6793,10 @@
         <v>131</v>
       </c>
       <c r="B133" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D133" s="16" t="s">
         <v>16</v>
@@ -6813,11 +6814,11 @@
         <v>19241</v>
       </c>
       <c r="I133" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="J133" s="8"/>
       <c r="K133" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L133" s="4">
         <v>6343</v>
@@ -6834,13 +6835,13 @@
         <v>111</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D134" s="28" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E134" s="36">
-        <v>109.649</v>
+        <v>2101</v>
       </c>
       <c r="F134" s="36">
         <v>109.649</v>
@@ -6851,12 +6852,12 @@
       <c r="H134" s="28">
         <v>59846</v>
       </c>
-      <c r="I134" s="35" t="s">
-        <v>168</v>
+      <c r="I134" s="33" t="s">
+        <v>167</v>
       </c>
       <c r="J134" s="29"/>
-      <c r="K134" s="34" t="s">
-        <v>119</v>
+      <c r="K134" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L134" s="27">
         <v>6338</v>
@@ -6870,26 +6871,26 @@
         <v>133</v>
       </c>
       <c r="B135" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="D135" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E135" s="37"/>
-      <c r="F135" s="37"/>
-      <c r="G135" s="37"/>
+        <v>275</v>
+      </c>
+      <c r="D135" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E135" s="38"/>
+      <c r="F135" s="38"/>
+      <c r="G135" s="38"/>
       <c r="H135" s="28">
         <v>59846</v>
       </c>
-      <c r="I135" s="35" t="s">
-        <v>380</v>
+      <c r="I135" s="33" t="s">
+        <v>379</v>
       </c>
       <c r="J135" s="29"/>
-      <c r="K135" s="34" t="s">
-        <v>119</v>
+      <c r="K135" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L135" s="27">
         <v>6338</v>
@@ -6908,21 +6909,21 @@
       <c r="C136" s="27" t="s">
         <v>107</v>
       </c>
-      <c r="D136" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E136" s="37"/>
-      <c r="F136" s="37"/>
-      <c r="G136" s="37"/>
+      <c r="D136" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E136" s="38"/>
+      <c r="F136" s="38"/>
+      <c r="G136" s="38"/>
       <c r="H136" s="28">
         <v>59846</v>
       </c>
-      <c r="I136" s="35" t="s">
-        <v>381</v>
+      <c r="I136" s="33" t="s">
+        <v>380</v>
       </c>
       <c r="J136" s="29"/>
-      <c r="K136" s="34" t="s">
-        <v>119</v>
+      <c r="K136" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L136" s="27">
         <v>6338</v>
@@ -6935,27 +6936,27 @@
       <c r="A137" s="25">
         <v>135</v>
       </c>
-      <c r="B137" s="32" t="s">
+      <c r="B137" s="31" t="s">
+        <v>337</v>
+      </c>
+      <c r="C137" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="C137" s="33" t="s">
-        <v>339</v>
-      </c>
-      <c r="D137" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E137" s="38"/>
-      <c r="F137" s="38"/>
-      <c r="G137" s="38"/>
+      <c r="D137" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E137" s="37"/>
+      <c r="F137" s="37"/>
+      <c r="G137" s="37"/>
       <c r="H137" s="28">
         <v>59846</v>
       </c>
-      <c r="I137" s="35" t="s">
-        <v>382</v>
+      <c r="I137" s="33" t="s">
+        <v>381</v>
       </c>
       <c r="J137" s="29"/>
-      <c r="K137" s="34" t="s">
-        <v>119</v>
+      <c r="K137" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L137" s="27">
         <v>6338</v>
@@ -6969,32 +6970,32 @@
         <v>136</v>
       </c>
       <c r="B138" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="D138" s="31" t="s">
-        <v>60</v>
+        <v>276</v>
+      </c>
+      <c r="D138" s="34" t="s">
+        <v>161</v>
       </c>
       <c r="E138" s="36">
-        <v>2.101</v>
+        <v>13828</v>
       </c>
       <c r="F138" s="36">
         <v>157.89400000000001</v>
       </c>
       <c r="G138" s="36">
-        <v>283368.40000000002</v>
+        <v>2183368.4</v>
       </c>
       <c r="H138" s="28">
         <v>59846</v>
       </c>
-      <c r="I138" s="35" t="s">
-        <v>383</v>
+      <c r="I138" s="33" t="s">
+        <v>382</v>
       </c>
       <c r="J138" s="29"/>
-      <c r="K138" s="34" t="s">
-        <v>119</v>
+      <c r="K138" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L138" s="27">
         <v>6338</v>
@@ -7011,23 +7012,23 @@
         <v>113</v>
       </c>
       <c r="C139" s="27" t="s">
-        <v>278</v>
-      </c>
-      <c r="D139" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="E139" s="38"/>
-      <c r="F139" s="38"/>
-      <c r="G139" s="38"/>
+        <v>277</v>
+      </c>
+      <c r="D139" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="E139" s="37"/>
+      <c r="F139" s="37"/>
+      <c r="G139" s="37"/>
       <c r="H139" s="28">
         <v>59846</v>
       </c>
-      <c r="I139" s="35" t="s">
-        <v>384</v>
+      <c r="I139" s="33" t="s">
+        <v>383</v>
       </c>
       <c r="J139" s="29"/>
-      <c r="K139" s="34" t="s">
-        <v>119</v>
+      <c r="K139" s="32" t="s">
+        <v>385</v>
       </c>
       <c r="L139" s="27">
         <v>6338</v>
@@ -7041,10 +7042,10 @@
         <v>138</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>16</v>
@@ -7066,13 +7067,13 @@
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L140" s="4">
         <v>6344</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7080,10 +7081,10 @@
         <v>139</v>
       </c>
       <c r="B141" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="C141" s="14" t="s">
         <v>342</v>
-      </c>
-      <c r="C141" s="14" t="s">
-        <v>343</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>16</v>
@@ -7105,13 +7106,13 @@
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L141" s="4">
         <v>6345</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7119,10 +7120,10 @@
         <v>140</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>16</v>
@@ -7144,13 +7145,13 @@
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L142" s="4">
         <v>6345</v>
       </c>
       <c r="M142" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7158,10 +7159,10 @@
         <v>141</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>16</v>
@@ -7183,13 +7184,13 @@
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L143" s="4">
         <v>6345</v>
       </c>
       <c r="M143" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7197,10 +7198,10 @@
         <v>142</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>16</v>
@@ -7222,13 +7223,13 @@
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L144" s="4">
         <v>6345</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7236,10 +7237,10 @@
         <v>143</v>
       </c>
       <c r="B145" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>16</v>
@@ -7261,13 +7262,13 @@
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L145" s="4">
         <v>6345</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7276,7 +7277,7 @@
       </c>
       <c r="B146" s="6"/>
       <c r="C146" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>16</v>
@@ -7298,13 +7299,13 @@
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L146" s="4">
         <v>6345</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7312,10 +7313,10 @@
         <v>145</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>16</v>
@@ -7337,13 +7338,13 @@
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L147" s="4">
         <v>6345</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7351,10 +7352,10 @@
         <v>146</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>16</v>
@@ -7376,13 +7377,13 @@
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L148" s="4">
         <v>6345</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7390,10 +7391,10 @@
         <v>147</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>16</v>
@@ -7415,13 +7416,13 @@
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L149" s="4">
         <v>6345</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7429,10 +7430,10 @@
         <v>148</v>
       </c>
       <c r="B150" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>16</v>
@@ -7454,13 +7455,13 @@
       </c>
       <c r="J150" s="8"/>
       <c r="K150" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L150" s="4">
         <v>6345</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7468,10 +7469,10 @@
         <v>149</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>16</v>
@@ -7493,13 +7494,13 @@
       </c>
       <c r="J151" s="8"/>
       <c r="K151" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L151" s="4">
         <v>6347</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7507,10 +7508,10 @@
         <v>150</v>
       </c>
       <c r="B152" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>16</v>
@@ -7532,13 +7533,13 @@
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L152" s="4">
         <v>6347</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7546,10 +7547,10 @@
         <v>151</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>16</v>
@@ -7571,13 +7572,13 @@
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L153" s="4">
         <v>6347</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7585,10 +7586,10 @@
         <v>152</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>16</v>
@@ -7610,13 +7611,13 @@
       </c>
       <c r="J154" s="8"/>
       <c r="K154" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L154" s="4">
         <v>6347</v>
       </c>
       <c r="M154" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7624,10 +7625,10 @@
         <v>153</v>
       </c>
       <c r="B155" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>16</v>
@@ -7649,13 +7650,13 @@
       </c>
       <c r="J155" s="8"/>
       <c r="K155" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L155" s="4">
         <v>6347</v>
       </c>
       <c r="M155" s="9" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -7663,10 +7664,10 @@
         <v>154</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>16</v>
@@ -7684,11 +7685,11 @@
         <v>93</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J156" s="8"/>
       <c r="K156" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L156" s="4">
         <v>6348</v>
@@ -7702,10 +7703,10 @@
         <v>155</v>
       </c>
       <c r="B157" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>16</v>
@@ -7723,11 +7724,11 @@
         <v>93</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L157" s="4">
         <v>6348</v>
@@ -7741,10 +7742,10 @@
         <v>156</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>16</v>
@@ -7762,11 +7763,11 @@
         <v>93</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L158" s="4">
         <v>6348</v>
@@ -7780,10 +7781,10 @@
         <v>157</v>
       </c>
       <c r="B159" s="12" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>16</v>
@@ -7801,11 +7802,11 @@
         <v>93</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L159" s="4">
         <v>6348</v>
@@ -7819,10 +7820,10 @@
         <v>158</v>
       </c>
       <c r="B160" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>16</v>
@@ -7840,11 +7841,11 @@
         <v>93</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L160" s="4">
         <v>6348</v>
@@ -7858,10 +7859,10 @@
         <v>159</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>16</v>
@@ -7879,11 +7880,11 @@
         <v>713</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L161" s="4">
         <v>6349</v>
@@ -7897,10 +7898,10 @@
         <v>160</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>16</v>
@@ -7918,11 +7919,11 @@
         <v>713</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L162" s="4">
         <v>6349</v>
@@ -7936,10 +7937,10 @@
         <v>161</v>
       </c>
       <c r="B163" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>16</v>
@@ -7957,11 +7958,11 @@
         <v>6350</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L163" s="4">
         <v>6350</v>
@@ -7978,7 +7979,7 @@
         <v>45</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>16</v>
@@ -7996,7 +7997,7 @@
         <v>26</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J164" s="8"/>
       <c r="K164" s="4" t="s">
@@ -8006,7 +8007,7 @@
         <v>6351</v>
       </c>
       <c r="M164" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8017,7 +8018,7 @@
         <v>45</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>16</v>
@@ -8035,17 +8036,17 @@
         <v>141</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J165" s="8"/>
       <c r="K165" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L165" s="4">
         <v>6358</v>
       </c>
       <c r="M165" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8053,10 +8054,10 @@
         <v>164</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>16</v>
@@ -8074,7 +8075,7 @@
         <v>1528</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="4" t="s">
@@ -8084,7 +8085,7 @@
         <v>6359</v>
       </c>
       <c r="M166" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8092,10 +8093,10 @@
         <v>165</v>
       </c>
       <c r="B167" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>16</v>
@@ -8113,7 +8114,7 @@
         <v>1528</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="4" t="s">
@@ -8123,7 +8124,7 @@
         <v>6359</v>
       </c>
       <c r="M167" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8131,10 +8132,10 @@
         <v>166</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>16</v>
@@ -8152,17 +8153,17 @@
         <v>142</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L168" s="4">
         <v>6360</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8170,10 +8171,10 @@
         <v>167</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>16</v>
@@ -8191,17 +8192,17 @@
         <v>142</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J169" s="8"/>
       <c r="K169" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L169" s="4">
         <v>6360</v>
       </c>
       <c r="M169" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8209,10 +8210,10 @@
         <v>168</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>16</v>
@@ -8230,17 +8231,17 @@
         <v>143</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J170" s="8"/>
       <c r="K170" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="L170" s="4">
         <v>6361</v>
       </c>
       <c r="M170" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8248,10 +8249,10 @@
         <v>169</v>
       </c>
       <c r="B171" s="11" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>16</v>
@@ -8269,17 +8270,17 @@
         <v>94</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J171" s="8"/>
       <c r="K171" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L171" s="4">
         <v>6362</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8288,7 +8289,7 @@
       </c>
       <c r="B172" s="12"/>
       <c r="C172" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>16</v>
@@ -8306,17 +8307,17 @@
         <v>94</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L172" s="4">
         <v>6362</v>
       </c>
       <c r="M172" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8324,10 +8325,10 @@
         <v>171</v>
       </c>
       <c r="B173" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>16</v>
@@ -8345,17 +8346,17 @@
         <v>94</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J173" s="8"/>
       <c r="K173" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L173" s="4">
         <v>6362</v>
       </c>
       <c r="M173" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8363,10 +8364,10 @@
         <v>172</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>16</v>
@@ -8384,17 +8385,17 @@
         <v>94</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L174" s="4">
         <v>6362</v>
       </c>
       <c r="M174" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8402,10 +8403,10 @@
         <v>173</v>
       </c>
       <c r="B175" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>16</v>
@@ -8423,17 +8424,17 @@
         <v>94</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="L175" s="4">
         <v>6362</v>
       </c>
       <c r="M175" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8441,10 +8442,10 @@
         <v>174</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>16</v>
@@ -8462,17 +8463,17 @@
         <v>14057</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L176" s="4">
         <v>6363</v>
       </c>
       <c r="M176" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8480,10 +8481,10 @@
         <v>175</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>16</v>
@@ -8501,17 +8502,17 @@
         <v>14057</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L177" s="4">
         <v>6363</v>
       </c>
       <c r="M177" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8519,10 +8520,10 @@
         <v>176</v>
       </c>
       <c r="B178" s="12" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>16</v>
@@ -8540,17 +8541,17 @@
         <v>14057</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J178" s="8"/>
       <c r="K178" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L178" s="4">
         <v>6363</v>
       </c>
       <c r="M178" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8561,7 +8562,7 @@
         <v>38</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>16</v>
@@ -8579,7 +8580,7 @@
         <v>2464</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="4" t="s">
@@ -8589,7 +8590,7 @@
         <v>6364</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8600,7 +8601,7 @@
         <v>49</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>16</v>
@@ -8618,7 +8619,7 @@
         <v>2464</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="4" t="s">
@@ -8628,7 +8629,7 @@
         <v>6364</v>
       </c>
       <c r="M180" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8636,10 +8637,10 @@
         <v>179</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>16</v>
@@ -8657,7 +8658,7 @@
         <v>2464</v>
       </c>
       <c r="I181" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="4" t="s">
@@ -8667,7 +8668,7 @@
         <v>6364</v>
       </c>
       <c r="M181" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8675,10 +8676,10 @@
         <v>180</v>
       </c>
       <c r="B182" s="11" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>16</v>
@@ -8696,7 +8697,7 @@
         <v>2464</v>
       </c>
       <c r="I182" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="4" t="s">
@@ -8706,7 +8707,7 @@
         <v>6364</v>
       </c>
       <c r="M182" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8717,7 +8718,7 @@
         <v>50</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>16</v>
@@ -8735,7 +8736,7 @@
         <v>2464</v>
       </c>
       <c r="I183" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="4" t="s">
@@ -8745,7 +8746,7 @@
         <v>6364</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8756,7 +8757,7 @@
         <v>47</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>16</v>
@@ -8774,7 +8775,7 @@
         <v>2464</v>
       </c>
       <c r="I184" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="4" t="s">
@@ -8784,7 +8785,7 @@
         <v>6364</v>
       </c>
       <c r="M184" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8792,10 +8793,10 @@
         <v>183</v>
       </c>
       <c r="B185" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>16</v>
@@ -8813,7 +8814,7 @@
         <v>2464</v>
       </c>
       <c r="I185" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="4" t="s">
@@ -8823,7 +8824,7 @@
         <v>6364</v>
       </c>
       <c r="M185" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8852,7 +8853,7 @@
         <v>2464</v>
       </c>
       <c r="I186" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="4" t="s">
@@ -8862,7 +8863,7 @@
         <v>6364</v>
       </c>
       <c r="M186" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8870,10 +8871,10 @@
         <v>185</v>
       </c>
       <c r="B187" s="11" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>16</v>
@@ -8891,7 +8892,7 @@
         <v>2464</v>
       </c>
       <c r="I187" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J187" s="8"/>
       <c r="K187" s="4" t="s">
@@ -8901,7 +8902,7 @@
         <v>6364</v>
       </c>
       <c r="M187" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8912,7 +8913,7 @@
         <v>42</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>16</v>
@@ -8930,7 +8931,7 @@
         <v>2464</v>
       </c>
       <c r="I188" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="4" t="s">
@@ -8940,7 +8941,7 @@
         <v>6364</v>
       </c>
       <c r="M188" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8951,7 +8952,7 @@
         <v>43</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>16</v>
@@ -8969,7 +8970,7 @@
         <v>2464</v>
       </c>
       <c r="I189" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="4" t="s">
@@ -8979,7 +8980,7 @@
         <v>6364</v>
       </c>
       <c r="M189" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9008,7 +9009,7 @@
         <v>2464</v>
       </c>
       <c r="I190" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="4" t="s">
@@ -9018,7 +9019,7 @@
         <v>6364</v>
       </c>
       <c r="M190" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9047,7 +9048,7 @@
         <v>2464</v>
       </c>
       <c r="I191" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="4" t="s">
@@ -9057,7 +9058,7 @@
         <v>6365</v>
       </c>
       <c r="M191" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9065,10 +9066,10 @@
         <v>190</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>16</v>
@@ -9086,7 +9087,7 @@
         <v>2464</v>
       </c>
       <c r="I192" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J192" s="8"/>
       <c r="K192" s="4" t="s">
@@ -9096,7 +9097,7 @@
         <v>6365</v>
       </c>
       <c r="M192" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9104,10 +9105,10 @@
         <v>191</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>16</v>
@@ -9125,7 +9126,7 @@
         <v>2464</v>
       </c>
       <c r="I193" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J193" s="8"/>
       <c r="K193" s="4" t="s">
@@ -9135,7 +9136,7 @@
         <v>6365</v>
       </c>
       <c r="M193" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9164,7 +9165,7 @@
         <v>2464</v>
       </c>
       <c r="I194" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J194" s="8"/>
       <c r="K194" s="4" t="s">
@@ -9174,7 +9175,7 @@
         <v>6365</v>
       </c>
       <c r="M194" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="195" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>

--- a/data/transactions/أذونات الإضافة لشهر 5.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 5.xlsx
@@ -8,27 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D310A3-C7CA-4D40-86A7-F9BBF452085B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B8D029-F246-4018-BA47-4159023020F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$194</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$M$193</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="947" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="391">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -345,9 +354,6 @@
     <t>لوح SST 1.2 مط  125×250</t>
   </si>
   <si>
-    <t>لوح SST 1.5 مصنفر 125 ×2</t>
-  </si>
-  <si>
     <t>لوح SST 0.8 مصنفر 125 ×2</t>
   </si>
   <si>
@@ -369,9 +375,6 @@
     <t>11301026</t>
   </si>
   <si>
-    <t>11301030</t>
-  </si>
-  <si>
     <t>11301049</t>
   </si>
   <si>
@@ -852,18 +855,9 @@
     <t>11001001</t>
   </si>
   <si>
-    <t>لوح SST .8 مصنفر 125×2</t>
-  </si>
-  <si>
     <t>لوح SST 1.5 مط 1×2</t>
   </si>
   <si>
-    <t xml:space="preserve">لوح SST 2 مم مصنفر 125 ×250 </t>
-  </si>
-  <si>
-    <t>لوحSST 1.5 مم مصنفر 125 ×2</t>
-  </si>
-  <si>
     <t>11301012</t>
   </si>
   <si>
@@ -1041,15 +1035,6 @@
     <t>كباس 3/4 حصان R134</t>
   </si>
   <si>
-    <t>11301014</t>
-  </si>
-  <si>
-    <t>لوح 1.5 مم SST لميع مغلف 1.25 ×3 م</t>
-  </si>
-  <si>
-    <t>11301033</t>
-  </si>
-  <si>
     <t>10202014</t>
   </si>
   <si>
@@ -1186,6 +1171,45 @@
   </si>
   <si>
     <t>المصريه لتشكيل المعادن</t>
+  </si>
+  <si>
+    <t>11301022</t>
+  </si>
+  <si>
+    <t>لوح 0.8 مم SST مصنفر مغلف 1.25 ×2.5 م</t>
+  </si>
+  <si>
+    <t>لوح SST 0.8 مصنفر 1.25×2</t>
+  </si>
+  <si>
+    <t>11301048</t>
+  </si>
+  <si>
+    <t>لوح 1.8 مم SST مصنفر 125 ×250</t>
+  </si>
+  <si>
+    <t>11301080</t>
+  </si>
+  <si>
+    <t>لوح 1.8 مم SST مصنفر 125 ×200</t>
+  </si>
+  <si>
+    <t>11301045</t>
+  </si>
+  <si>
+    <t>لوح 1.5 مم SST لميع 1 × 2.5 م (430)</t>
+  </si>
+  <si>
+    <t>11301081</t>
+  </si>
+  <si>
+    <t>لوح 1.5 مم SST مصنفر مغلف 1.25 × 2 م</t>
+  </si>
+  <si>
+    <t>11301046</t>
+  </si>
+  <si>
+    <t>لوح 1.5 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1.25 × 2 م</t>
   </si>
 </sst>
 </file>
@@ -1533,16 +1557,16 @@
     <xf numFmtId="2" fontId="2" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1825,12 +1849,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M195"/>
+  <dimension ref="A1:M194"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
-    <col min="3" max="3" width="43.28515625" customWidth="1"/>
+    <col min="3" max="3" width="47.85546875" customWidth="1"/>
     <col min="4" max="4" width="8.140625" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.85546875" customWidth="1"/>
@@ -1854,7 +1878,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1871,7 +1895,7 @@
     </row>
     <row r="4" spans="1:13" s="23" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3559,32 +3583,33 @@
         <v>45</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C49" s="27" t="s">
         <v>103</v>
       </c>
       <c r="D49" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E49" s="36">
-        <v>8.5370000000000008</v>
-      </c>
-      <c r="F49" s="39">
-        <v>149122.79999999999</v>
-      </c>
-      <c r="G49" s="36">
-        <v>1273061</v>
+        <v>159</v>
+      </c>
+      <c r="E49" s="39">
+        <v>2700</v>
+      </c>
+      <c r="F49" s="41">
+        <v>149.12280699999999</v>
+      </c>
+      <c r="G49" s="39">
+        <f>F49*E49</f>
+        <v>402631.57889999996</v>
       </c>
       <c r="H49" s="28">
         <v>59830</v>
       </c>
       <c r="I49" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J49" s="29"/>
       <c r="K49" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L49" s="27">
         <v>6323</v>
@@ -3598,26 +3623,33 @@
         <v>46</v>
       </c>
       <c r="B50" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C50" s="27" t="s">
         <v>104</v>
       </c>
-      <c r="D50" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E50" s="38"/>
-      <c r="F50" s="40"/>
-      <c r="G50" s="38"/>
+      <c r="D50" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E50" s="39">
+        <v>2010</v>
+      </c>
+      <c r="F50" s="41">
+        <v>149.12280699999999</v>
+      </c>
+      <c r="G50" s="39">
+        <f t="shared" ref="G50:G53" si="0">F50*E50</f>
+        <v>299736.84207000001</v>
+      </c>
       <c r="H50" s="28">
         <v>59830</v>
       </c>
       <c r="I50" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L50" s="27">
         <v>6323</v>
@@ -3631,26 +3663,33 @@
         <v>47</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>113</v>
+        <v>389</v>
       </c>
       <c r="C51" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D51" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="38"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="38"/>
+        <v>390</v>
+      </c>
+      <c r="D51" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="39">
+        <v>1170</v>
+      </c>
+      <c r="F51" s="41">
+        <v>149.12280699999999</v>
+      </c>
+      <c r="G51" s="39">
+        <f t="shared" si="0"/>
+        <v>174473.68419</v>
+      </c>
       <c r="H51" s="28">
         <v>59830</v>
       </c>
       <c r="I51" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J51" s="29"/>
       <c r="K51" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L51" s="27">
         <v>6323</v>
@@ -3664,26 +3703,33 @@
         <v>48</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52" s="27" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52" s="38"/>
-      <c r="F52" s="40"/>
-      <c r="G52" s="38"/>
+        <v>105</v>
+      </c>
+      <c r="D52" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="39">
+        <v>1600</v>
+      </c>
+      <c r="F52" s="41">
+        <v>149.12280699999999</v>
+      </c>
+      <c r="G52" s="39">
+        <f t="shared" si="0"/>
+        <v>238596.49119999999</v>
+      </c>
       <c r="H52" s="28">
         <v>59830</v>
       </c>
       <c r="I52" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L52" s="27">
         <v>6323</v>
@@ -3697,26 +3743,33 @@
         <v>49</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C53" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="D53" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53" s="38"/>
-      <c r="F53" s="40"/>
-      <c r="G53" s="38"/>
+        <v>106</v>
+      </c>
+      <c r="D53" s="39" t="s">
+        <v>159</v>
+      </c>
+      <c r="E53" s="39">
+        <v>1000</v>
+      </c>
+      <c r="F53" s="41">
+        <v>149.12280699999999</v>
+      </c>
+      <c r="G53" s="39">
+        <f t="shared" si="0"/>
+        <v>149122.807</v>
+      </c>
       <c r="H53" s="28">
         <v>59830</v>
       </c>
       <c r="I53" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L53" s="27">
         <v>6323</v>
@@ -3726,47 +3779,53 @@
       </c>
     </row>
     <row r="54" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="25">
-        <v>50</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D54" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54" s="37"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="28">
-        <v>59830</v>
-      </c>
-      <c r="I54" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J54" s="29"/>
-      <c r="K54" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="L54" s="27">
-        <v>6323</v>
-      </c>
-      <c r="M54" s="30">
+      <c r="A54" s="1">
+        <v>51</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="4">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4">
+        <v>5500</v>
+      </c>
+      <c r="G54" s="4">
+        <v>11000</v>
+      </c>
+      <c r="H54" s="4">
+        <v>1031</v>
+      </c>
+      <c r="I54" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J54" s="8"/>
+      <c r="K54" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="L54" s="4">
+        <v>6324</v>
+      </c>
+      <c r="M54" s="9">
         <v>46117</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D55" s="4" t="s">
         <v>16</v>
@@ -3775,20 +3834,20 @@
         <v>2</v>
       </c>
       <c r="F55" s="4">
-        <v>5500</v>
+        <v>2000</v>
       </c>
       <c r="G55" s="4">
-        <v>11000</v>
+        <v>4000</v>
       </c>
       <c r="H55" s="4">
         <v>1031</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J55" s="8"/>
       <c r="K55" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L55" s="4">
         <v>6324</v>
@@ -3799,13 +3858,13 @@
     </row>
     <row r="56" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>120</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>16</v>
@@ -3814,20 +3873,20 @@
         <v>2</v>
       </c>
       <c r="F56" s="4">
+        <v>1000</v>
+      </c>
+      <c r="G56" s="4">
         <v>2000</v>
-      </c>
-      <c r="G56" s="4">
-        <v>4000</v>
       </c>
       <c r="H56" s="4">
         <v>1031</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="J56" s="8"/>
       <c r="K56" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="L56" s="4">
         <v>6324</v>
@@ -3837,75 +3896,77 @@
       </c>
     </row>
     <row r="57" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="1">
-        <v>53</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" s="4">
-        <v>2</v>
-      </c>
-      <c r="F57" s="4">
-        <v>1000</v>
-      </c>
-      <c r="G57" s="4">
-        <v>2000</v>
-      </c>
-      <c r="H57" s="4">
-        <v>1031</v>
-      </c>
-      <c r="I57" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="J57" s="8"/>
-      <c r="K57" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="L57" s="4">
-        <v>6324</v>
-      </c>
-      <c r="M57" s="9">
+      <c r="A57" s="25">
+        <v>55</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" s="27">
+        <v>3560</v>
+      </c>
+      <c r="F57" s="41">
+        <v>157.89473000000001</v>
+      </c>
+      <c r="G57" s="40">
+        <f>F57*E57</f>
+        <v>562105.23880000005</v>
+      </c>
+      <c r="H57" s="27">
+        <v>59837</v>
+      </c>
+      <c r="I57" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="J57" s="29"/>
+      <c r="K57" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="L57" s="27">
+        <v>6325</v>
+      </c>
+      <c r="M57" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="E58" s="27">
-        <v>70</v>
-      </c>
-      <c r="F58" s="39">
-        <v>157894.73000000001</v>
-      </c>
-      <c r="G58" s="36">
-        <v>913894.73</v>
+        <v>941</v>
+      </c>
+      <c r="F58" s="41">
+        <v>157.89473000000001</v>
+      </c>
+      <c r="G58" s="40">
+        <f t="shared" ref="G58:G59" si="1">F58*E58</f>
+        <v>148578.94093000001</v>
       </c>
       <c r="H58" s="27">
         <v>59837</v>
       </c>
       <c r="I58" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J58" s="29"/>
       <c r="K58" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L58" s="27">
         <v>6325</v>
@@ -3916,31 +3977,36 @@
     </row>
     <row r="59" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="C59" s="27" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="E59" s="27">
-        <v>95</v>
-      </c>
-      <c r="F59" s="40"/>
-      <c r="G59" s="38"/>
+        <v>1232</v>
+      </c>
+      <c r="F59" s="41">
+        <v>157.89473000000001</v>
+      </c>
+      <c r="G59" s="40">
+        <f t="shared" si="1"/>
+        <v>194526.30736000001</v>
+      </c>
       <c r="H59" s="27">
         <v>59837</v>
       </c>
       <c r="I59" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J59" s="29"/>
       <c r="K59" s="27" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L59" s="27">
         <v>6325</v>
@@ -3950,109 +4016,117 @@
       </c>
     </row>
     <row r="60" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="25">
-        <v>56</v>
-      </c>
-      <c r="B60" s="26" t="s">
+      <c r="A60" s="1">
+        <v>58</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C60" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="C60" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E60" s="27">
-        <v>88</v>
-      </c>
-      <c r="F60" s="40"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="27">
-        <v>59837</v>
-      </c>
-      <c r="I60" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J60" s="29"/>
-      <c r="K60" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="L60" s="27">
-        <v>6325</v>
-      </c>
-      <c r="M60" s="30">
+      <c r="D60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E60" s="4">
+        <v>50</v>
+      </c>
+      <c r="F60" s="4">
+        <v>811</v>
+      </c>
+      <c r="G60" s="4">
+        <v>40570</v>
+      </c>
+      <c r="H60" s="4">
+        <v>711</v>
+      </c>
+      <c r="I60" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J60" s="8"/>
+      <c r="K60" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L60" s="4">
+        <v>6326</v>
+      </c>
+      <c r="M60" s="9">
         <v>46117</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="25">
-        <v>57</v>
-      </c>
-      <c r="B61" s="26" t="s">
+      <c r="A61" s="1">
+        <v>59</v>
+      </c>
+      <c r="B61" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C61" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C61" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="E61" s="27">
-        <v>80</v>
-      </c>
-      <c r="F61" s="41"/>
-      <c r="G61" s="37"/>
-      <c r="H61" s="27">
-        <v>59837</v>
-      </c>
-      <c r="I61" s="30" t="s">
-        <v>109</v>
-      </c>
-      <c r="J61" s="29"/>
-      <c r="K61" s="27" t="s">
-        <v>385</v>
-      </c>
-      <c r="L61" s="27">
-        <v>6325</v>
-      </c>
-      <c r="M61" s="30">
+      <c r="D61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E61" s="4">
+        <v>50</v>
+      </c>
+      <c r="F61" s="4">
+        <v>622</v>
+      </c>
+      <c r="G61" s="4">
+        <v>31140</v>
+      </c>
+      <c r="H61" s="4">
+        <v>711</v>
+      </c>
+      <c r="I61" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="J61" s="8"/>
+      <c r="K61" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="L61" s="4">
+        <v>6326</v>
+      </c>
+      <c r="M61" s="9">
         <v>46117</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B62" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="D62" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E62" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F62" s="4">
-        <v>811</v>
+        <v>125</v>
       </c>
       <c r="G62" s="4">
-        <v>40570</v>
+        <v>625</v>
       </c>
       <c r="H62" s="4">
-        <v>711</v>
+        <v>4905</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J62" s="8"/>
       <c r="K62" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L62" s="4">
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="M62" s="9">
         <v>46117</v>
@@ -4060,38 +4134,38 @@
     </row>
     <row r="63" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E63" s="4">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="F63" s="4">
-        <v>622</v>
+        <v>190</v>
       </c>
       <c r="G63" s="4">
-        <v>31140</v>
+        <v>950</v>
       </c>
       <c r="H63" s="4">
-        <v>711</v>
+        <v>4905</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J63" s="8"/>
       <c r="K63" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L63" s="4">
-        <v>6326</v>
+        <v>6327</v>
       </c>
       <c r="M63" s="9">
         <v>46117</v>
@@ -4099,35 +4173,35 @@
     </row>
     <row r="64" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E64" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F64" s="4">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="G64" s="4">
-        <v>625</v>
+        <v>1500</v>
       </c>
       <c r="H64" s="4">
         <v>4905</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J64" s="8"/>
       <c r="K64" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L64" s="4">
         <v>6327</v>
@@ -4138,13 +4212,13 @@
     </row>
     <row r="65" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>16</v>
@@ -4153,20 +4227,20 @@
         <v>5</v>
       </c>
       <c r="F65" s="4">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="G65" s="4">
-        <v>950</v>
+        <v>725</v>
       </c>
       <c r="H65" s="4">
         <v>4905</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J65" s="8"/>
       <c r="K65" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L65" s="4">
         <v>6327</v>
@@ -4177,35 +4251,35 @@
     </row>
     <row r="66" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
-        <v>62</v>
-      </c>
-      <c r="B66" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="D66" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E66" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F66" s="4">
-        <v>30</v>
+        <v>1950</v>
       </c>
       <c r="G66" s="4">
-        <v>1500</v>
+        <v>1950</v>
       </c>
       <c r="H66" s="4">
         <v>4905</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J66" s="8"/>
       <c r="K66" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L66" s="4">
         <v>6327</v>
@@ -4216,35 +4290,35 @@
     </row>
     <row r="67" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E67" s="4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F67" s="4">
-        <v>145</v>
+        <v>110</v>
       </c>
       <c r="G67" s="4">
-        <v>725</v>
+        <v>3300</v>
       </c>
       <c r="H67" s="4">
         <v>4905</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J67" s="8"/>
       <c r="K67" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L67" s="4">
         <v>6327</v>
@@ -4255,35 +4329,35 @@
     </row>
     <row r="68" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
-        <v>64</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>151</v>
+        <v>66</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>144</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E68" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F68" s="4">
-        <v>1950</v>
+        <v>135</v>
       </c>
       <c r="G68" s="4">
-        <v>1950</v>
+        <v>675</v>
       </c>
       <c r="H68" s="4">
         <v>4905</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J68" s="8"/>
       <c r="K68" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L68" s="4">
         <v>6327</v>
@@ -4294,10 +4368,10 @@
     </row>
     <row r="69" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B69" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>138</v>
@@ -4306,23 +4380,23 @@
         <v>16</v>
       </c>
       <c r="E69" s="4">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F69" s="4">
         <v>110</v>
       </c>
       <c r="G69" s="4">
-        <v>3300</v>
+        <v>550</v>
       </c>
       <c r="H69" s="4">
         <v>4905</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J69" s="8"/>
       <c r="K69" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L69" s="4">
         <v>6327</v>
@@ -4333,7 +4407,7 @@
     </row>
     <row r="70" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>146</v>
@@ -4348,20 +4422,20 @@
         <v>5</v>
       </c>
       <c r="F70" s="4">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="G70" s="4">
-        <v>675</v>
+        <v>775</v>
       </c>
       <c r="H70" s="4">
         <v>4905</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J70" s="8"/>
       <c r="K70" s="4" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="L70" s="4">
         <v>6327</v>
@@ -4372,38 +4446,38 @@
     </row>
     <row r="71" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B71" s="12" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E71" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F71" s="4">
-        <v>110</v>
+        <v>750</v>
       </c>
       <c r="G71" s="4">
-        <v>550</v>
+        <v>1500</v>
       </c>
       <c r="H71" s="4">
-        <v>4905</v>
+        <v>34453</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J71" s="8"/>
       <c r="K71" s="4" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="L71" s="4">
-        <v>6327</v>
+        <v>6328</v>
       </c>
       <c r="M71" s="9">
         <v>46117</v>
@@ -4411,38 +4485,38 @@
     </row>
     <row r="72" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B72" s="12" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E72" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F72" s="4">
         <v>155</v>
       </c>
       <c r="G72" s="4">
-        <v>775</v>
+        <v>310</v>
       </c>
       <c r="H72" s="4">
-        <v>4905</v>
+        <v>34453</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J72" s="8"/>
       <c r="K72" s="4" t="s">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="L72" s="4">
-        <v>6327</v>
+        <v>6328</v>
       </c>
       <c r="M72" s="9">
         <v>46117</v>
@@ -4450,7 +4524,7 @@
     </row>
     <row r="73" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>156</v>
@@ -4465,20 +4539,20 @@
         <v>2</v>
       </c>
       <c r="F73" s="4">
-        <v>750</v>
+        <v>165</v>
       </c>
       <c r="G73" s="4">
-        <v>1500</v>
+        <v>330</v>
       </c>
       <c r="H73" s="4">
         <v>34453</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J73" s="8"/>
       <c r="K73" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L73" s="4">
         <v>6328</v>
@@ -4489,10 +4563,10 @@
     </row>
     <row r="74" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B74" s="12" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C74" s="4" t="s">
         <v>153</v>
@@ -4501,23 +4575,23 @@
         <v>16</v>
       </c>
       <c r="E74" s="4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F74" s="4">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="G74" s="4">
-        <v>310</v>
+        <v>1275</v>
       </c>
       <c r="H74" s="4">
         <v>34453</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J74" s="8"/>
       <c r="K74" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L74" s="4">
         <v>6328</v>
@@ -4528,38 +4602,38 @@
     </row>
     <row r="75" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B75" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="D75" s="4" t="s">
-        <v>16</v>
+        <v>159</v>
       </c>
       <c r="E75" s="4">
-        <v>2</v>
+        <v>45.5</v>
       </c>
       <c r="F75" s="4">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="G75" s="4">
-        <v>330</v>
+        <v>5681.25</v>
       </c>
       <c r="H75" s="4">
-        <v>34453</v>
+        <v>13993</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J75" s="8"/>
       <c r="K75" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="L75" s="4">
-        <v>6328</v>
+        <v>6329</v>
       </c>
       <c r="M75" s="9">
         <v>46117</v>
@@ -4567,38 +4641,38 @@
     </row>
     <row r="76" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
-        <v>73</v>
-      </c>
-      <c r="B76" s="12" t="s">
-        <v>157</v>
+        <v>75</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>171</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E76" s="4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F76" s="4">
-        <v>85</v>
+        <v>725</v>
       </c>
       <c r="G76" s="4">
-        <v>1275</v>
+        <v>14500</v>
       </c>
       <c r="H76" s="4">
-        <v>34453</v>
+        <v>5287</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J76" s="8"/>
       <c r="K76" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L76" s="4">
-        <v>6328</v>
+        <v>6330</v>
       </c>
       <c r="M76" s="9">
         <v>46117</v>
@@ -4606,38 +4680,38 @@
     </row>
     <row r="77" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B77" s="12" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
       <c r="E77" s="4">
-        <v>45.5</v>
+        <v>200</v>
       </c>
       <c r="F77" s="4">
-        <v>125</v>
+        <v>17.5</v>
       </c>
       <c r="G77" s="4">
-        <v>5681.25</v>
+        <v>3500</v>
       </c>
       <c r="H77" s="4">
-        <v>13993</v>
+        <v>6525</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="J77" s="8"/>
       <c r="K77" s="4" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L77" s="4">
-        <v>6329</v>
+        <v>6331</v>
       </c>
       <c r="M77" s="9">
         <v>46117</v>
@@ -4645,38 +4719,38 @@
     </row>
     <row r="78" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
-        <v>75</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>173</v>
+        <v>77</v>
+      </c>
+      <c r="B78" s="12" t="s">
+        <v>170</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D78" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E78" s="4">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="F78" s="4">
-        <v>725</v>
+        <v>140</v>
       </c>
       <c r="G78" s="4">
-        <v>14500</v>
+        <v>28000</v>
       </c>
       <c r="H78" s="4">
-        <v>5287</v>
+        <v>6525</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>109</v>
+        <v>165</v>
       </c>
       <c r="J78" s="8"/>
       <c r="K78" s="4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="L78" s="4">
-        <v>6330</v>
+        <v>6331</v>
       </c>
       <c r="M78" s="9">
         <v>46117</v>
@@ -4684,38 +4758,38 @@
     </row>
     <row r="79" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C79" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="4">
+        <v>100</v>
+      </c>
+      <c r="F79" s="4">
+        <v>60</v>
+      </c>
+      <c r="G79" s="4">
+        <v>6000</v>
+      </c>
+      <c r="H79" s="4">
+        <v>6526</v>
+      </c>
+      <c r="I79" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E79" s="4">
-        <v>200</v>
-      </c>
-      <c r="F79" s="4">
-        <v>17.5</v>
-      </c>
-      <c r="G79" s="4">
-        <v>3500</v>
-      </c>
-      <c r="H79" s="4">
-        <v>6525</v>
-      </c>
-      <c r="I79" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="J79" s="8"/>
       <c r="K79" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L79" s="4">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="M79" s="9">
         <v>46117</v>
@@ -4723,13 +4797,13 @@
     </row>
     <row r="80" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>16</v>
@@ -4738,23 +4812,23 @@
         <v>200</v>
       </c>
       <c r="F80" s="4">
-        <v>140</v>
+        <v>17.5</v>
       </c>
       <c r="G80" s="4">
-        <v>28000</v>
+        <v>3500</v>
       </c>
       <c r="H80" s="4">
-        <v>6525</v>
+        <v>6526</v>
       </c>
       <c r="I80" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L80" s="4">
-        <v>6331</v>
+        <v>6332</v>
       </c>
       <c r="M80" s="9">
         <v>46117</v>
@@ -4762,35 +4836,35 @@
     </row>
     <row r="81" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B81" s="12" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E81" s="4">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F81" s="4">
-        <v>60</v>
+        <v>140</v>
       </c>
       <c r="G81" s="4">
-        <v>6000</v>
+        <v>12320</v>
       </c>
       <c r="H81" s="4">
         <v>6526</v>
       </c>
       <c r="I81" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J81" s="8"/>
       <c r="K81" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="L81" s="4">
         <v>6332</v>
@@ -4801,38 +4875,38 @@
     </row>
     <row r="82" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
-        <v>79</v>
-      </c>
-      <c r="B82" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="C82" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E82" s="4">
+        <v>10</v>
+      </c>
+      <c r="F82" s="4">
+        <v>550</v>
+      </c>
+      <c r="G82" s="4">
+        <v>5500</v>
+      </c>
+      <c r="H82" s="4">
+        <v>929</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E82" s="4">
-        <v>200</v>
-      </c>
-      <c r="F82" s="4">
-        <v>17.5</v>
-      </c>
-      <c r="G82" s="4">
-        <v>3500</v>
-      </c>
-      <c r="H82" s="4">
-        <v>6526</v>
-      </c>
-      <c r="I82" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="4" t="s">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="L82" s="4">
-        <v>6332</v>
+        <v>6333</v>
       </c>
       <c r="M82" s="9">
         <v>46117</v>
@@ -4840,38 +4914,38 @@
     </row>
     <row r="83" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
-        <v>80</v>
-      </c>
-      <c r="B83" s="12" t="s">
-        <v>172</v>
+        <v>82</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>183</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E83" s="4">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="F83" s="4">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="G83" s="4">
-        <v>12320</v>
+        <v>24000</v>
       </c>
       <c r="H83" s="4">
-        <v>6526</v>
+        <v>929</v>
       </c>
       <c r="I83" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="4" t="s">
-        <v>168</v>
+        <v>376</v>
       </c>
       <c r="L83" s="4">
-        <v>6332</v>
+        <v>6333</v>
       </c>
       <c r="M83" s="9">
         <v>46117</v>
@@ -4879,35 +4953,35 @@
     </row>
     <row r="84" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>203</v>
+        <v>185</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>184</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E84" s="4">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="F84" s="4">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="G84" s="4">
-        <v>5500</v>
+        <v>3000</v>
       </c>
       <c r="H84" s="4">
         <v>929</v>
       </c>
       <c r="I84" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L84" s="4">
         <v>6333</v>
@@ -4918,35 +4992,35 @@
     </row>
     <row r="85" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E85" s="4">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="F85" s="4">
-        <v>1000</v>
+        <v>2300</v>
       </c>
       <c r="G85" s="4">
-        <v>24000</v>
+        <v>2300</v>
       </c>
       <c r="H85" s="4">
         <v>929</v>
       </c>
       <c r="I85" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L85" s="4">
         <v>6333</v>
@@ -4957,35 +5031,35 @@
     </row>
     <row r="86" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>187</v>
+        <v>119</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>186</v>
+        <v>113</v>
       </c>
       <c r="D86" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E86" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="F86" s="4">
-        <v>60</v>
+        <v>5500</v>
       </c>
       <c r="G86" s="4">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="H86" s="4">
         <v>929</v>
       </c>
       <c r="I86" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L86" s="4">
         <v>6333</v>
@@ -4996,35 +5070,35 @@
     </row>
     <row r="87" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E87" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" s="4">
-        <v>2300</v>
+        <v>2500</v>
       </c>
       <c r="G87" s="4">
-        <v>2300</v>
+        <v>5000</v>
       </c>
       <c r="H87" s="4">
         <v>929</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L87" s="4">
         <v>6333</v>
@@ -5035,13 +5109,13 @@
     </row>
     <row r="88" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D88" s="4" t="s">
         <v>16</v>
@@ -5050,20 +5124,20 @@
         <v>2</v>
       </c>
       <c r="F88" s="4">
-        <v>5500</v>
+        <v>1500</v>
       </c>
       <c r="G88" s="4">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="H88" s="4">
         <v>929</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L88" s="4">
         <v>6333</v>
@@ -5074,35 +5148,35 @@
     </row>
     <row r="89" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D89" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E89" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" s="4">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="G89" s="4">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="H89" s="4">
         <v>929</v>
       </c>
       <c r="I89" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L89" s="4">
         <v>6333</v>
@@ -5113,22 +5187,22 @@
     </row>
     <row r="90" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="D90" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E90" s="4">
-        <v>2</v>
+        <v>3300</v>
       </c>
       <c r="F90" s="4">
-        <v>1500</v>
+        <v>10</v>
       </c>
       <c r="G90" s="4">
         <v>3000</v>
@@ -5137,11 +5211,11 @@
         <v>929</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L90" s="4">
         <v>6333</v>
@@ -5152,10 +5226,10 @@
     </row>
     <row r="91" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C91" s="4" t="s">
         <v>178</v>
@@ -5164,23 +5238,23 @@
         <v>16</v>
       </c>
       <c r="E91" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F91" s="4">
-        <v>1500</v>
+        <v>350</v>
       </c>
       <c r="G91" s="4">
-        <v>1500</v>
+        <v>17500</v>
       </c>
       <c r="H91" s="4">
         <v>929</v>
       </c>
       <c r="I91" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L91" s="4">
         <v>6333</v>
@@ -5191,7 +5265,7 @@
     </row>
     <row r="92" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>192</v>
@@ -5203,23 +5277,23 @@
         <v>16</v>
       </c>
       <c r="E92" s="4">
-        <v>3300</v>
+        <v>5</v>
       </c>
       <c r="F92" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G92" s="4">
-        <v>3000</v>
+        <v>500</v>
       </c>
       <c r="H92" s="4">
         <v>929</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L92" s="4">
         <v>6333</v>
@@ -5230,7 +5304,7 @@
     </row>
     <row r="93" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>193</v>
@@ -5245,20 +5319,20 @@
         <v>5</v>
       </c>
       <c r="F93" s="4">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="G93" s="4">
-        <v>17500</v>
+        <v>500</v>
       </c>
       <c r="H93" s="4">
         <v>929</v>
       </c>
       <c r="I93" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L93" s="4">
         <v>6333</v>
@@ -5269,10 +5343,10 @@
     </row>
     <row r="94" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C94" s="4" t="s">
         <v>181</v>
@@ -5281,23 +5355,23 @@
         <v>16</v>
       </c>
       <c r="E94" s="4">
-        <v>5</v>
-      </c>
-      <c r="F94" s="4">
-        <v>100</v>
+        <v>1</v>
+      </c>
+      <c r="F94" s="16">
+        <v>25100</v>
       </c>
       <c r="G94" s="4">
-        <v>500</v>
+        <v>25100</v>
       </c>
       <c r="H94" s="4">
         <v>929</v>
       </c>
       <c r="I94" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L94" s="4">
         <v>6333</v>
@@ -5308,10 +5382,10 @@
     </row>
     <row r="95" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C95" s="4" t="s">
         <v>182</v>
@@ -5320,23 +5394,23 @@
         <v>16</v>
       </c>
       <c r="E95" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F95" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G95" s="4">
-        <v>500</v>
+        <v>1500</v>
       </c>
       <c r="H95" s="4">
         <v>929</v>
       </c>
       <c r="I95" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L95" s="4">
         <v>6333</v>
@@ -5347,13 +5421,13 @@
     </row>
     <row r="96" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="D96" s="4" t="s">
         <v>16</v>
@@ -5361,24 +5435,24 @@
       <c r="E96" s="4">
         <v>1</v>
       </c>
-      <c r="F96" s="16">
-        <v>25100</v>
+      <c r="F96" s="4">
+        <v>3200</v>
       </c>
       <c r="G96" s="4">
-        <v>25100</v>
+        <v>3200</v>
       </c>
       <c r="H96" s="4">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I96" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L96" s="4">
-        <v>6333</v>
+        <v>6335</v>
       </c>
       <c r="M96" s="9">
         <v>46117</v>
@@ -5386,13 +5460,13 @@
     </row>
     <row r="97" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="D97" s="4" t="s">
         <v>16</v>
@@ -5401,23 +5475,23 @@
         <v>10</v>
       </c>
       <c r="F97" s="4">
-        <v>150</v>
+        <v>2500</v>
       </c>
       <c r="G97" s="4">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="H97" s="4">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="I97" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L97" s="4">
-        <v>6333</v>
+        <v>6335</v>
       </c>
       <c r="M97" s="9">
         <v>46117</v>
@@ -5425,35 +5499,35 @@
     </row>
     <row r="98" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E98" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F98" s="4">
-        <v>3200</v>
+        <v>6500</v>
       </c>
       <c r="G98" s="4">
-        <v>3200</v>
+        <v>3900</v>
       </c>
       <c r="H98" s="4">
         <v>928</v>
       </c>
       <c r="I98" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L98" s="4">
         <v>6335</v>
@@ -5464,10 +5538,10 @@
     </row>
     <row r="99" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C99" s="4" t="s">
         <v>197</v>
@@ -5476,23 +5550,23 @@
         <v>16</v>
       </c>
       <c r="E99" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F99" s="4">
         <v>2500</v>
       </c>
       <c r="G99" s="4">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="H99" s="4">
         <v>928</v>
       </c>
       <c r="I99" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L99" s="4">
         <v>6335</v>
@@ -5503,35 +5577,35 @@
     </row>
     <row r="100" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>198</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E100" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F100" s="4">
-        <v>6500</v>
+        <v>1450</v>
       </c>
       <c r="G100" s="4">
-        <v>3900</v>
+        <v>2900</v>
       </c>
       <c r="H100" s="4">
         <v>928</v>
       </c>
       <c r="I100" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L100" s="4">
         <v>6335</v>
@@ -5542,10 +5616,10 @@
     </row>
     <row r="101" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C101" s="4" t="s">
         <v>199</v>
@@ -5554,23 +5628,23 @@
         <v>16</v>
       </c>
       <c r="E101" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="F101" s="4">
         <v>2500</v>
       </c>
       <c r="G101" s="4">
-        <v>5000</v>
+        <v>22500</v>
       </c>
       <c r="H101" s="4">
         <v>928</v>
       </c>
       <c r="I101" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L101" s="4">
         <v>6335</v>
@@ -5581,35 +5655,35 @@
     </row>
     <row r="102" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="C102" s="4" t="s">
         <v>200</v>
       </c>
+      <c r="C102" s="15" t="s">
+        <v>201</v>
+      </c>
       <c r="D102" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E102" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F102" s="4">
-        <v>1450</v>
+        <v>550</v>
       </c>
       <c r="G102" s="4">
-        <v>2900</v>
+        <v>3300</v>
       </c>
       <c r="H102" s="4">
         <v>928</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L102" s="4">
         <v>6335</v>
@@ -5620,22 +5694,22 @@
     </row>
     <row r="103" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E103" s="4">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F103" s="4">
-        <v>2500</v>
+        <v>450</v>
       </c>
       <c r="G103" s="4">
         <v>22500</v>
@@ -5644,11 +5718,11 @@
         <v>928</v>
       </c>
       <c r="I103" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L103" s="4">
         <v>6335</v>
@@ -5659,35 +5733,35 @@
     </row>
     <row r="104" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>202</v>
-      </c>
-      <c r="C104" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" s="4" t="s">
         <v>203</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E104" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F104" s="4">
-        <v>550</v>
+        <v>8100</v>
       </c>
       <c r="G104" s="4">
-        <v>3300</v>
+        <v>8100</v>
       </c>
       <c r="H104" s="4">
         <v>928</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L104" s="4">
         <v>6335</v>
@@ -5698,7 +5772,7 @@
     </row>
     <row r="105" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>209</v>
@@ -5707,26 +5781,26 @@
         <v>204</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E105" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F105" s="4">
-        <v>450</v>
+        <v>4250</v>
       </c>
       <c r="G105" s="4">
-        <v>22500</v>
+        <v>4250</v>
       </c>
       <c r="H105" s="4">
         <v>928</v>
       </c>
       <c r="I105" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J105" s="8"/>
       <c r="K105" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L105" s="4">
         <v>6335</v>
@@ -5737,35 +5811,35 @@
     </row>
     <row r="106" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="C106" s="4" t="s">
         <v>205</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E106" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F106" s="4">
-        <v>8100</v>
+        <v>300</v>
       </c>
       <c r="G106" s="4">
-        <v>8100</v>
+        <v>15000</v>
       </c>
       <c r="H106" s="4">
         <v>928</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J106" s="8"/>
       <c r="K106" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="L106" s="4">
         <v>6335</v>
@@ -5776,38 +5850,38 @@
     </row>
     <row r="107" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
-        <v>104</v>
-      </c>
-      <c r="B107" s="11" t="s">
-        <v>211</v>
+        <v>106</v>
+      </c>
+      <c r="B107" s="12" t="s">
+        <v>225</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>16</v>
+        <v>134</v>
       </c>
       <c r="E107" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F107" s="4">
-        <v>4250</v>
+        <v>55</v>
       </c>
       <c r="G107" s="4">
-        <v>4250</v>
+        <v>2750</v>
       </c>
       <c r="H107" s="4">
-        <v>928</v>
+        <v>81</v>
       </c>
       <c r="I107" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J107" s="8"/>
       <c r="K107" s="4" t="s">
-        <v>384</v>
+        <v>226</v>
       </c>
       <c r="L107" s="4">
-        <v>6335</v>
+        <v>6336</v>
       </c>
       <c r="M107" s="9">
         <v>46117</v>
@@ -5815,38 +5889,38 @@
     </row>
     <row r="108" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
-        <v>105</v>
-      </c>
-      <c r="B108" s="11" t="s">
-        <v>191</v>
+        <v>107</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>223</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E108" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F108" s="4">
-        <v>300</v>
+        <v>55</v>
       </c>
       <c r="G108" s="4">
-        <v>15000</v>
+        <v>550</v>
       </c>
       <c r="H108" s="4">
-        <v>928</v>
+        <v>81</v>
       </c>
       <c r="I108" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J108" s="8"/>
       <c r="K108" s="4" t="s">
-        <v>384</v>
+        <v>226</v>
       </c>
       <c r="L108" s="4">
-        <v>6335</v>
+        <v>6336</v>
       </c>
       <c r="M108" s="9">
         <v>46117</v>
@@ -5854,35 +5928,35 @@
     </row>
     <row r="109" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B109" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C109" s="4" t="s">
         <v>216</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>136</v>
+        <v>16</v>
       </c>
       <c r="E109" s="4">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F109" s="4">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="G109" s="4">
-        <v>2750</v>
+        <v>700</v>
       </c>
       <c r="H109" s="4">
         <v>81</v>
       </c>
       <c r="I109" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J109" s="8"/>
       <c r="K109" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L109" s="4">
         <v>6336</v>
@@ -5893,10 +5967,10 @@
     </row>
     <row r="110" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B110" s="12" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>217</v>
@@ -5905,23 +5979,23 @@
         <v>16</v>
       </c>
       <c r="E110" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F110" s="4">
-        <v>55</v>
+        <v>175</v>
       </c>
       <c r="G110" s="4">
-        <v>550</v>
+        <v>175</v>
       </c>
       <c r="H110" s="4">
         <v>81</v>
       </c>
       <c r="I110" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J110" s="8"/>
       <c r="K110" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L110" s="4">
         <v>6336</v>
@@ -5932,10 +6006,10 @@
     </row>
     <row r="111" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
-        <v>108</v>
-      </c>
-      <c r="B111" s="12" t="s">
-        <v>226</v>
+        <v>110</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>220</v>
       </c>
       <c r="C111" s="4" t="s">
         <v>218</v>
@@ -5944,23 +6018,23 @@
         <v>16</v>
       </c>
       <c r="E111" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F111" s="4">
-        <v>70</v>
+        <v>250</v>
       </c>
       <c r="G111" s="4">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="H111" s="4">
         <v>81</v>
       </c>
       <c r="I111" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J111" s="8"/>
       <c r="K111" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L111" s="4">
         <v>6336</v>
@@ -5971,10 +6045,10 @@
     </row>
     <row r="112" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
-        <v>109</v>
-      </c>
-      <c r="B112" s="12" t="s">
-        <v>224</v>
+        <v>111</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>221</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>219</v>
@@ -5983,23 +6057,23 @@
         <v>16</v>
       </c>
       <c r="E112" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" s="4">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="G112" s="4">
-        <v>175</v>
+        <v>400</v>
       </c>
       <c r="H112" s="4">
         <v>81</v>
       </c>
       <c r="I112" s="9" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J112" s="8"/>
       <c r="K112" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L112" s="4">
         <v>6336</v>
@@ -6010,88 +6084,88 @@
     </row>
     <row r="113" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
-        <v>110</v>
-      </c>
-      <c r="B113" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="C113" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="D113" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E113" s="4">
-        <v>2</v>
-      </c>
-      <c r="F113" s="4">
-        <v>250</v>
-      </c>
-      <c r="G113" s="4">
-        <v>500</v>
-      </c>
-      <c r="H113" s="4">
-        <v>81</v>
-      </c>
-      <c r="I113" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J113" s="8"/>
-      <c r="K113" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B113" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C113" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="L113" s="4">
-        <v>6336</v>
-      </c>
-      <c r="M113" s="9">
+      <c r="D113" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E113" s="17">
+        <v>1</v>
+      </c>
+      <c r="F113" s="17">
+        <v>1429</v>
+      </c>
+      <c r="G113" s="17">
+        <v>1429</v>
+      </c>
+      <c r="H113" s="17">
+        <v>1755</v>
+      </c>
+      <c r="I113" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J113" s="19"/>
+      <c r="K113" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="L113" s="17">
+        <v>6337</v>
+      </c>
+      <c r="M113" s="18">
         <v>46117</v>
       </c>
     </row>
     <row r="114" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
-        <v>111</v>
-      </c>
-      <c r="B114" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E114" s="4">
-        <v>2</v>
-      </c>
-      <c r="F114" s="4">
-        <v>200</v>
-      </c>
-      <c r="G114" s="4">
-        <v>400</v>
-      </c>
-      <c r="H114" s="4">
-        <v>81</v>
-      </c>
-      <c r="I114" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="J114" s="8"/>
-      <c r="K114" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L114" s="4">
-        <v>6336</v>
-      </c>
-      <c r="M114" s="9">
+        <v>114</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="D114" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E114" s="17">
+        <v>1</v>
+      </c>
+      <c r="F114" s="17">
+        <v>3591</v>
+      </c>
+      <c r="G114" s="17">
+        <v>3591</v>
+      </c>
+      <c r="H114" s="17">
+        <v>1755</v>
+      </c>
+      <c r="I114" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="J114" s="19"/>
+      <c r="K114" s="17" t="s">
+        <v>227</v>
+      </c>
+      <c r="L114" s="17">
+        <v>6337</v>
+      </c>
+      <c r="M114" s="18">
         <v>46117</v>
       </c>
     </row>
     <row r="115" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>230</v>
@@ -6100,23 +6174,23 @@
         <v>16</v>
       </c>
       <c r="E115" s="17">
-        <v>1</v>
-      </c>
-      <c r="F115" s="17">
-        <v>1429</v>
+        <v>2</v>
+      </c>
+      <c r="F115" s="20">
+        <v>12373</v>
       </c>
       <c r="G115" s="17">
-        <v>1429</v>
+        <v>24746</v>
       </c>
       <c r="H115" s="17">
         <v>1755</v>
       </c>
       <c r="I115" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J115" s="19"/>
       <c r="K115" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L115" s="17">
         <v>6337</v>
@@ -6127,10 +6201,10 @@
     </row>
     <row r="116" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C116" s="17" t="s">
         <v>231</v>
@@ -6142,20 +6216,20 @@
         <v>1</v>
       </c>
       <c r="F116" s="17">
-        <v>3591</v>
+        <v>856</v>
       </c>
       <c r="G116" s="17">
-        <v>3591</v>
+        <v>856</v>
       </c>
       <c r="H116" s="17">
         <v>1755</v>
       </c>
       <c r="I116" s="18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J116" s="19"/>
       <c r="K116" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L116" s="17">
         <v>6337</v>
@@ -6166,113 +6240,113 @@
     </row>
     <row r="117" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="C117" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D117" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E117" s="17">
-        <v>2</v>
-      </c>
-      <c r="F117" s="20">
-        <v>12373</v>
-      </c>
-      <c r="G117" s="17">
-        <v>24746</v>
-      </c>
-      <c r="H117" s="17">
-        <v>1755</v>
-      </c>
-      <c r="I117" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="J117" s="19"/>
-      <c r="K117" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="L117" s="17">
-        <v>6337</v>
-      </c>
-      <c r="M117" s="18">
+      <c r="D117" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E117" s="4">
+        <v>10</v>
+      </c>
+      <c r="F117" s="4">
+        <v>140.5</v>
+      </c>
+      <c r="G117" s="4">
+        <v>1405</v>
+      </c>
+      <c r="H117" s="4">
+        <v>85</v>
+      </c>
+      <c r="I117" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J117" s="8"/>
+      <c r="K117" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L117" s="4">
+        <v>6339</v>
+      </c>
+      <c r="M117" s="9">
         <v>46117</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
-        <v>116</v>
-      </c>
-      <c r="B118" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="B118" s="11" t="s">
         <v>259</v>
       </c>
-      <c r="C118" s="17" t="s">
+      <c r="C118" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E118" s="4">
+        <v>15</v>
+      </c>
+      <c r="F118" s="4">
+        <v>205</v>
+      </c>
+      <c r="G118" s="4">
+        <v>3075</v>
+      </c>
+      <c r="H118" s="4">
+        <v>85</v>
+      </c>
+      <c r="I118" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="D118" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E118" s="17">
-        <v>1</v>
-      </c>
-      <c r="F118" s="17">
-        <v>856</v>
-      </c>
-      <c r="G118" s="17">
-        <v>856</v>
-      </c>
-      <c r="H118" s="17">
-        <v>1755</v>
-      </c>
-      <c r="I118" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="J118" s="19"/>
-      <c r="K118" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="L118" s="17">
-        <v>6337</v>
-      </c>
-      <c r="M118" s="18">
+      <c r="J118" s="8"/>
+      <c r="K118" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L118" s="4">
+        <v>6339</v>
+      </c>
+      <c r="M118" s="9">
         <v>46117</v>
       </c>
     </row>
     <row r="119" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
-        <v>117</v>
-      </c>
-      <c r="B119" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="B119" s="11" t="s">
         <v>260</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E119" s="4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F119" s="4">
-        <v>140.5</v>
+        <v>99.45</v>
       </c>
       <c r="G119" s="4">
-        <v>1405</v>
+        <v>1989</v>
       </c>
       <c r="H119" s="4">
         <v>85</v>
       </c>
       <c r="I119" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J119" s="8"/>
       <c r="K119" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L119" s="4">
         <v>6339</v>
@@ -6283,35 +6357,35 @@
     </row>
     <row r="120" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
-        <v>118</v>
-      </c>
-      <c r="B120" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="B120" s="12" t="s">
         <v>261</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D120" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E120" s="4">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F120" s="4">
-        <v>205</v>
+        <v>23.4</v>
       </c>
       <c r="G120" s="4">
-        <v>3075</v>
+        <v>2340</v>
       </c>
       <c r="H120" s="4">
         <v>85</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J120" s="8"/>
       <c r="K120" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L120" s="4">
         <v>6339</v>
@@ -6322,35 +6396,35 @@
     </row>
     <row r="121" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
-        <v>119</v>
-      </c>
-      <c r="B121" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B121" s="13" t="s">
         <v>262</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D121" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E121" s="4">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="F121" s="4">
-        <v>99.45</v>
+        <v>2.95</v>
       </c>
       <c r="G121" s="4">
-        <v>1989</v>
+        <v>295</v>
       </c>
       <c r="H121" s="4">
         <v>85</v>
       </c>
       <c r="I121" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J121" s="8"/>
       <c r="K121" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L121" s="4">
         <v>6339</v>
@@ -6361,9 +6435,9 @@
     </row>
     <row r="122" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
-        <v>120</v>
-      </c>
-      <c r="B122" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="B122" s="13" t="s">
         <v>263</v>
       </c>
       <c r="C122" s="4" t="s">
@@ -6376,20 +6450,20 @@
         <v>100</v>
       </c>
       <c r="F122" s="4">
-        <v>23.4</v>
+        <v>2.95</v>
       </c>
       <c r="G122" s="4">
-        <v>2340</v>
+        <v>295</v>
       </c>
       <c r="H122" s="4">
         <v>85</v>
       </c>
       <c r="I122" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J122" s="8"/>
       <c r="K122" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L122" s="4">
         <v>6339</v>
@@ -6400,10 +6474,10 @@
     </row>
     <row r="123" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
-        <v>121</v>
-      </c>
-      <c r="B123" s="13" t="s">
-        <v>264</v>
+        <v>123</v>
+      </c>
+      <c r="B123" s="11" t="s">
+        <v>260</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>238</v>
@@ -6412,26 +6486,26 @@
         <v>16</v>
       </c>
       <c r="E123" s="4">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F123" s="4">
-        <v>2.95</v>
+        <v>99.45</v>
       </c>
       <c r="G123" s="4">
-        <v>295</v>
+        <v>994.5</v>
       </c>
       <c r="H123" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I123" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J123" s="8"/>
       <c r="K123" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L123" s="4">
-        <v>6339</v>
+        <v>6340</v>
       </c>
       <c r="M123" s="9">
         <v>46117</v>
@@ -6439,10 +6513,10 @@
     </row>
     <row r="124" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
-        <v>122</v>
-      </c>
-      <c r="B124" s="13" t="s">
-        <v>265</v>
+        <v>124</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>264</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>239</v>
@@ -6451,26 +6525,26 @@
         <v>16</v>
       </c>
       <c r="E124" s="4">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="F124" s="4">
-        <v>2.95</v>
+        <v>122.85</v>
       </c>
       <c r="G124" s="4">
-        <v>295</v>
+        <v>614.25</v>
       </c>
       <c r="H124" s="4">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I124" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J124" s="8"/>
       <c r="K124" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L124" s="4">
-        <v>6339</v>
+        <v>6340</v>
       </c>
       <c r="M124" s="9">
         <v>46117</v>
@@ -6478,10 +6552,10 @@
     </row>
     <row r="125" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
-        <v>123</v>
-      </c>
-      <c r="B125" s="11" t="s">
-        <v>262</v>
+        <v>125</v>
+      </c>
+      <c r="B125" s="12" t="s">
+        <v>265</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>240</v>
@@ -6490,23 +6564,23 @@
         <v>16</v>
       </c>
       <c r="E125" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F125" s="4">
-        <v>99.45</v>
+        <v>210</v>
       </c>
       <c r="G125" s="4">
-        <v>994.5</v>
+        <v>2520</v>
       </c>
       <c r="H125" s="4">
         <v>86</v>
       </c>
       <c r="I125" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J125" s="8"/>
       <c r="K125" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L125" s="4">
         <v>6340</v>
@@ -6517,35 +6591,35 @@
     </row>
     <row r="126" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
-        <v>124</v>
-      </c>
-      <c r="B126" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B126" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C126" s="4" t="s">
+      <c r="C126" s="21" t="s">
         <v>241</v>
       </c>
       <c r="D126" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E126" s="4">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F126" s="4">
-        <v>122.85</v>
+        <v>44.46</v>
       </c>
       <c r="G126" s="4">
-        <v>614.25</v>
+        <v>889.2</v>
       </c>
       <c r="H126" s="4">
         <v>86</v>
       </c>
       <c r="I126" s="9" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="J126" s="8"/>
       <c r="K126" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L126" s="4">
         <v>6340</v>
@@ -6556,9 +6630,9 @@
     </row>
     <row r="127" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
-        <v>125</v>
-      </c>
-      <c r="B127" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B127" s="11" t="s">
         <v>267</v>
       </c>
       <c r="C127" s="4" t="s">
@@ -6568,26 +6642,26 @@
         <v>16</v>
       </c>
       <c r="E127" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F127" s="4">
-        <v>210</v>
+        <v>4390.5600000000004</v>
       </c>
       <c r="G127" s="4">
-        <v>2520</v>
+        <v>4390.5600000000004</v>
       </c>
       <c r="H127" s="4">
-        <v>86</v>
+        <v>722</v>
       </c>
       <c r="I127" s="9" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="J127" s="8"/>
       <c r="K127" s="4" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="L127" s="4">
-        <v>6340</v>
+        <v>6341</v>
       </c>
       <c r="M127" s="9">
         <v>46117</v>
@@ -6595,269 +6669,265 @@
     </row>
     <row r="128" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>268</v>
       </c>
-      <c r="C128" s="21" t="s">
-        <v>243</v>
+      <c r="C128" s="4" t="s">
+        <v>245</v>
       </c>
       <c r="D128" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E128" s="4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F128" s="4">
-        <v>44.46</v>
+        <v>117</v>
       </c>
       <c r="G128" s="4">
-        <v>889.2</v>
+        <v>2808</v>
       </c>
       <c r="H128" s="4">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I128" s="9" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="J128" s="8"/>
       <c r="K128" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L128" s="4">
-        <v>6340</v>
-      </c>
-      <c r="M128" s="9">
-        <v>46117</v>
+        <v>6342</v>
+      </c>
+      <c r="M128" s="9" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>269</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E129" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F129" s="4">
-        <v>4390.5600000000004</v>
+        <v>321.75</v>
       </c>
       <c r="G129" s="4">
-        <v>4390.5600000000004</v>
+        <v>1608.75</v>
       </c>
       <c r="H129" s="4">
-        <v>722</v>
+        <v>89</v>
       </c>
       <c r="I129" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="J129" s="8"/>
       <c r="K129" s="4" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
       <c r="L129" s="4">
-        <v>6341</v>
-      </c>
-      <c r="M129" s="9">
-        <v>46117</v>
+        <v>6342</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
-        <v>128</v>
-      </c>
-      <c r="B130" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B130" s="11" t="s">
         <v>270</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E130" s="4">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F130" s="4">
-        <v>117</v>
+        <v>438</v>
       </c>
       <c r="G130" s="4">
-        <v>2808</v>
+        <v>5265</v>
       </c>
       <c r="H130" s="4">
         <v>89</v>
       </c>
       <c r="I130" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J130" s="8"/>
       <c r="K130" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L130" s="4">
         <v>6342</v>
       </c>
       <c r="M130" s="9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
-        <v>129</v>
-      </c>
-      <c r="B131" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="B131" s="12" t="s">
         <v>271</v>
       </c>
       <c r="C131" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D131" s="4" t="s">
+      <c r="D131" s="16" t="s">
         <v>16</v>
       </c>
       <c r="E131" s="4">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="F131" s="4">
-        <v>321.75</v>
+        <v>30</v>
       </c>
       <c r="G131" s="4">
-        <v>1608.75</v>
+        <v>30000</v>
       </c>
       <c r="H131" s="4">
-        <v>89</v>
+        <v>19241</v>
       </c>
       <c r="I131" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="4" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="L131" s="4">
-        <v>6342</v>
-      </c>
-      <c r="M131" s="9" t="s">
-        <v>249</v>
+        <v>6343</v>
+      </c>
+      <c r="M131" s="9">
+        <v>46117</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="1">
-        <v>130</v>
-      </c>
-      <c r="B132" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="C132" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="D132" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E132" s="4">
-        <v>12</v>
-      </c>
-      <c r="F132" s="4">
-        <v>438</v>
-      </c>
-      <c r="G132" s="4">
-        <v>5265</v>
-      </c>
-      <c r="H132" s="4">
-        <v>89</v>
-      </c>
-      <c r="I132" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="J132" s="8"/>
-      <c r="K132" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L132" s="4">
-        <v>6342</v>
-      </c>
-      <c r="M132" s="9" t="s">
-        <v>249</v>
+      <c r="A132" s="25"/>
+      <c r="B132" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C132" s="35" t="s">
+        <v>386</v>
+      </c>
+      <c r="D132" s="36" t="s">
+        <v>159</v>
+      </c>
+      <c r="E132" s="36">
+        <v>2101</v>
+      </c>
+      <c r="F132" s="36">
+        <v>109.649</v>
+      </c>
+      <c r="G132" s="36">
+        <v>230372.8</v>
+      </c>
+      <c r="H132" s="36">
+        <v>59846</v>
+      </c>
+      <c r="I132" s="33" t="s">
+        <v>373</v>
+      </c>
+      <c r="J132" s="29"/>
+      <c r="K132" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="L132" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M132" s="30">
+        <v>46117</v>
       </c>
     </row>
     <row r="133" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="1">
-        <v>131</v>
-      </c>
-      <c r="B133" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="C133" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D133" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="E133" s="4">
-        <v>1000</v>
-      </c>
-      <c r="F133" s="4">
-        <v>30</v>
-      </c>
-      <c r="G133" s="4">
-        <v>30000</v>
-      </c>
-      <c r="H133" s="4">
-        <v>19241</v>
-      </c>
-      <c r="I133" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="J133" s="8"/>
-      <c r="K133" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="L133" s="4">
-        <v>6343</v>
-      </c>
-      <c r="M133" s="9">
+      <c r="A133" s="25"/>
+      <c r="B133" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="C133" s="27" t="s">
+        <v>379</v>
+      </c>
+      <c r="D133" s="38" t="s">
+        <v>159</v>
+      </c>
+      <c r="E133" s="36">
+        <v>1814</v>
+      </c>
+      <c r="F133" s="36">
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G133" s="36">
+        <f>F133*E133</f>
+        <v>286419.71600000001</v>
+      </c>
+      <c r="H133" s="36">
+        <v>59846</v>
+      </c>
+      <c r="I133" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="J133" s="29"/>
+      <c r="K133" s="36" t="s">
+        <v>377</v>
+      </c>
+      <c r="L133" s="27">
+        <v>6338</v>
+      </c>
+      <c r="M133" s="30">
         <v>46117</v>
       </c>
     </row>
     <row r="134" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="25">
-        <v>132</v>
-      </c>
+      <c r="A134" s="25"/>
       <c r="B134" s="26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>274</v>
+        <v>380</v>
       </c>
       <c r="D134" s="28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E134" s="36">
-        <v>2101</v>
+        <v>3718</v>
       </c>
       <c r="F134" s="36">
-        <v>109.649</v>
-      </c>
-      <c r="G134" s="36">
-        <v>230372.8</v>
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G134" s="39">
+        <f t="shared" ref="G134:G138" si="2">F134*E134</f>
+        <v>587049.89199999999</v>
       </c>
       <c r="H134" s="28">
         <v>59846</v>
       </c>
       <c r="I134" s="33" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J134" s="29"/>
       <c r="K134" s="32" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L134" s="27">
         <v>6338</v>
@@ -6867,30 +6937,35 @@
       </c>
     </row>
     <row r="135" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="25">
-        <v>133</v>
-      </c>
+      <c r="A135" s="25"/>
       <c r="B135" s="26" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="D135" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E135" s="38"/>
-      <c r="F135" s="38"/>
-      <c r="G135" s="38"/>
+        <v>159</v>
+      </c>
+      <c r="E135" s="36">
+        <v>1538</v>
+      </c>
+      <c r="F135" s="36">
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G135" s="39">
+        <f t="shared" si="2"/>
+        <v>242840.97200000001</v>
+      </c>
       <c r="H135" s="28">
         <v>59846</v>
       </c>
       <c r="I135" s="33" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="J135" s="29"/>
       <c r="K135" s="32" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L135" s="27">
         <v>6338</v>
@@ -6900,30 +6975,35 @@
       </c>
     </row>
     <row r="136" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="25">
-        <v>134</v>
-      </c>
+      <c r="A136" s="25"/>
       <c r="B136" s="26" t="s">
-        <v>114</v>
+        <v>383</v>
       </c>
       <c r="C136" s="27" t="s">
-        <v>107</v>
+        <v>384</v>
       </c>
       <c r="D136" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E136" s="38"/>
-      <c r="F136" s="38"/>
-      <c r="G136" s="38"/>
+        <v>159</v>
+      </c>
+      <c r="E136" s="36">
+        <v>1656</v>
+      </c>
+      <c r="F136" s="36">
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G136" s="39">
+        <f t="shared" si="2"/>
+        <v>261472.46400000001</v>
+      </c>
       <c r="H136" s="28">
         <v>59846</v>
       </c>
       <c r="I136" s="33" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="J136" s="29"/>
       <c r="K136" s="32" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L136" s="27">
         <v>6338</v>
@@ -6933,30 +7013,35 @@
       </c>
     </row>
     <row r="137" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="25">
-        <v>135</v>
-      </c>
-      <c r="B137" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="C137" s="35" t="s">
-        <v>338</v>
+      <c r="A137" s="25"/>
+      <c r="B137" s="26" t="s">
+        <v>381</v>
+      </c>
+      <c r="C137" s="27" t="s">
+        <v>382</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E137" s="37"/>
-      <c r="F137" s="37"/>
-      <c r="G137" s="37"/>
+        <v>159</v>
+      </c>
+      <c r="E137" s="36">
+        <v>1529</v>
+      </c>
+      <c r="F137" s="36">
+        <v>157.89400000000001</v>
+      </c>
+      <c r="G137" s="39">
+        <f t="shared" si="2"/>
+        <v>241419.92600000001</v>
+      </c>
       <c r="H137" s="28">
         <v>59846</v>
       </c>
       <c r="I137" s="33" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
       <c r="J137" s="29"/>
       <c r="K137" s="32" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L137" s="27">
         <v>6338</v>
@@ -6966,36 +7051,35 @@
       </c>
     </row>
     <row r="138" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="25">
-        <v>136</v>
-      </c>
+      <c r="A138" s="25"/>
       <c r="B138" s="26" t="s">
-        <v>339</v>
+        <v>387</v>
       </c>
       <c r="C138" s="27" t="s">
-        <v>276</v>
+        <v>388</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E138" s="36">
-        <v>13828</v>
+        <v>159</v>
+      </c>
+      <c r="E138" s="37">
+        <v>3605</v>
       </c>
       <c r="F138" s="36">
         <v>157.89400000000001</v>
       </c>
-      <c r="G138" s="36">
-        <v>2183368.4</v>
+      <c r="G138" s="39">
+        <f t="shared" si="2"/>
+        <v>569207.87</v>
       </c>
       <c r="H138" s="28">
         <v>59846</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>382</v>
+        <v>375</v>
       </c>
       <c r="J138" s="29"/>
       <c r="K138" s="32" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="L138" s="27">
         <v>6338</v>
@@ -7005,86 +7089,92 @@
       </c>
     </row>
     <row r="139" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="25">
-        <v>137</v>
-      </c>
-      <c r="B139" s="26" t="s">
-        <v>113</v>
-      </c>
-      <c r="C139" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="D139" s="34" t="s">
-        <v>161</v>
-      </c>
-      <c r="E139" s="37"/>
-      <c r="F139" s="37"/>
-      <c r="G139" s="37"/>
-      <c r="H139" s="28">
-        <v>59846</v>
-      </c>
-      <c r="I139" s="33" t="s">
-        <v>383</v>
-      </c>
-      <c r="J139" s="29"/>
-      <c r="K139" s="32" t="s">
-        <v>385</v>
-      </c>
-      <c r="L139" s="27">
-        <v>6338</v>
-      </c>
-      <c r="M139" s="30">
-        <v>46117</v>
+      <c r="A139" s="1">
+        <v>138</v>
+      </c>
+      <c r="B139" s="11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C139" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="D139" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E139" s="4">
+        <v>4</v>
+      </c>
+      <c r="F139" s="4">
+        <v>4500</v>
+      </c>
+      <c r="G139" s="4">
+        <v>18000</v>
+      </c>
+      <c r="H139" s="4">
+        <v>5300</v>
+      </c>
+      <c r="I139" s="9">
+        <v>46117</v>
+      </c>
+      <c r="J139" s="8"/>
+      <c r="K139" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="L139" s="4">
+        <v>6344</v>
+      </c>
+      <c r="M139" s="9" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="140" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
-        <v>138</v>
-      </c>
-      <c r="B140" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="C140" s="4" t="s">
-        <v>279</v>
+        <v>139</v>
+      </c>
+      <c r="B140" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>334</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E140" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F140" s="4">
-        <v>4500</v>
+        <v>750</v>
       </c>
       <c r="G140" s="4">
-        <v>18000</v>
+        <v>7500</v>
       </c>
       <c r="H140" s="4">
-        <v>5300</v>
+        <v>14019</v>
       </c>
       <c r="I140" s="9">
         <v>46117</v>
       </c>
       <c r="J140" s="8"/>
       <c r="K140" s="4" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="L140" s="4">
-        <v>6344</v>
+        <v>6345</v>
       </c>
       <c r="M140" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
-        <v>139</v>
-      </c>
-      <c r="B141" s="24" t="s">
-        <v>341</v>
-      </c>
-      <c r="C141" s="14" t="s">
-        <v>342</v>
+        <v>140</v>
+      </c>
+      <c r="B141" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C141" s="4" t="s">
+        <v>275</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>16</v>
@@ -7093,10 +7183,10 @@
         <v>10</v>
       </c>
       <c r="F141" s="4">
-        <v>750</v>
+        <v>30</v>
       </c>
       <c r="G141" s="4">
-        <v>7500</v>
+        <v>300</v>
       </c>
       <c r="H141" s="4">
         <v>14019</v>
@@ -7106,36 +7196,36 @@
       </c>
       <c r="J141" s="8"/>
       <c r="K141" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L141" s="4">
         <v>6345</v>
       </c>
       <c r="M141" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="142" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>145</v>
+        <v>335</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E142" s="4">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F142" s="4">
-        <v>30</v>
+        <v>550</v>
       </c>
       <c r="G142" s="4">
-        <v>300</v>
+        <v>3850</v>
       </c>
       <c r="H142" s="4">
         <v>14019</v>
@@ -7145,36 +7235,36 @@
       </c>
       <c r="J142" s="8"/>
       <c r="K142" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L142" s="4">
         <v>6345</v>
       </c>
       <c r="M142" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="143" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E143" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F143" s="4">
-        <v>550</v>
+        <v>60</v>
       </c>
       <c r="G143" s="4">
-        <v>3850</v>
+        <v>120</v>
       </c>
       <c r="H143" s="4">
         <v>14019</v>
@@ -7184,36 +7274,36 @@
       </c>
       <c r="J143" s="8"/>
       <c r="K143" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L143" s="4">
         <v>6345</v>
       </c>
       <c r="M143" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E144" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" s="4">
-        <v>60</v>
+        <v>1500</v>
       </c>
       <c r="G144" s="4">
-        <v>120</v>
+        <v>1500</v>
       </c>
       <c r="H144" s="4">
         <v>14019</v>
@@ -7223,36 +7313,34 @@
       </c>
       <c r="J144" s="8"/>
       <c r="K144" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L144" s="4">
         <v>6345</v>
       </c>
       <c r="M144" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
-        <v>143</v>
-      </c>
-      <c r="B145" s="12" t="s">
-        <v>345</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="B145" s="6"/>
       <c r="C145" s="4" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E145" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F145" s="4">
-        <v>1500</v>
+        <v>45</v>
       </c>
       <c r="G145" s="4">
-        <v>1500</v>
+        <v>180</v>
       </c>
       <c r="H145" s="4">
         <v>14019</v>
@@ -7262,34 +7350,36 @@
       </c>
       <c r="J145" s="8"/>
       <c r="K145" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L145" s="4">
         <v>6345</v>
       </c>
       <c r="M145" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
-        <v>144</v>
-      </c>
-      <c r="B146" s="6"/>
+        <v>145</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>338</v>
+      </c>
       <c r="C146" s="4" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E146" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F146" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G146" s="4">
-        <v>180</v>
+        <v>75</v>
       </c>
       <c r="H146" s="4">
         <v>14019</v>
@@ -7299,36 +7389,36 @@
       </c>
       <c r="J146" s="8"/>
       <c r="K146" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L146" s="4">
         <v>6345</v>
       </c>
       <c r="M146" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="147" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E147" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F147" s="4">
-        <v>15</v>
+        <v>375</v>
       </c>
       <c r="G147" s="4">
-        <v>75</v>
+        <v>3750</v>
       </c>
       <c r="H147" s="4">
         <v>14019</v>
@@ -7338,36 +7428,36 @@
       </c>
       <c r="J147" s="8"/>
       <c r="K147" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L147" s="4">
         <v>6345</v>
       </c>
       <c r="M147" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E148" s="4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F148" s="4">
-        <v>375</v>
+        <v>575</v>
       </c>
       <c r="G148" s="4">
-        <v>3750</v>
+        <v>2300</v>
       </c>
       <c r="H148" s="4">
         <v>14019</v>
@@ -7377,36 +7467,36 @@
       </c>
       <c r="J148" s="8"/>
       <c r="K148" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L148" s="4">
         <v>6345</v>
       </c>
       <c r="M148" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E149" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F149" s="4">
-        <v>575</v>
+        <v>25</v>
       </c>
       <c r="G149" s="4">
-        <v>2300</v>
+        <v>125</v>
       </c>
       <c r="H149" s="4">
         <v>14019</v>
@@ -7416,63 +7506,63 @@
       </c>
       <c r="J149" s="8"/>
       <c r="K149" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L149" s="4">
         <v>6345</v>
       </c>
       <c r="M149" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
-        <v>148</v>
-      </c>
-      <c r="B150" s="12" t="s">
-        <v>349</v>
+        <v>149</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>342</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E150" s="4">
-        <v>5</v>
-      </c>
-      <c r="F150" s="4">
-        <v>25</v>
+        <v>1</v>
+      </c>
+      <c r="F150" s="16">
+        <v>152775</v>
       </c>
       <c r="G150" s="4">
-        <v>125</v>
+        <v>152775</v>
       </c>
       <c r="H150" s="4">
-        <v>14019</v>
+        <v>80</v>
       </c>
       <c r="I150" s="9">
         <v>46117</v>
       </c>
       <c r="J150" s="8"/>
-      <c r="K150" s="4" t="s">
-        <v>162</v>
+      <c r="K150" s="17" t="s">
+        <v>227</v>
       </c>
       <c r="L150" s="4">
-        <v>6345</v>
+        <v>6347</v>
       </c>
       <c r="M150" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>16</v>
@@ -7480,11 +7570,11 @@
       <c r="E151" s="4">
         <v>1</v>
       </c>
-      <c r="F151" s="16">
-        <v>152775</v>
+      <c r="F151" s="4">
+        <v>43125</v>
       </c>
       <c r="G151" s="4">
-        <v>152775</v>
+        <v>43125</v>
       </c>
       <c r="H151" s="4">
         <v>80</v>
@@ -7494,24 +7584,24 @@
       </c>
       <c r="J151" s="8"/>
       <c r="K151" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L151" s="4">
         <v>6347</v>
       </c>
       <c r="M151" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
-        <v>150</v>
-      </c>
-      <c r="B152" s="11" t="s">
-        <v>351</v>
+        <v>151</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>344</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>16</v>
@@ -7520,10 +7610,10 @@
         <v>1</v>
       </c>
       <c r="F152" s="4">
-        <v>43125</v>
+        <v>3300</v>
       </c>
       <c r="G152" s="4">
-        <v>43125</v>
+        <v>3300</v>
       </c>
       <c r="H152" s="4">
         <v>80</v>
@@ -7533,24 +7623,24 @@
       </c>
       <c r="J152" s="8"/>
       <c r="K152" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L152" s="4">
         <v>6347</v>
       </c>
       <c r="M152" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>16</v>
@@ -7559,10 +7649,10 @@
         <v>1</v>
       </c>
       <c r="F153" s="4">
-        <v>3300</v>
+        <v>580</v>
       </c>
       <c r="G153" s="4">
-        <v>3300</v>
+        <v>580</v>
       </c>
       <c r="H153" s="4">
         <v>80</v>
@@ -7572,24 +7662,24 @@
       </c>
       <c r="J153" s="8"/>
       <c r="K153" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L153" s="4">
         <v>6347</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="154" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>16</v>
@@ -7598,10 +7688,10 @@
         <v>1</v>
       </c>
       <c r="F154" s="4">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="G154" s="4">
-        <v>580</v>
+        <v>220</v>
       </c>
       <c r="H154" s="4">
         <v>80</v>
@@ -7611,63 +7701,63 @@
       </c>
       <c r="J154" s="8"/>
       <c r="K154" s="17" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L154" s="4">
         <v>6347</v>
       </c>
       <c r="M154" s="9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="155" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
-        <v>153</v>
-      </c>
-      <c r="B155" s="12" t="s">
-        <v>354</v>
+        <v>154</v>
+      </c>
+      <c r="B155" s="11" t="s">
+        <v>347</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E155" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F155" s="4">
-        <v>220</v>
+        <v>134.55000000000001</v>
       </c>
       <c r="G155" s="4">
-        <v>220</v>
+        <v>1345.5</v>
       </c>
       <c r="H155" s="4">
-        <v>80</v>
-      </c>
-      <c r="I155" s="9">
-        <v>46117</v>
+        <v>93</v>
+      </c>
+      <c r="I155" s="9" t="s">
+        <v>288</v>
       </c>
       <c r="J155" s="8"/>
-      <c r="K155" s="17" t="s">
-        <v>229</v>
+      <c r="K155" s="4" t="s">
+        <v>226</v>
       </c>
       <c r="L155" s="4">
-        <v>6347</v>
-      </c>
-      <c r="M155" s="9" t="s">
-        <v>248</v>
+        <v>6348</v>
+      </c>
+      <c r="M155" s="9">
+        <v>46147</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>16</v>
@@ -7676,20 +7766,20 @@
         <v>10</v>
       </c>
       <c r="F156" s="4">
-        <v>134.55000000000001</v>
+        <v>526.5</v>
       </c>
       <c r="G156" s="4">
-        <v>1345.5</v>
+        <v>5265</v>
       </c>
       <c r="H156" s="4">
         <v>93</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J156" s="8"/>
       <c r="K156" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L156" s="4">
         <v>6348</v>
@@ -7700,35 +7790,35 @@
     </row>
     <row r="157" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
-        <v>155</v>
-      </c>
-      <c r="B157" s="11" t="s">
-        <v>356</v>
+        <v>156</v>
+      </c>
+      <c r="B157" s="12" t="s">
+        <v>349</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E157" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F157" s="4">
-        <v>526.5</v>
+        <v>234</v>
       </c>
       <c r="G157" s="4">
-        <v>5265</v>
+        <v>468</v>
       </c>
       <c r="H157" s="4">
         <v>93</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L157" s="4">
         <v>6348</v>
@@ -7739,35 +7829,35 @@
     </row>
     <row r="158" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E158" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" s="4">
-        <v>234</v>
+        <v>82</v>
       </c>
       <c r="G158" s="4">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="H158" s="4">
         <v>93</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L158" s="4">
         <v>6348</v>
@@ -7778,35 +7868,35 @@
     </row>
     <row r="159" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
-        <v>157</v>
-      </c>
-      <c r="B159" s="12" t="s">
-        <v>358</v>
+        <v>158</v>
+      </c>
+      <c r="B159" s="11" t="s">
+        <v>351</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E159" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F159" s="4">
-        <v>82</v>
+        <v>8775</v>
       </c>
       <c r="G159" s="4">
-        <v>82</v>
+        <v>1755</v>
       </c>
       <c r="H159" s="4">
         <v>93</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L159" s="4">
         <v>6348</v>
@@ -7817,74 +7907,74 @@
     </row>
     <row r="160" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
-        <v>158</v>
-      </c>
-      <c r="B160" s="11" t="s">
-        <v>359</v>
+        <v>159</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>352</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E160" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F160" s="4">
-        <v>8775</v>
+        <v>5701</v>
       </c>
       <c r="G160" s="4">
-        <v>1755</v>
+        <v>11402</v>
       </c>
       <c r="H160" s="4">
-        <v>93</v>
+        <v>713</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="4" t="s">
-        <v>228</v>
+        <v>127</v>
       </c>
       <c r="L160" s="4">
-        <v>6348</v>
+        <v>6349</v>
       </c>
       <c r="M160" s="9">
-        <v>46147</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E161" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F161" s="4">
-        <v>5701</v>
+        <v>807</v>
       </c>
       <c r="G161" s="4">
-        <v>11402</v>
+        <v>807</v>
       </c>
       <c r="H161" s="4">
         <v>713</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L161" s="4">
         <v>6349</v>
@@ -7895,38 +7985,38 @@
     </row>
     <row r="162" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E162" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F162" s="4">
-        <v>807</v>
+        <v>1184.21</v>
       </c>
       <c r="G162" s="4">
-        <v>807</v>
+        <v>4736.84</v>
       </c>
       <c r="H162" s="4">
-        <v>713</v>
+        <v>6350</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="4" t="s">
-        <v>129</v>
+        <v>299</v>
       </c>
       <c r="L162" s="4">
-        <v>6349</v>
+        <v>6350</v>
       </c>
       <c r="M162" s="9">
         <v>46117</v>
@@ -7934,10 +8024,10 @@
     </row>
     <row r="163" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
-        <v>161</v>
-      </c>
-      <c r="B163" s="12" t="s">
-        <v>362</v>
+        <v>162</v>
+      </c>
+      <c r="B163" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="C163" s="4" t="s">
         <v>302</v>
@@ -7946,76 +8036,76 @@
         <v>16</v>
       </c>
       <c r="E163" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F163" s="4">
-        <v>1184.21</v>
+        <v>480</v>
       </c>
       <c r="G163" s="4">
-        <v>4736.84</v>
+        <v>480</v>
       </c>
       <c r="H163" s="4">
-        <v>6350</v>
+        <v>26</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="4" t="s">
-        <v>304</v>
+        <v>17</v>
       </c>
       <c r="L163" s="4">
-        <v>6350</v>
-      </c>
-      <c r="M163" s="9">
-        <v>46117</v>
+        <v>6351</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B164" s="10" t="s">
         <v>45</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E164" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F164" s="4">
-        <v>480</v>
+        <v>275</v>
       </c>
       <c r="G164" s="4">
-        <v>480</v>
+        <v>27500</v>
       </c>
       <c r="H164" s="4">
-        <v>26</v>
+        <v>141</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J164" s="8"/>
       <c r="K164" s="4" t="s">
-        <v>17</v>
+        <v>305</v>
       </c>
       <c r="L164" s="4">
-        <v>6351</v>
+        <v>6358</v>
       </c>
       <c r="M164" s="9" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
-        <v>163</v>
-      </c>
-      <c r="B165" s="10" t="s">
-        <v>45</v>
+        <v>164</v>
+      </c>
+      <c r="B165" s="12" t="s">
+        <v>355</v>
       </c>
       <c r="C165" s="4" t="s">
         <v>307</v>
@@ -8027,37 +8117,37 @@
         <v>10</v>
       </c>
       <c r="F165" s="4">
-        <v>275</v>
+        <v>1025</v>
       </c>
       <c r="G165" s="4">
-        <v>27500</v>
+        <v>10250</v>
       </c>
       <c r="H165" s="4">
-        <v>141</v>
+        <v>1528</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J165" s="8"/>
       <c r="K165" s="4" t="s">
-        <v>310</v>
+        <v>17</v>
       </c>
       <c r="L165" s="4">
-        <v>6358</v>
+        <v>6359</v>
       </c>
       <c r="M165" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>16</v>
@@ -8066,16 +8156,16 @@
         <v>10</v>
       </c>
       <c r="F166" s="4">
-        <v>1025</v>
+        <v>900</v>
       </c>
       <c r="G166" s="4">
-        <v>10250</v>
+        <v>9000</v>
       </c>
       <c r="H166" s="4">
         <v>1528</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="4" t="s">
@@ -8085,289 +8175,289 @@
         <v>6359</v>
       </c>
       <c r="M166" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
-        <v>165</v>
-      </c>
-      <c r="B167" s="12" t="s">
-        <v>364</v>
+        <v>166</v>
+      </c>
+      <c r="B167" s="11" t="s">
+        <v>357</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E167" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F167" s="4">
-        <v>900</v>
+        <v>11000</v>
       </c>
       <c r="G167" s="4">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H167" s="4">
-        <v>1528</v>
+        <v>142</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="4" t="s">
-        <v>17</v>
+        <v>305</v>
       </c>
       <c r="L167" s="4">
-        <v>6359</v>
+        <v>6360</v>
       </c>
       <c r="M167" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E168" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="F168" s="4">
-        <v>11000</v>
+        <v>15</v>
       </c>
       <c r="G168" s="4">
-        <v>11000</v>
+        <v>750</v>
       </c>
       <c r="H168" s="4">
         <v>142</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="4" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="L168" s="4">
         <v>6360</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>366</v>
+        <v>359</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E169" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="F169" s="4">
-        <v>15</v>
+        <v>450</v>
       </c>
       <c r="G169" s="4">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="H169" s="4">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J169" s="8"/>
       <c r="K169" s="4" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="L169" s="4">
-        <v>6360</v>
+        <v>6361</v>
       </c>
       <c r="M169" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E170" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F170" s="4">
-        <v>450</v>
+        <v>351</v>
       </c>
       <c r="G170" s="4">
-        <v>450</v>
+        <v>5265</v>
       </c>
       <c r="H170" s="4">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J170" s="8"/>
       <c r="K170" s="4" t="s">
-        <v>310</v>
+        <v>226</v>
       </c>
       <c r="L170" s="4">
-        <v>6361</v>
+        <v>6362</v>
       </c>
       <c r="M170" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
-        <v>169</v>
-      </c>
-      <c r="B171" s="11" t="s">
-        <v>368</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="B171" s="12"/>
       <c r="C171" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E171" s="4">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F171" s="4">
-        <v>351</v>
+        <v>702</v>
       </c>
       <c r="G171" s="4">
-        <v>5265</v>
+        <v>702</v>
       </c>
       <c r="H171" s="4">
         <v>94</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J171" s="8"/>
       <c r="K171" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L171" s="4">
         <v>6362</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
-        <v>170</v>
-      </c>
-      <c r="B172" s="12"/>
+        <v>171</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>268</v>
+      </c>
       <c r="C172" s="4" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E172" s="4">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="F172" s="4">
-        <v>702</v>
+        <v>117</v>
       </c>
       <c r="G172" s="4">
-        <v>702</v>
+        <v>2808</v>
       </c>
       <c r="H172" s="4">
         <v>94</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L172" s="4">
         <v>6362</v>
       </c>
       <c r="M172" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
-        <v>171</v>
-      </c>
-      <c r="B173" s="12" t="s">
-        <v>270</v>
+        <v>172</v>
+      </c>
+      <c r="B173" s="10" t="s">
+        <v>361</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E173" s="4">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="F173" s="4">
-        <v>117</v>
+        <v>25740</v>
       </c>
       <c r="G173" s="4">
-        <v>2808</v>
+        <v>17220</v>
       </c>
       <c r="H173" s="4">
         <v>94</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J173" s="8"/>
       <c r="K173" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L173" s="4">
         <v>6362</v>
       </c>
       <c r="M173" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>369</v>
+        <v>362</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>16</v>
@@ -8376,211 +8466,211 @@
         <v>3</v>
       </c>
       <c r="F174" s="4">
-        <v>25740</v>
+        <v>2457</v>
       </c>
       <c r="G174" s="4">
-        <v>17220</v>
+        <v>7371</v>
       </c>
       <c r="H174" s="4">
         <v>94</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L174" s="4">
         <v>6362</v>
       </c>
       <c r="M174" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
-        <v>173</v>
-      </c>
-      <c r="B175" s="10" t="s">
-        <v>370</v>
+        <v>174</v>
+      </c>
+      <c r="B175" s="12" t="s">
+        <v>363</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E175" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F175" s="4">
-        <v>2457</v>
+        <v>1000</v>
       </c>
       <c r="G175" s="4">
-        <v>7371</v>
+        <v>2000</v>
       </c>
       <c r="H175" s="4">
-        <v>94</v>
+        <v>14057</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="4" t="s">
-        <v>228</v>
+        <v>160</v>
       </c>
       <c r="L175" s="4">
-        <v>6362</v>
+        <v>6363</v>
       </c>
       <c r="M175" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>371</v>
+        <v>340</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>322</v>
+        <v>280</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E176" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F176" s="4">
-        <v>1000</v>
+        <v>550</v>
       </c>
       <c r="G176" s="4">
-        <v>2000</v>
+        <v>2750</v>
       </c>
       <c r="H176" s="4">
         <v>14057</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L176" s="4">
         <v>6363</v>
       </c>
       <c r="M176" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E177" s="4">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F177" s="4">
-        <v>550</v>
+        <v>20</v>
       </c>
       <c r="G177" s="4">
-        <v>2750</v>
+        <v>1000</v>
       </c>
       <c r="H177" s="4">
         <v>14057</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="L177" s="4">
         <v>6363</v>
       </c>
       <c r="M177" s="9" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
-        <v>176</v>
-      </c>
-      <c r="B178" s="12" t="s">
-        <v>372</v>
+        <v>177</v>
+      </c>
+      <c r="B178" s="10" t="s">
+        <v>38</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E178" s="4">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="F178" s="4">
-        <v>20</v>
+        <v>7649</v>
       </c>
       <c r="G178" s="4">
-        <v>1000</v>
+        <v>30597</v>
       </c>
       <c r="H178" s="4">
-        <v>14057</v>
+        <v>2464</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="J178" s="8"/>
       <c r="K178" s="4" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="L178" s="4">
-        <v>6363</v>
+        <v>6364</v>
       </c>
       <c r="M178" s="9" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
-        <v>177</v>
-      </c>
-      <c r="B179" s="10" t="s">
-        <v>38</v>
+        <v>178</v>
+      </c>
+      <c r="B179" s="11" t="s">
+        <v>49</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E179" s="4">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="F179" s="4">
-        <v>7649</v>
+        <v>32</v>
       </c>
       <c r="G179" s="4">
-        <v>30597</v>
+        <v>2240</v>
       </c>
       <c r="H179" s="4">
         <v>2464</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="4" t="s">
@@ -8590,36 +8680,36 @@
         <v>6364</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>49</v>
+        <v>365</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E180" s="4">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="F180" s="4">
-        <v>32</v>
+        <v>313</v>
       </c>
       <c r="G180" s="4">
-        <v>2240</v>
+        <v>3135</v>
       </c>
       <c r="H180" s="4">
         <v>2464</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="4" t="s">
@@ -8629,18 +8719,18 @@
         <v>6364</v>
       </c>
       <c r="M180" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>16</v>
@@ -8658,7 +8748,7 @@
         <v>2464</v>
       </c>
       <c r="I181" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="4" t="s">
@@ -8668,36 +8758,36 @@
         <v>6364</v>
       </c>
       <c r="M181" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
-        <v>180</v>
-      </c>
-      <c r="B182" s="11" t="s">
-        <v>374</v>
+        <v>181</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E182" s="4">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F182" s="4">
-        <v>313</v>
+        <v>1661</v>
       </c>
       <c r="G182" s="4">
-        <v>3135</v>
+        <v>249222</v>
       </c>
       <c r="H182" s="4">
         <v>2464</v>
       </c>
       <c r="I182" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="4" t="s">
@@ -8707,36 +8797,36 @@
         <v>6364</v>
       </c>
       <c r="M182" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
-        <v>181</v>
-      </c>
-      <c r="B183" s="10" t="s">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="B183" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E183" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F183" s="4">
-        <v>1661</v>
+        <v>2225</v>
       </c>
       <c r="G183" s="4">
-        <v>249222</v>
+        <v>28936</v>
       </c>
       <c r="H183" s="4">
         <v>2464</v>
       </c>
       <c r="I183" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="4" t="s">
@@ -8746,36 +8836,36 @@
         <v>6364</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
-        <v>182</v>
-      </c>
-      <c r="B184" s="11" t="s">
-        <v>47</v>
+        <v>183</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>367</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E184" s="4">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F184" s="4">
-        <v>2225</v>
+        <v>5580</v>
       </c>
       <c r="G184" s="4">
-        <v>28936</v>
+        <v>80045</v>
       </c>
       <c r="H184" s="4">
         <v>2464</v>
       </c>
       <c r="I184" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="4" t="s">
@@ -8785,36 +8875,36 @@
         <v>6364</v>
       </c>
       <c r="M184" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
-        <v>183</v>
-      </c>
-      <c r="B185" s="10" t="s">
-        <v>375</v>
+        <v>184</v>
+      </c>
+      <c r="B185" s="12" t="s">
+        <v>52</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>330</v>
+        <v>32</v>
       </c>
       <c r="D185" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E185" s="4">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F185" s="4">
-        <v>5580</v>
+        <v>288</v>
       </c>
       <c r="G185" s="4">
-        <v>80045</v>
+        <v>6056</v>
       </c>
       <c r="H185" s="4">
         <v>2464</v>
       </c>
       <c r="I185" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="4" t="s">
@@ -8824,36 +8914,36 @@
         <v>6364</v>
       </c>
       <c r="M185" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
-        <v>184</v>
-      </c>
-      <c r="B186" s="12" t="s">
-        <v>52</v>
+        <v>185</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>368</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>32</v>
+        <v>326</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E186" s="4">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F186" s="4">
-        <v>288</v>
+        <v>1943</v>
       </c>
       <c r="G186" s="4">
-        <v>6056</v>
+        <v>1943</v>
       </c>
       <c r="H186" s="4">
         <v>2464</v>
       </c>
       <c r="I186" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="4" t="s">
@@ -8863,36 +8953,36 @@
         <v>6364</v>
       </c>
       <c r="M186" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
-        <v>185</v>
-      </c>
-      <c r="B187" s="11" t="s">
-        <v>376</v>
+        <v>186</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>42</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E187" s="4">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="F187" s="4">
-        <v>1943</v>
+        <v>1611</v>
       </c>
       <c r="G187" s="4">
-        <v>1943</v>
+        <v>29005</v>
       </c>
       <c r="H187" s="4">
         <v>2464</v>
       </c>
       <c r="I187" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J187" s="8"/>
       <c r="K187" s="4" t="s">
@@ -8902,36 +8992,36 @@
         <v>6364</v>
       </c>
       <c r="M187" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E188" s="4">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F188" s="4">
-        <v>1611</v>
+        <v>2100</v>
       </c>
       <c r="G188" s="4">
-        <v>29005</v>
+        <v>12602</v>
       </c>
       <c r="H188" s="4">
         <v>2464</v>
       </c>
       <c r="I188" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="4" t="s">
@@ -8941,36 +9031,36 @@
         <v>6364</v>
       </c>
       <c r="M188" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>333</v>
+        <v>31</v>
       </c>
       <c r="D189" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E189" s="4">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="F189" s="4">
-        <v>2100</v>
+        <v>601</v>
       </c>
       <c r="G189" s="4">
-        <v>12602</v>
+        <v>14446</v>
       </c>
       <c r="H189" s="4">
         <v>2464</v>
       </c>
       <c r="I189" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="4" t="s">
@@ -8980,75 +9070,75 @@
         <v>6364</v>
       </c>
       <c r="M189" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D190" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E190" s="4">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F190" s="4">
-        <v>601</v>
+        <v>6395</v>
       </c>
       <c r="G190" s="4">
-        <v>14446</v>
+        <v>102326</v>
       </c>
       <c r="H190" s="4">
         <v>2464</v>
       </c>
       <c r="I190" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="4" t="s">
         <v>17</v>
       </c>
       <c r="L190" s="4">
-        <v>6364</v>
+        <v>6365</v>
       </c>
       <c r="M190" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>41</v>
+        <v>370</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>33</v>
+        <v>330</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E191" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F191" s="4">
         <v>6395</v>
       </c>
       <c r="G191" s="4">
-        <v>102326</v>
+        <v>12790</v>
       </c>
       <c r="H191" s="4">
         <v>2464</v>
       </c>
       <c r="I191" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="4" t="s">
@@ -9058,18 +9148,18 @@
         <v>6365</v>
       </c>
       <c r="M191" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>16</v>
@@ -9078,16 +9168,16 @@
         <v>2</v>
       </c>
       <c r="F192" s="4">
-        <v>6395</v>
+        <v>8030</v>
       </c>
       <c r="G192" s="4">
-        <v>12790</v>
+        <v>16060</v>
       </c>
       <c r="H192" s="4">
         <v>2464</v>
       </c>
       <c r="I192" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J192" s="8"/>
       <c r="K192" s="4" t="s">
@@ -9097,36 +9187,36 @@
         <v>6365</v>
       </c>
       <c r="M192" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
-        <v>191</v>
-      </c>
-      <c r="B193" s="10" t="s">
-        <v>377</v>
+        <v>192</v>
+      </c>
+      <c r="B193" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>336</v>
+        <v>34</v>
       </c>
       <c r="D193" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E193" s="4">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F193" s="4">
-        <v>8030</v>
+        <v>2445</v>
       </c>
       <c r="G193" s="4">
-        <v>16060</v>
+        <v>51351</v>
       </c>
       <c r="H193" s="4">
         <v>2464</v>
       </c>
       <c r="I193" s="9" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="J193" s="8"/>
       <c r="K193" s="4" t="s">
@@ -9136,69 +9226,17 @@
         <v>6365</v>
       </c>
       <c r="M193" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="194" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="1">
-        <v>192</v>
-      </c>
-      <c r="B194" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="D194" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E194" s="4">
-        <v>21</v>
-      </c>
-      <c r="F194" s="4">
-        <v>2445</v>
-      </c>
-      <c r="G194" s="4">
-        <v>51351</v>
-      </c>
-      <c r="H194" s="4">
-        <v>2464</v>
-      </c>
-      <c r="I194" s="9" t="s">
-        <v>334</v>
-      </c>
-      <c r="J194" s="8"/>
-      <c r="K194" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L194" s="4">
-        <v>6365</v>
-      </c>
-      <c r="M194" s="9" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="195" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+        <v>329</v>
+      </c>
+    </row>
+    <row r="194" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="E138:E139"/>
-    <mergeCell ref="E134:E137"/>
-    <mergeCell ref="F49:F54"/>
-    <mergeCell ref="F58:F61"/>
-    <mergeCell ref="G58:G61"/>
-    <mergeCell ref="E49:E54"/>
-    <mergeCell ref="G49:G54"/>
-    <mergeCell ref="F134:F137"/>
-    <mergeCell ref="G134:G137"/>
-    <mergeCell ref="G138:G139"/>
-    <mergeCell ref="F138:F139"/>
-  </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="69" orientation="landscape" r:id="rId1"/>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="97" max="12" man="1"/>
+    <brk id="95" max="12" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/data/transactions/أذونات الإضافة لشهر 5.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4B8D029-F246-4018-BA47-4159023020F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51AD9B8-7B97-4B62-8E5C-D9102F3DA5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="3240" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="392">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -1210,6 +1210,9 @@
   </si>
   <si>
     <t>لوح 1.5 ﻣﻢ SST ﻣﺼﻨﻔﺮ ﻣﻐﻠﻒ 1.25 × 2 م</t>
+  </si>
+  <si>
+    <t>شركة الذهب للتيريد</t>
   </si>
 </sst>
 </file>
@@ -8052,7 +8055,7 @@
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="4" t="s">
-        <v>17</v>
+        <v>391</v>
       </c>
       <c r="L163" s="4">
         <v>6351</v>

--- a/data/transactions/أذونات الإضافة لشهر 5.xlsx
+++ b/data/transactions/أذونات الإضافة لشهر 5.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\ERP\Development\erp-server\data\transactions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C51AD9B8-7B97-4B62-8E5C-D9102F3DA5F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92496DF7-FEE0-4933-ADAE-04A42B1DFD53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="942" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="391">
   <si>
     <t>بورسعيد لصناعة المعادن</t>
   </si>
@@ -778,9 +778,6 @@
   </si>
   <si>
     <t>23-4-2026</t>
-  </si>
-  <si>
-    <t>4-5-206</t>
   </si>
   <si>
     <t>ميكروستش بنز</t>
@@ -1881,7 +1878,7 @@
     </row>
     <row r="3" spans="1:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -1898,7 +1895,7 @@
     </row>
     <row r="4" spans="1:13" s="23" customFormat="1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
@@ -3612,7 +3609,7 @@
       </c>
       <c r="J49" s="29"/>
       <c r="K49" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L49" s="27">
         <v>6323</v>
@@ -3652,7 +3649,7 @@
       </c>
       <c r="J50" s="29"/>
       <c r="K50" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L50" s="27">
         <v>6323</v>
@@ -3666,10 +3663,10 @@
         <v>47</v>
       </c>
       <c r="B51" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="C51" s="27" t="s">
         <v>389</v>
-      </c>
-      <c r="C51" s="27" t="s">
-        <v>390</v>
       </c>
       <c r="D51" s="39" t="s">
         <v>159</v>
@@ -3692,7 +3689,7 @@
       </c>
       <c r="J51" s="29"/>
       <c r="K51" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L51" s="27">
         <v>6323</v>
@@ -3732,7 +3729,7 @@
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L52" s="27">
         <v>6323</v>
@@ -3772,7 +3769,7 @@
       </c>
       <c r="J53" s="29"/>
       <c r="K53" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L53" s="27">
         <v>6323</v>
@@ -3929,7 +3926,7 @@
       </c>
       <c r="J57" s="29"/>
       <c r="K57" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L57" s="27">
         <v>6325</v>
@@ -3969,7 +3966,7 @@
       </c>
       <c r="J58" s="29"/>
       <c r="K58" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L58" s="27">
         <v>6325</v>
@@ -4009,7 +4006,7 @@
       </c>
       <c r="J59" s="29"/>
       <c r="K59" s="27" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L59" s="27">
         <v>6325</v>
@@ -4906,7 +4903,7 @@
       </c>
       <c r="J82" s="8"/>
       <c r="K82" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L82" s="4">
         <v>6333</v>
@@ -4945,7 +4942,7 @@
       </c>
       <c r="J83" s="8"/>
       <c r="K83" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L83" s="4">
         <v>6333</v>
@@ -4984,7 +4981,7 @@
       </c>
       <c r="J84" s="8"/>
       <c r="K84" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L84" s="4">
         <v>6333</v>
@@ -5023,7 +5020,7 @@
       </c>
       <c r="J85" s="8"/>
       <c r="K85" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L85" s="4">
         <v>6333</v>
@@ -5062,7 +5059,7 @@
       </c>
       <c r="J86" s="8"/>
       <c r="K86" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L86" s="4">
         <v>6333</v>
@@ -5101,7 +5098,7 @@
       </c>
       <c r="J87" s="8"/>
       <c r="K87" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L87" s="4">
         <v>6333</v>
@@ -5140,7 +5137,7 @@
       </c>
       <c r="J88" s="8"/>
       <c r="K88" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L88" s="4">
         <v>6333</v>
@@ -5179,7 +5176,7 @@
       </c>
       <c r="J89" s="8"/>
       <c r="K89" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L89" s="4">
         <v>6333</v>
@@ -5218,7 +5215,7 @@
       </c>
       <c r="J90" s="8"/>
       <c r="K90" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L90" s="4">
         <v>6333</v>
@@ -5257,7 +5254,7 @@
       </c>
       <c r="J91" s="8"/>
       <c r="K91" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L91" s="4">
         <v>6333</v>
@@ -5296,7 +5293,7 @@
       </c>
       <c r="J92" s="8"/>
       <c r="K92" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L92" s="4">
         <v>6333</v>
@@ -5335,7 +5332,7 @@
       </c>
       <c r="J93" s="8"/>
       <c r="K93" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L93" s="4">
         <v>6333</v>
@@ -5374,7 +5371,7 @@
       </c>
       <c r="J94" s="8"/>
       <c r="K94" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L94" s="4">
         <v>6333</v>
@@ -5413,7 +5410,7 @@
       </c>
       <c r="J95" s="8"/>
       <c r="K95" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L95" s="4">
         <v>6333</v>
@@ -5452,7 +5449,7 @@
       </c>
       <c r="J96" s="8"/>
       <c r="K96" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L96" s="4">
         <v>6335</v>
@@ -5491,7 +5488,7 @@
       </c>
       <c r="J97" s="8"/>
       <c r="K97" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L97" s="4">
         <v>6335</v>
@@ -5530,7 +5527,7 @@
       </c>
       <c r="J98" s="8"/>
       <c r="K98" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L98" s="4">
         <v>6335</v>
@@ -5569,7 +5566,7 @@
       </c>
       <c r="J99" s="8"/>
       <c r="K99" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L99" s="4">
         <v>6335</v>
@@ -5608,7 +5605,7 @@
       </c>
       <c r="J100" s="8"/>
       <c r="K100" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L100" s="4">
         <v>6335</v>
@@ -5647,7 +5644,7 @@
       </c>
       <c r="J101" s="8"/>
       <c r="K101" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L101" s="4">
         <v>6335</v>
@@ -5686,7 +5683,7 @@
       </c>
       <c r="J102" s="8"/>
       <c r="K102" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L102" s="4">
         <v>6335</v>
@@ -5725,7 +5722,7 @@
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L103" s="4">
         <v>6335</v>
@@ -5764,7 +5761,7 @@
       </c>
       <c r="J104" s="8"/>
       <c r="K104" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L104" s="4">
         <v>6335</v>
@@ -5803,7 +5800,7 @@
       </c>
       <c r="J105" s="8"/>
       <c r="K105" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L105" s="4">
         <v>6335</v>
@@ -5842,7 +5839,7 @@
       </c>
       <c r="J106" s="8"/>
       <c r="K106" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="L106" s="4">
         <v>6335</v>
@@ -6090,7 +6087,7 @@
         <v>113</v>
       </c>
       <c r="B113" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C113" s="17" t="s">
         <v>228</v>
@@ -6129,7 +6126,7 @@
         <v>114</v>
       </c>
       <c r="B114" s="12" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C114" s="17" t="s">
         <v>229</v>
@@ -6168,7 +6165,7 @@
         <v>115</v>
       </c>
       <c r="B115" s="12" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C115" s="17" t="s">
         <v>230</v>
@@ -6207,7 +6204,7 @@
         <v>116</v>
       </c>
       <c r="B116" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C116" s="17" t="s">
         <v>231</v>
@@ -6246,7 +6243,7 @@
         <v>117</v>
       </c>
       <c r="B117" s="12" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C117" s="4" t="s">
         <v>232</v>
@@ -6285,7 +6282,7 @@
         <v>118</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C118" s="4" t="s">
         <v>234</v>
@@ -6324,7 +6321,7 @@
         <v>119</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C119" s="4" t="s">
         <v>238</v>
@@ -6363,7 +6360,7 @@
         <v>120</v>
       </c>
       <c r="B120" s="12" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>235</v>
@@ -6402,7 +6399,7 @@
         <v>121</v>
       </c>
       <c r="B121" s="13" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>236</v>
@@ -6441,7 +6438,7 @@
         <v>122</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C122" s="4" t="s">
         <v>237</v>
@@ -6480,7 +6477,7 @@
         <v>123</v>
       </c>
       <c r="B123" s="11" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>238</v>
@@ -6519,7 +6516,7 @@
         <v>124</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C124" s="4" t="s">
         <v>239</v>
@@ -6558,7 +6555,7 @@
         <v>125</v>
       </c>
       <c r="B125" s="12" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C125" s="4" t="s">
         <v>240</v>
@@ -6597,7 +6594,7 @@
         <v>126</v>
       </c>
       <c r="B126" s="12" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C126" s="21" t="s">
         <v>241</v>
@@ -6636,7 +6633,7 @@
         <v>127</v>
       </c>
       <c r="B127" s="11" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C127" s="4" t="s">
         <v>242</v>
@@ -6675,7 +6672,7 @@
         <v>128</v>
       </c>
       <c r="B128" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C128" s="4" t="s">
         <v>245</v>
@@ -6705,8 +6702,8 @@
       <c r="L128" s="4">
         <v>6342</v>
       </c>
-      <c r="M128" s="9" t="s">
-        <v>247</v>
+      <c r="M128" s="9">
+        <v>46117</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6714,10 +6711,10 @@
         <v>129</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D129" s="4" t="s">
         <v>16</v>
@@ -6744,8 +6741,8 @@
       <c r="L129" s="4">
         <v>6342</v>
       </c>
-      <c r="M129" s="9" t="s">
-        <v>247</v>
+      <c r="M129" s="9">
+        <v>46117</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6753,10 +6750,10 @@
         <v>130</v>
       </c>
       <c r="B130" s="11" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D130" s="4" t="s">
         <v>16</v>
@@ -6783,8 +6780,8 @@
       <c r="L130" s="4">
         <v>6342</v>
       </c>
-      <c r="M130" s="9" t="s">
-        <v>247</v>
+      <c r="M130" s="9">
+        <v>46117</v>
       </c>
     </row>
     <row r="131" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -6792,10 +6789,10 @@
         <v>131</v>
       </c>
       <c r="B131" s="12" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D131" s="16" t="s">
         <v>16</v>
@@ -6817,7 +6814,7 @@
       </c>
       <c r="J131" s="8"/>
       <c r="K131" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="L131" s="4">
         <v>6343</v>
@@ -6829,10 +6826,10 @@
     <row r="132" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A132" s="25"/>
       <c r="B132" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="C132" s="35" t="s">
         <v>385</v>
-      </c>
-      <c r="C132" s="35" t="s">
-        <v>386</v>
       </c>
       <c r="D132" s="36" t="s">
         <v>159</v>
@@ -6850,11 +6847,11 @@
         <v>59846</v>
       </c>
       <c r="I132" s="33" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J132" s="29"/>
       <c r="K132" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L132" s="27">
         <v>6338</v>
@@ -6866,10 +6863,10 @@
     <row r="133" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A133" s="25"/>
       <c r="B133" s="26" t="s">
+        <v>377</v>
+      </c>
+      <c r="C133" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="C133" s="27" t="s">
-        <v>379</v>
       </c>
       <c r="D133" s="38" t="s">
         <v>159</v>
@@ -6892,7 +6889,7 @@
       </c>
       <c r="J133" s="29"/>
       <c r="K133" s="36" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L133" s="27">
         <v>6338</v>
@@ -6907,7 +6904,7 @@
         <v>110</v>
       </c>
       <c r="C134" s="27" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D134" s="28" t="s">
         <v>159</v>
@@ -6930,7 +6927,7 @@
       </c>
       <c r="J134" s="29"/>
       <c r="K134" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L134" s="27">
         <v>6338</v>
@@ -6942,10 +6939,10 @@
     <row r="135" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A135" s="25"/>
       <c r="B135" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C135" s="27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D135" s="34" t="s">
         <v>159</v>
@@ -6964,11 +6961,11 @@
         <v>59846</v>
       </c>
       <c r="I135" s="33" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="J135" s="29"/>
       <c r="K135" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L135" s="27">
         <v>6338</v>
@@ -6980,10 +6977,10 @@
     <row r="136" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A136" s="25"/>
       <c r="B136" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="C136" s="27" t="s">
         <v>383</v>
-      </c>
-      <c r="C136" s="27" t="s">
-        <v>384</v>
       </c>
       <c r="D136" s="34" t="s">
         <v>159</v>
@@ -7002,11 +6999,11 @@
         <v>59846</v>
       </c>
       <c r="I136" s="33" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J136" s="29"/>
       <c r="K136" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L136" s="27">
         <v>6338</v>
@@ -7018,10 +7015,10 @@
     <row r="137" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A137" s="25"/>
       <c r="B137" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="C137" s="27" t="s">
         <v>381</v>
-      </c>
-      <c r="C137" s="27" t="s">
-        <v>382</v>
       </c>
       <c r="D137" s="34" t="s">
         <v>159</v>
@@ -7040,11 +7037,11 @@
         <v>59846</v>
       </c>
       <c r="I137" s="33" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J137" s="29"/>
       <c r="K137" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L137" s="27">
         <v>6338</v>
@@ -7056,10 +7053,10 @@
     <row r="138" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A138" s="25"/>
       <c r="B138" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="C138" s="27" t="s">
         <v>387</v>
-      </c>
-      <c r="C138" s="27" t="s">
-        <v>388</v>
       </c>
       <c r="D138" s="34" t="s">
         <v>159</v>
@@ -7078,11 +7075,11 @@
         <v>59846</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="J138" s="29"/>
       <c r="K138" s="32" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="L138" s="27">
         <v>6338</v>
@@ -7096,10 +7093,10 @@
         <v>138</v>
       </c>
       <c r="B139" s="11" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D139" s="4" t="s">
         <v>16</v>
@@ -7135,10 +7132,10 @@
         <v>139</v>
       </c>
       <c r="B140" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="C140" s="14" t="s">
         <v>333</v>
-      </c>
-      <c r="C140" s="14" t="s">
-        <v>334</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>16</v>
@@ -7177,7 +7174,7 @@
         <v>143</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D141" s="4" t="s">
         <v>16</v>
@@ -7213,10 +7210,10 @@
         <v>141</v>
       </c>
       <c r="B142" s="12" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D142" s="4" t="s">
         <v>16</v>
@@ -7252,10 +7249,10 @@
         <v>142</v>
       </c>
       <c r="B143" s="12" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>16</v>
@@ -7291,10 +7288,10 @@
         <v>143</v>
       </c>
       <c r="B144" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>16</v>
@@ -7331,7 +7328,7 @@
       </c>
       <c r="B145" s="6"/>
       <c r="C145" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>16</v>
@@ -7367,10 +7364,10 @@
         <v>145</v>
       </c>
       <c r="B146" s="12" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D146" s="4" t="s">
         <v>16</v>
@@ -7406,10 +7403,10 @@
         <v>146</v>
       </c>
       <c r="B147" s="12" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D147" s="4" t="s">
         <v>16</v>
@@ -7445,10 +7442,10 @@
         <v>147</v>
       </c>
       <c r="B148" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D148" s="4" t="s">
         <v>16</v>
@@ -7484,10 +7481,10 @@
         <v>148</v>
       </c>
       <c r="B149" s="12" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D149" s="4" t="s">
         <v>16</v>
@@ -7523,10 +7520,10 @@
         <v>149</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D150" s="4" t="s">
         <v>16</v>
@@ -7562,10 +7559,10 @@
         <v>150</v>
       </c>
       <c r="B151" s="11" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D151" s="4" t="s">
         <v>16</v>
@@ -7601,10 +7598,10 @@
         <v>151</v>
       </c>
       <c r="B152" s="12" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D152" s="4" t="s">
         <v>16</v>
@@ -7640,10 +7637,10 @@
         <v>152</v>
       </c>
       <c r="B153" s="12" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D153" s="4" t="s">
         <v>16</v>
@@ -7679,10 +7676,10 @@
         <v>153</v>
       </c>
       <c r="B154" s="12" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D154" s="4" t="s">
         <v>16</v>
@@ -7718,10 +7715,10 @@
         <v>154</v>
       </c>
       <c r="B155" s="11" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D155" s="4" t="s">
         <v>16</v>
@@ -7739,7 +7736,7 @@
         <v>93</v>
       </c>
       <c r="I155" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J155" s="8"/>
       <c r="K155" s="4" t="s">
@@ -7757,10 +7754,10 @@
         <v>155</v>
       </c>
       <c r="B156" s="11" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D156" s="4" t="s">
         <v>16</v>
@@ -7778,7 +7775,7 @@
         <v>93</v>
       </c>
       <c r="I156" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J156" s="8"/>
       <c r="K156" s="4" t="s">
@@ -7796,10 +7793,10 @@
         <v>156</v>
       </c>
       <c r="B157" s="12" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>16</v>
@@ -7817,7 +7814,7 @@
         <v>93</v>
       </c>
       <c r="I157" s="9" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J157" s="8"/>
       <c r="K157" s="4" t="s">
@@ -7835,10 +7832,10 @@
         <v>157</v>
       </c>
       <c r="B158" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D158" s="4" t="s">
         <v>16</v>
@@ -7856,7 +7853,7 @@
         <v>93</v>
       </c>
       <c r="I158" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J158" s="8"/>
       <c r="K158" s="4" t="s">
@@ -7874,10 +7871,10 @@
         <v>158</v>
       </c>
       <c r="B159" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D159" s="4" t="s">
         <v>16</v>
@@ -7895,7 +7892,7 @@
         <v>93</v>
       </c>
       <c r="I159" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J159" s="8"/>
       <c r="K159" s="4" t="s">
@@ -7913,10 +7910,10 @@
         <v>159</v>
       </c>
       <c r="B160" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D160" s="4" t="s">
         <v>16</v>
@@ -7934,7 +7931,7 @@
         <v>713</v>
       </c>
       <c r="I160" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J160" s="8"/>
       <c r="K160" s="4" t="s">
@@ -7952,10 +7949,10 @@
         <v>160</v>
       </c>
       <c r="B161" s="12" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D161" s="4" t="s">
         <v>16</v>
@@ -7973,7 +7970,7 @@
         <v>713</v>
       </c>
       <c r="I161" s="9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J161" s="8"/>
       <c r="K161" s="4" t="s">
@@ -7991,10 +7988,10 @@
         <v>161</v>
       </c>
       <c r="B162" s="12" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D162" s="4" t="s">
         <v>16</v>
@@ -8012,11 +8009,11 @@
         <v>6350</v>
       </c>
       <c r="I162" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J162" s="8"/>
       <c r="K162" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="L162" s="4">
         <v>6350</v>
@@ -8033,7 +8030,7 @@
         <v>45</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D163" s="4" t="s">
         <v>16</v>
@@ -8051,17 +8048,17 @@
         <v>26</v>
       </c>
       <c r="I163" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J163" s="8"/>
       <c r="K163" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="L163" s="4">
         <v>6351</v>
       </c>
       <c r="M163" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8072,7 +8069,7 @@
         <v>45</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D164" s="4" t="s">
         <v>16</v>
@@ -8090,17 +8087,17 @@
         <v>141</v>
       </c>
       <c r="I164" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J164" s="8"/>
       <c r="K164" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L164" s="4">
         <v>6358</v>
       </c>
       <c r="M164" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8108,10 +8105,10 @@
         <v>164</v>
       </c>
       <c r="B165" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>16</v>
@@ -8129,7 +8126,7 @@
         <v>1528</v>
       </c>
       <c r="I165" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J165" s="8"/>
       <c r="K165" s="4" t="s">
@@ -8139,7 +8136,7 @@
         <v>6359</v>
       </c>
       <c r="M165" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8147,10 +8144,10 @@
         <v>165</v>
       </c>
       <c r="B166" s="12" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D166" s="4" t="s">
         <v>16</v>
@@ -8168,7 +8165,7 @@
         <v>1528</v>
       </c>
       <c r="I166" s="9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J166" s="8"/>
       <c r="K166" s="4" t="s">
@@ -8178,7 +8175,7 @@
         <v>6359</v>
       </c>
       <c r="M166" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8186,10 +8183,10 @@
         <v>166</v>
       </c>
       <c r="B167" s="11" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D167" s="4" t="s">
         <v>16</v>
@@ -8207,17 +8204,17 @@
         <v>142</v>
       </c>
       <c r="I167" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J167" s="8"/>
       <c r="K167" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L167" s="4">
         <v>6360</v>
       </c>
       <c r="M167" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8225,10 +8222,10 @@
         <v>167</v>
       </c>
       <c r="B168" s="11" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D168" s="4" t="s">
         <v>16</v>
@@ -8246,17 +8243,17 @@
         <v>142</v>
       </c>
       <c r="I168" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J168" s="8"/>
       <c r="K168" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L168" s="4">
         <v>6360</v>
       </c>
       <c r="M168" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8264,10 +8261,10 @@
         <v>168</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D169" s="4" t="s">
         <v>16</v>
@@ -8285,17 +8282,17 @@
         <v>143</v>
       </c>
       <c r="I169" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J169" s="8"/>
       <c r="K169" s="4" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="L169" s="4">
         <v>6361</v>
       </c>
       <c r="M169" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="170" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8303,10 +8300,10 @@
         <v>169</v>
       </c>
       <c r="B170" s="11" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D170" s="4" t="s">
         <v>16</v>
@@ -8324,7 +8321,7 @@
         <v>94</v>
       </c>
       <c r="I170" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J170" s="8"/>
       <c r="K170" s="4" t="s">
@@ -8334,7 +8331,7 @@
         <v>6362</v>
       </c>
       <c r="M170" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8343,7 +8340,7 @@
       </c>
       <c r="B171" s="12"/>
       <c r="C171" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>16</v>
@@ -8361,7 +8358,7 @@
         <v>94</v>
       </c>
       <c r="I171" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J171" s="8"/>
       <c r="K171" s="4" t="s">
@@ -8371,7 +8368,7 @@
         <v>6362</v>
       </c>
       <c r="M171" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8379,10 +8376,10 @@
         <v>171</v>
       </c>
       <c r="B172" s="12" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D172" s="4" t="s">
         <v>16</v>
@@ -8400,7 +8397,7 @@
         <v>94</v>
       </c>
       <c r="I172" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J172" s="8"/>
       <c r="K172" s="4" t="s">
@@ -8410,7 +8407,7 @@
         <v>6362</v>
       </c>
       <c r="M172" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8418,10 +8415,10 @@
         <v>172</v>
       </c>
       <c r="B173" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D173" s="4" t="s">
         <v>16</v>
@@ -8439,7 +8436,7 @@
         <v>94</v>
       </c>
       <c r="I173" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J173" s="8"/>
       <c r="K173" s="4" t="s">
@@ -8449,7 +8446,7 @@
         <v>6362</v>
       </c>
       <c r="M173" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8457,10 +8454,10 @@
         <v>173</v>
       </c>
       <c r="B174" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D174" s="4" t="s">
         <v>16</v>
@@ -8478,7 +8475,7 @@
         <v>94</v>
       </c>
       <c r="I174" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J174" s="8"/>
       <c r="K174" s="4" t="s">
@@ -8488,7 +8485,7 @@
         <v>6362</v>
       </c>
       <c r="M174" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8496,10 +8493,10 @@
         <v>174</v>
       </c>
       <c r="B175" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D175" s="4" t="s">
         <v>16</v>
@@ -8517,7 +8514,7 @@
         <v>14057</v>
       </c>
       <c r="I175" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J175" s="8"/>
       <c r="K175" s="4" t="s">
@@ -8527,7 +8524,7 @@
         <v>6363</v>
       </c>
       <c r="M175" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="176" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8535,10 +8532,10 @@
         <v>175</v>
       </c>
       <c r="B176" s="12" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D176" s="4" t="s">
         <v>16</v>
@@ -8556,7 +8553,7 @@
         <v>14057</v>
       </c>
       <c r="I176" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J176" s="8"/>
       <c r="K176" s="4" t="s">
@@ -8566,7 +8563,7 @@
         <v>6363</v>
       </c>
       <c r="M176" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="177" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8574,10 +8571,10 @@
         <v>176</v>
       </c>
       <c r="B177" s="12" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D177" s="4" t="s">
         <v>16</v>
@@ -8595,7 +8592,7 @@
         <v>14057</v>
       </c>
       <c r="I177" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J177" s="8"/>
       <c r="K177" s="4" t="s">
@@ -8605,7 +8602,7 @@
         <v>6363</v>
       </c>
       <c r="M177" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="178" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8616,7 +8613,7 @@
         <v>38</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D178" s="4" t="s">
         <v>16</v>
@@ -8634,7 +8631,7 @@
         <v>2464</v>
       </c>
       <c r="I178" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J178" s="8"/>
       <c r="K178" s="4" t="s">
@@ -8644,7 +8641,7 @@
         <v>6364</v>
       </c>
       <c r="M178" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8655,7 +8652,7 @@
         <v>49</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D179" s="4" t="s">
         <v>16</v>
@@ -8673,7 +8670,7 @@
         <v>2464</v>
       </c>
       <c r="I179" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J179" s="8"/>
       <c r="K179" s="4" t="s">
@@ -8683,7 +8680,7 @@
         <v>6364</v>
       </c>
       <c r="M179" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8691,10 +8688,10 @@
         <v>179</v>
       </c>
       <c r="B180" s="11" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D180" s="4" t="s">
         <v>16</v>
@@ -8712,7 +8709,7 @@
         <v>2464</v>
       </c>
       <c r="I180" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J180" s="8"/>
       <c r="K180" s="4" t="s">
@@ -8722,7 +8719,7 @@
         <v>6364</v>
       </c>
       <c r="M180" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="181" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8730,10 +8727,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="11" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D181" s="4" t="s">
         <v>16</v>
@@ -8751,7 +8748,7 @@
         <v>2464</v>
       </c>
       <c r="I181" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J181" s="8"/>
       <c r="K181" s="4" t="s">
@@ -8761,7 +8758,7 @@
         <v>6364</v>
       </c>
       <c r="M181" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="182" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8772,7 +8769,7 @@
         <v>50</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D182" s="4" t="s">
         <v>16</v>
@@ -8790,7 +8787,7 @@
         <v>2464</v>
       </c>
       <c r="I182" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J182" s="8"/>
       <c r="K182" s="4" t="s">
@@ -8800,7 +8797,7 @@
         <v>6364</v>
       </c>
       <c r="M182" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8811,7 +8808,7 @@
         <v>47</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D183" s="4" t="s">
         <v>16</v>
@@ -8829,7 +8826,7 @@
         <v>2464</v>
       </c>
       <c r="I183" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J183" s="8"/>
       <c r="K183" s="4" t="s">
@@ -8839,7 +8836,7 @@
         <v>6364</v>
       </c>
       <c r="M183" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8847,10 +8844,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="D184" s="4" t="s">
         <v>16</v>
@@ -8868,7 +8865,7 @@
         <v>2464</v>
       </c>
       <c r="I184" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J184" s="8"/>
       <c r="K184" s="4" t="s">
@@ -8878,7 +8875,7 @@
         <v>6364</v>
       </c>
       <c r="M184" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="185" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8907,7 +8904,7 @@
         <v>2464</v>
       </c>
       <c r="I185" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J185" s="8"/>
       <c r="K185" s="4" t="s">
@@ -8917,7 +8914,7 @@
         <v>6364</v>
       </c>
       <c r="M185" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="186" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8925,10 +8922,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D186" s="4" t="s">
         <v>16</v>
@@ -8946,7 +8943,7 @@
         <v>2464</v>
       </c>
       <c r="I186" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J186" s="8"/>
       <c r="K186" s="4" t="s">
@@ -8956,7 +8953,7 @@
         <v>6364</v>
       </c>
       <c r="M186" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="187" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -8967,7 +8964,7 @@
         <v>42</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D187" s="4" t="s">
         <v>16</v>
@@ -8985,7 +8982,7 @@
         <v>2464</v>
       </c>
       <c r="I187" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J187" s="8"/>
       <c r="K187" s="4" t="s">
@@ -8995,7 +8992,7 @@
         <v>6364</v>
       </c>
       <c r="M187" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9006,7 +9003,7 @@
         <v>43</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="D188" s="4" t="s">
         <v>16</v>
@@ -9024,7 +9021,7 @@
         <v>2464</v>
       </c>
       <c r="I188" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J188" s="8"/>
       <c r="K188" s="4" t="s">
@@ -9034,7 +9031,7 @@
         <v>6364</v>
       </c>
       <c r="M188" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="189" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9063,7 +9060,7 @@
         <v>2464</v>
       </c>
       <c r="I189" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J189" s="8"/>
       <c r="K189" s="4" t="s">
@@ -9073,7 +9070,7 @@
         <v>6364</v>
       </c>
       <c r="M189" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="190" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9102,7 +9099,7 @@
         <v>2464</v>
       </c>
       <c r="I190" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J190" s="8"/>
       <c r="K190" s="4" t="s">
@@ -9112,7 +9109,7 @@
         <v>6365</v>
       </c>
       <c r="M190" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="191" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9120,10 +9117,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>16</v>
@@ -9141,7 +9138,7 @@
         <v>2464</v>
       </c>
       <c r="I191" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J191" s="8"/>
       <c r="K191" s="4" t="s">
@@ -9151,7 +9148,7 @@
         <v>6365</v>
       </c>
       <c r="M191" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="192" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9159,10 +9156,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D192" s="4" t="s">
         <v>16</v>
@@ -9180,7 +9177,7 @@
         <v>2464</v>
       </c>
       <c r="I192" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J192" s="8"/>
       <c r="K192" s="4" t="s">
@@ -9190,7 +9187,7 @@
         <v>6365</v>
       </c>
       <c r="M192" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="193" spans="1:13" ht="28.9" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -9219,7 +9216,7 @@
         <v>2464</v>
       </c>
       <c r="I193" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J193" s="8"/>
       <c r="K193" s="4" t="s">
@@ -9229,7 +9226,7 @@
         <v>6365</v>
       </c>
       <c r="M193" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
